--- a/Lab9_11-v1-3.xlsx
+++ b/Lab9_11-v1-3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://masseyuni-my.sharepoint.com/personal/ajmurphy_massey_ac_nz/Documents/115.109 Shared/Lab Worksheets 2602/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/528060d74b554012/Pictures/Lab-9-and-11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{ACD3182E-A37D-3D45-8E9A-761CA87F184A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE1AD19A-AC04-9744-B56F-5F012011BADF}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{ACD3182E-A37D-3D45-8E9A-761CA87F184A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02F2EE6C-FC6A-4EA3-A3BC-A3D1DB39AA20}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lab 9" sheetId="1" r:id="rId1"/>
@@ -2862,7 +2862,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="1025">
   <si>
     <t>X</t>
   </si>
@@ -6817,6 +6817,9 @@
   <si>
     <t>Version: 1.3 (29 Sept 2026)</t>
   </si>
+  <si>
+    <t>ŷ = 5.58 + 0.38X</t>
+  </si>
 </sst>
 </file>
 
@@ -6831,7 +6834,7 @@
     <numFmt numFmtId="168" formatCode="0.000000"/>
     <numFmt numFmtId="169" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="57" x14ac:knownFonts="1">
+  <fonts count="57">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -8231,6 +8234,282 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Test 2 mark vs Test 1 mark</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lab 9'!$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Lab 9'!$B$7:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.83</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.83</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.83</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9.33</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Lab 9'!$C$7:$C$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1614-4A5D-A338-1654E7A3D3AD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="169843232"/>
+        <c:axId val="1715986832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="169843232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1715986832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1715986832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="169843232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11123,15 +11402,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>866140</xdr:colOff>
+      <xdr:colOff>863599</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>111760</xdr:rowOff>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>510997</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>469899</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>157863</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11146,8 +11425,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5722620" y="13868400"/>
-          <a:ext cx="3119577" cy="1062103"/>
+          <a:off x="5702299" y="13411200"/>
+          <a:ext cx="6413500" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11180,11 +11459,22 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1000">
+            <a:rPr lang="cy-GB" sz="1000">
               <a:effectLst/>
             </a:rPr>
             <a:t>&lt;&lt;Data Interpretation&gt;&gt;</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="cy-GB" sz="1000">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Positive, moderately strong linear relationship: students scoring higher in Test 1 tended to score higher in Test 2. Trendline ŷ = 5.58 + 0.38X: each extra Test 1 mark is associated with about 0.38 of an extra Test 2 mark, on average. R2 = 0.404: Test 1 marks explain about 40% of the variation in Test 2 marks; the rest is due to other factors. The student with Test 1 = 2 and Test 2 = 5 is an outlier that weakens the fit.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11261,8 +11551,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12798585" y="15278100"/>
-          <a:ext cx="7993137" cy="2308860"/>
+          <a:off x="12737625" y="14866620"/>
+          <a:ext cx="7947417" cy="2252980"/>
           <a:chOff x="12798585" y="15278100"/>
           <a:chExt cx="7993137" cy="2308860"/>
         </a:xfrm>
@@ -11581,8 +11871,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="17453123" y="18227040"/>
-          <a:ext cx="10733257" cy="3410442"/>
+          <a:off x="17366763" y="17739360"/>
+          <a:ext cx="10667217" cy="3334242"/>
           <a:chOff x="17747763" y="19822160"/>
           <a:chExt cx="10733257" cy="3410442"/>
         </a:xfrm>
@@ -12002,8 +12292,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="26751280" y="16073120"/>
-          <a:ext cx="5179060" cy="2471420"/>
+          <a:off x="26609040" y="15641320"/>
+          <a:ext cx="5148580" cy="2410460"/>
           <a:chOff x="22555200" y="16062960"/>
           <a:chExt cx="5179060" cy="2471420"/>
         </a:xfrm>
@@ -12166,8 +12456,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="21874480" y="16111205"/>
-          <a:ext cx="4434989" cy="1638315"/>
+          <a:off x="21757640" y="15679405"/>
+          <a:ext cx="4409589" cy="1597675"/>
           <a:chOff x="21539200" y="15989285"/>
           <a:chExt cx="4434989" cy="1638315"/>
         </a:xfrm>
@@ -12307,8 +12597,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="28641040" y="18836640"/>
-          <a:ext cx="7742470" cy="1460568"/>
+          <a:off x="28483560" y="18338800"/>
+          <a:ext cx="7696750" cy="1425008"/>
           <a:chOff x="28691840" y="16012160"/>
           <a:chExt cx="7742470" cy="1460568"/>
         </a:xfrm>
@@ -12430,6 +12720,42 @@
         </xdr:spPr>
       </xdr:pic>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Task1Scatter">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{218B2CE9-BD5B-B70B-AB85-D1941DCDBB24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -18588,8 +18914,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14661156" y="33766535"/>
-          <a:ext cx="5350831" cy="2817051"/>
+          <a:off x="14712992" y="32461978"/>
+          <a:ext cx="5376750" cy="2786812"/>
           <a:chOff x="14661156" y="33766535"/>
           <a:chExt cx="5350831" cy="2817051"/>
         </a:xfrm>
@@ -18902,8 +19228,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="19906013" y="33766536"/>
-          <a:ext cx="6116459" cy="2643673"/>
+          <a:off x="19983768" y="32461979"/>
+          <a:ext cx="6146697" cy="2613434"/>
           <a:chOff x="19906013" y="33766536"/>
           <a:chExt cx="6116459" cy="2643673"/>
         </a:xfrm>
@@ -19151,8 +19477,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12055112" y="35239821"/>
-          <a:ext cx="7098735" cy="3186922"/>
+          <a:off x="12093989" y="33909345"/>
+          <a:ext cx="7133293" cy="3143724"/>
           <a:chOff x="12055112" y="35239821"/>
           <a:chExt cx="7098735" cy="3186922"/>
         </a:xfrm>
@@ -19904,7 +20230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI215"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
@@ -19912,7 +20238,7 @@
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="26">
       <c r="A1" s="6" t="s">
         <v>34</v>
       </c>
@@ -19922,7 +20248,7 @@
       <c r="H1" s="56"/>
       <c r="I1" s="57"/>
     </row>
-    <row r="2" spans="1:10" ht="26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="26">
       <c r="A2" s="9" t="s">
         <v>328</v>
       </c>
@@ -19937,10 +20263,10 @@
       <c r="H2" s="56"/>
       <c r="I2" s="57"/>
     </row>
-    <row r="3" spans="1:10" ht="26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="26">
       <c r="A3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="73" t="s">
         <v>270</v>
       </c>
@@ -19954,7 +20280,7 @@
       <c r="I4" s="73"/>
       <c r="J4" s="73"/>
     </row>
-    <row r="5" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -19974,7 +20300,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
@@ -20000,313 +20326,676 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="91">
         <v>9.83</v>
       </c>
       <c r="C7" s="91">
         <v>8</v>
       </c>
-      <c r="E7" s="87"/>
+      <c r="E7" s="87">
+        <f>B7-B$27</f>
+        <v>2.2599999999999998</v>
+      </c>
       <c r="F7" s="20">
         <f>C7-C$27</f>
-        <v>8</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>-0.42500000000000071</v>
+      </c>
+      <c r="G7" s="3">
+        <f>E7*F7</f>
+        <v>-0.96050000000000146</v>
+      </c>
+      <c r="H7" s="3">
+        <f>E7*E7</f>
+        <v>5.1075999999999988</v>
+      </c>
+      <c r="I7" s="51">
+        <f>H$29+H$28*B7</f>
+        <v>9.2738788794209697</v>
+      </c>
+      <c r="J7" s="51">
+        <f>C7-I7</f>
+        <v>-1.2738788794209697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" s="91">
         <v>8.5</v>
       </c>
       <c r="C8" s="91">
         <v>10</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E8" s="20">
+        <f>B8-B$27</f>
+        <v>0.92999999999999972</v>
+      </c>
+      <c r="F8" s="20">
+        <f>C8-C$27</f>
+        <v>1.5749999999999993</v>
+      </c>
+      <c r="G8" s="3">
+        <f>E8*F8</f>
+        <v>1.4647499999999989</v>
+      </c>
+      <c r="H8" s="3">
+        <f>E8*E8</f>
+        <v>0.86489999999999945</v>
+      </c>
+      <c r="I8" s="51">
+        <f>H$29+H$28*B8</f>
+        <v>8.7743174149829652</v>
+      </c>
+      <c r="J8" s="51">
+        <f>C8-I8</f>
+        <v>1.2256825850170348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="91">
         <v>8.83</v>
       </c>
       <c r="C9" s="91">
         <v>9</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E9" s="20">
+        <f>B9-B$27</f>
+        <v>1.2599999999999998</v>
+      </c>
+      <c r="F9" s="20">
+        <f>C9-C$27</f>
+        <v>0.57499999999999929</v>
+      </c>
+      <c r="G9" s="3">
+        <f>E9*F9</f>
+        <v>0.72449999999999903</v>
+      </c>
+      <c r="H9" s="3">
+        <f>E9*E9</f>
+        <v>1.5875999999999995</v>
+      </c>
+      <c r="I9" s="51">
+        <f>H$29+H$28*B9</f>
+        <v>8.8982687557833717</v>
+      </c>
+      <c r="J9" s="51">
+        <f>C9-I9</f>
+        <v>0.10173124421662827</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" s="91">
         <v>7.5</v>
       </c>
       <c r="C10" s="91">
         <v>10</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E10" s="20">
+        <f>B10-B$27</f>
+        <v>-7.0000000000000284E-2</v>
+      </c>
+      <c r="F10" s="20">
+        <f>C10-C$27</f>
+        <v>1.5749999999999993</v>
+      </c>
+      <c r="G10" s="3">
+        <f>E10*F10</f>
+        <v>-0.1102500000000004</v>
+      </c>
+      <c r="H10" s="3">
+        <f>E10*E10</f>
+        <v>4.9000000000000397E-3</v>
+      </c>
+      <c r="I10" s="51">
+        <f>H$29+H$28*B10</f>
+        <v>8.3987072913453691</v>
+      </c>
+      <c r="J10" s="51">
+        <f>C10-I10</f>
+        <v>1.6012927086546309</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" s="91">
         <v>5.42</v>
       </c>
       <c r="C11" s="91">
         <v>8</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E11" s="20">
+        <f>B11-B$27</f>
+        <v>-2.1500000000000004</v>
+      </c>
+      <c r="F11" s="20">
+        <f>C11-C$27</f>
+        <v>-0.42500000000000071</v>
+      </c>
+      <c r="G11" s="3">
+        <f>E11*F11</f>
+        <v>0.91375000000000173</v>
+      </c>
+      <c r="H11" s="3">
+        <f>E11*E11</f>
+        <v>4.6225000000000014</v>
+      </c>
+      <c r="I11" s="51">
+        <f>H$29+H$28*B11</f>
+        <v>7.6174382341791684</v>
+      </c>
+      <c r="J11" s="51">
+        <f>C11-I11</f>
+        <v>0.38256176582083157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" s="91">
         <v>4</v>
       </c>
       <c r="C12" s="91">
         <v>8</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E12" s="20">
+        <f>B12-B$27</f>
+        <v>-3.5700000000000003</v>
+      </c>
+      <c r="F12" s="87">
+        <f>C12-C$27</f>
+        <v>-0.42500000000000071</v>
+      </c>
+      <c r="G12" s="3">
+        <f>E12*F12</f>
+        <v>1.5172500000000027</v>
+      </c>
+      <c r="H12" s="3">
+        <f>E12*E12</f>
+        <v>12.744900000000001</v>
+      </c>
+      <c r="I12" s="51">
+        <f>H$29+H$28*B12</f>
+        <v>7.0840718586137807</v>
+      </c>
+      <c r="J12" s="51">
+        <f>C12-I12</f>
+        <v>0.91592814138621925</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" s="91">
         <v>9.5</v>
       </c>
       <c r="C13" s="91">
         <v>9</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E13" s="20">
+        <f>B13-B$27</f>
+        <v>1.9299999999999997</v>
+      </c>
+      <c r="F13" s="20">
+        <f>C13-C$27</f>
+        <v>0.57499999999999929</v>
+      </c>
+      <c r="G13" s="3">
+        <f>E13*F13</f>
+        <v>1.1097499999999985</v>
+      </c>
+      <c r="H13" s="3">
+        <f>E13*E13</f>
+        <v>3.724899999999999</v>
+      </c>
+      <c r="I13" s="51">
+        <f>H$29+H$28*B13</f>
+        <v>9.1499275386205632</v>
+      </c>
+      <c r="J13" s="51">
+        <f>C13-I13</f>
+        <v>-0.14992753862056318</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="91">
         <v>6.83</v>
       </c>
       <c r="C14" s="91">
         <v>7</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E14" s="20">
+        <f>B14-B$27</f>
+        <v>-0.74000000000000021</v>
+      </c>
+      <c r="F14" s="20">
+        <f>C14-C$27</f>
+        <v>-1.4250000000000007</v>
+      </c>
+      <c r="G14" s="3">
+        <f>E14*F14</f>
+        <v>1.0545000000000009</v>
+      </c>
+      <c r="H14" s="3">
+        <f>E14*E14</f>
+        <v>0.54760000000000031</v>
+      </c>
+      <c r="I14" s="51">
+        <f>H$29+H$28*B14</f>
+        <v>8.1470485085081794</v>
+      </c>
+      <c r="J14" s="51">
+        <f>C14-I14</f>
+        <v>-1.1470485085081794</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" s="91">
         <v>6.83</v>
       </c>
       <c r="C15" s="91">
         <v>8.5</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E15" s="20">
+        <f>B15-B$27</f>
+        <v>-0.74000000000000021</v>
+      </c>
+      <c r="F15" s="20">
+        <f>C15-C$27</f>
+        <v>7.4999999999999289E-2</v>
+      </c>
+      <c r="G15" s="3">
+        <f>E15*F15</f>
+        <v>-5.5499999999999487E-2</v>
+      </c>
+      <c r="H15" s="3">
+        <f>E15*E15</f>
+        <v>0.54760000000000031</v>
+      </c>
+      <c r="I15" s="51">
+        <f>H$29+H$28*B15</f>
+        <v>8.1470485085081794</v>
+      </c>
+      <c r="J15" s="51">
+        <f>C15-I15</f>
+        <v>0.35295149149182059</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16" s="91">
         <v>7.5</v>
       </c>
       <c r="C16" s="91">
         <v>9.5</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E16" s="20">
+        <f>B16-B$27</f>
+        <v>-7.0000000000000284E-2</v>
+      </c>
+      <c r="F16" s="20">
+        <f>C16-C$27</f>
+        <v>1.0749999999999993</v>
+      </c>
+      <c r="G16" s="3">
+        <f>E16*F16</f>
+        <v>-7.5250000000000261E-2</v>
+      </c>
+      <c r="H16" s="3">
+        <f>E16*E16</f>
+        <v>4.9000000000000397E-3</v>
+      </c>
+      <c r="I16" s="51">
+        <f>H$29+H$28*B16</f>
+        <v>8.3987072913453691</v>
+      </c>
+      <c r="J16" s="51">
+        <f>C16-I16</f>
+        <v>1.1012927086546309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="B17" s="91">
         <v>8</v>
       </c>
       <c r="C17" s="91">
         <v>7.5</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E17" s="20">
+        <f>B17-B$27</f>
+        <v>0.42999999999999972</v>
+      </c>
+      <c r="F17" s="20">
+        <f>C17-C$27</f>
+        <v>-0.92500000000000071</v>
+      </c>
+      <c r="G17" s="3">
+        <f>E17*F17</f>
+        <v>-0.39775000000000005</v>
+      </c>
+      <c r="H17" s="3">
+        <f>E17*E17</f>
+        <v>0.18489999999999976</v>
+      </c>
+      <c r="I17" s="51">
+        <f>H$29+H$28*B17</f>
+        <v>8.5865123531641672</v>
+      </c>
+      <c r="J17" s="51">
+        <f>C17-I17</f>
+        <v>-1.0865123531641672</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="B18" s="91">
         <v>9</v>
       </c>
       <c r="C18" s="91">
         <v>10</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E18" s="20">
+        <f>B18-B$27</f>
+        <v>1.4299999999999997</v>
+      </c>
+      <c r="F18" s="20">
+        <f>C18-C$27</f>
+        <v>1.5749999999999993</v>
+      </c>
+      <c r="G18" s="3">
+        <f>E18*F18</f>
+        <v>2.2522499999999988</v>
+      </c>
+      <c r="H18" s="3">
+        <f>E18*E18</f>
+        <v>2.0448999999999993</v>
+      </c>
+      <c r="I18" s="51">
+        <f>H$29+H$28*B18</f>
+        <v>8.9621224768017633</v>
+      </c>
+      <c r="J18" s="51">
+        <f>C18-I18</f>
+        <v>1.0378775231982367</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="B19" s="91">
         <v>8.83</v>
       </c>
       <c r="C19" s="91">
         <v>8</v>
       </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="65"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E19" s="20">
+        <f>B19-B$27</f>
+        <v>1.2599999999999998</v>
+      </c>
+      <c r="F19" s="20">
+        <f>C19-C$27</f>
+        <v>-0.42500000000000071</v>
+      </c>
+      <c r="G19" s="3">
+        <f>E19*F19</f>
+        <v>-0.53550000000000075</v>
+      </c>
+      <c r="H19" s="3">
+        <f>E19*E19</f>
+        <v>1.5875999999999995</v>
+      </c>
+      <c r="I19" s="51">
+        <f>H$29+H$28*B19</f>
+        <v>8.8982687557833717</v>
+      </c>
+      <c r="J19" s="65">
+        <f>C19-I19</f>
+        <v>-0.89826875578337173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="B20" s="91">
         <v>8.5</v>
       </c>
       <c r="C20" s="91">
         <v>9</v>
       </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E20" s="20">
+        <f>B20-B$27</f>
+        <v>0.92999999999999972</v>
+      </c>
+      <c r="F20" s="20">
+        <f>C20-C$27</f>
+        <v>0.57499999999999929</v>
+      </c>
+      <c r="G20" s="3">
+        <f>E20*F20</f>
+        <v>0.53474999999999917</v>
+      </c>
+      <c r="H20" s="3">
+        <f>E20*E20</f>
+        <v>0.86489999999999945</v>
+      </c>
+      <c r="I20" s="51">
+        <f>H$29+H$28*B20</f>
+        <v>8.7743174149829652</v>
+      </c>
+      <c r="J20" s="51">
+        <f>C20-I20</f>
+        <v>0.22568258501703475</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="B21" s="91">
         <v>2</v>
       </c>
       <c r="C21" s="91">
         <v>5</v>
       </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="51"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E21" s="20">
+        <f>B21-B$27</f>
+        <v>-5.57</v>
+      </c>
+      <c r="F21" s="20">
+        <f>C21-C$27</f>
+        <v>-3.4250000000000007</v>
+      </c>
+      <c r="G21" s="90">
+        <f>E21*F21</f>
+        <v>19.077250000000006</v>
+      </c>
+      <c r="H21" s="3">
+        <f>E21*E21</f>
+        <v>31.024900000000002</v>
+      </c>
+      <c r="I21" s="74">
+        <f>H$29+H$28*B21</f>
+        <v>6.3328516113385875</v>
+      </c>
+      <c r="J21" s="51">
+        <f>C21-I21</f>
+        <v>-1.3328516113385875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="B22" s="91">
         <v>4.5</v>
       </c>
       <c r="C22" s="91">
         <v>7.5</v>
       </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E22" s="20">
+        <f>B22-B$27</f>
+        <v>-3.0700000000000003</v>
+      </c>
+      <c r="F22" s="20">
+        <f>C22-C$27</f>
+        <v>-0.92500000000000071</v>
+      </c>
+      <c r="G22" s="3">
+        <f>E22*F22</f>
+        <v>2.8397500000000027</v>
+      </c>
+      <c r="H22" s="3">
+        <f>E22*E22</f>
+        <v>9.4249000000000009</v>
+      </c>
+      <c r="I22" s="51">
+        <f>H$29+H$28*B22</f>
+        <v>7.2718769204325788</v>
+      </c>
+      <c r="J22" s="51">
+        <f>C22-I22</f>
+        <v>0.22812307956742117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="B23" s="91">
         <v>8</v>
       </c>
       <c r="C23" s="91">
         <v>8</v>
       </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E23" s="20">
+        <f>B23-B$27</f>
+        <v>0.42999999999999972</v>
+      </c>
+      <c r="F23" s="20">
+        <f>C23-C$27</f>
+        <v>-0.42500000000000071</v>
+      </c>
+      <c r="G23" s="3">
+        <f>E23*F23</f>
+        <v>-0.18275000000000019</v>
+      </c>
+      <c r="H23" s="3">
+        <f>E23*E23</f>
+        <v>0.18489999999999976</v>
+      </c>
+      <c r="I23" s="51">
+        <f>H$29+H$28*B23</f>
+        <v>8.5865123531641672</v>
+      </c>
+      <c r="J23" s="51">
+        <f>C23-I23</f>
+        <v>-0.58651235316416717</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="B24" s="91">
         <v>9.33</v>
       </c>
       <c r="C24" s="91">
         <v>7.5</v>
       </c>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E24" s="20">
+        <f>B24-B$27</f>
+        <v>1.7599999999999998</v>
+      </c>
+      <c r="F24" s="20">
+        <f>C24-C$27</f>
+        <v>-0.92500000000000071</v>
+      </c>
+      <c r="G24" s="3">
+        <f>E24*F24</f>
+        <v>-1.628000000000001</v>
+      </c>
+      <c r="H24" s="3">
+        <f>E24*E24</f>
+        <v>3.0975999999999995</v>
+      </c>
+      <c r="I24" s="51">
+        <f>H$29+H$28*B24</f>
+        <v>9.0860738176021698</v>
+      </c>
+      <c r="J24" s="51">
+        <f>C24-I24</f>
+        <v>-1.5860738176021698</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="B25" s="91">
         <v>10</v>
       </c>
       <c r="C25" s="91">
         <v>10</v>
       </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E25" s="20">
+        <f>B25-B$27</f>
+        <v>2.4299999999999997</v>
+      </c>
+      <c r="F25" s="20">
+        <f>C25-C$27</f>
+        <v>1.5749999999999993</v>
+      </c>
+      <c r="G25" s="3">
+        <f>E25*F25</f>
+        <v>3.827249999999998</v>
+      </c>
+      <c r="H25" s="90">
+        <f>E25*E25</f>
+        <v>5.9048999999999987</v>
+      </c>
+      <c r="I25" s="51">
+        <f>H$29+H$28*B25</f>
+        <v>9.3377326004393595</v>
+      </c>
+      <c r="J25" s="51">
+        <f>C25-I25</f>
+        <v>0.66226739956064051</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="B26" s="91">
         <v>8.5</v>
       </c>
       <c r="C26" s="91">
         <v>9</v>
       </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-    </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E26" s="20">
+        <f>B26-B$27</f>
+        <v>0.92999999999999972</v>
+      </c>
+      <c r="F26" s="20">
+        <f>C26-C$27</f>
+        <v>0.57499999999999929</v>
+      </c>
+      <c r="G26" s="3">
+        <f>E26*F26</f>
+        <v>0.53474999999999917</v>
+      </c>
+      <c r="H26" s="3">
+        <f>E26*E26</f>
+        <v>0.86489999999999945</v>
+      </c>
+      <c r="I26" s="51">
+        <f>H$29+H$28*B26</f>
+        <v>8.7743174149829652</v>
+      </c>
+      <c r="J26" s="51">
+        <f>C26-I26</f>
+        <v>0.22568258501703475</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="18" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="88"/>
-      <c r="C27" s="87"/>
+      <c r="B27" s="88">
+        <f>AVERAGE(B7:B26)</f>
+        <v>7.57</v>
+      </c>
+      <c r="C27" s="87">
+        <f>AVERAGE(C7:C26)</f>
+        <v>8.4250000000000007</v>
+      </c>
       <c r="E27" s="52"/>
       <c r="F27" s="5" t="s">
         <v>2</v>
       </c>
       <c r="G27">
         <f>SUM(G7:G26)</f>
-        <v>0</v>
+        <v>31.905000000000005</v>
       </c>
       <c r="H27">
         <f>SUM(H7:H26)</f>
-        <v>0</v>
+        <v>84.941800000000001</v>
       </c>
       <c r="J27" s="92">
         <f>SUM(J7:J26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>-1.1546319456101628E-14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="B28" s="1" t="s">
         <v>28</v>
       </c>
@@ -20316,28 +21005,30 @@
       <c r="G28" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="89" t="e">
+      <c r="H28" s="89">
         <f>G27/H27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.3756101236375966</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="G29" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="90" t="e">
+      <c r="H29" s="90">
         <f>C27-H28*B27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5.5816313640633943</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="G30" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H30" s="127"/>
+      <c r="H30" s="127" t="s">
+        <v>1024</v>
+      </c>
       <c r="I30" s="128"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="73" t="s">
         <v>32</v>
       </c>
@@ -20345,7 +21036,7 @@
       <c r="C32" s="73"/>
       <c r="D32" s="73"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8">
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
@@ -20357,14 +21048,17 @@
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8">
       <c r="B34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C34" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="93"/>
+      <c r="E34" s="93">
+        <f>PEARSON(C7:C26,B7:B26)</f>
+        <v>0.63588303078241637</v>
+      </c>
       <c r="F34" s="2" t="s">
         <v>9</v>
       </c>
@@ -20372,14 +21066,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8">
       <c r="B35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
       </c>
-      <c r="E35" s="90"/>
+      <c r="E35" s="90">
+        <f>LINEST(C7:C26,B7:B26)</f>
+        <v>0.37561012363759649</v>
+      </c>
       <c r="F35" s="2" t="s">
         <v>318</v>
       </c>
@@ -20390,11 +21087,14 @@
         <v>276</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8">
       <c r="C36" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="89"/>
+      <c r="E36" s="89">
+        <f>INTERCEPT(C7:C26,B7:B26)</f>
+        <v>5.5816313640633943</v>
+      </c>
       <c r="F36" s="2" t="s">
         <v>10</v>
       </c>
@@ -20405,11 +21105,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" ht="17.5">
       <c r="C37" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="89"/>
+      <c r="E37" s="89">
+        <f>RSQ(C7:C26,B7:B26)</f>
+        <v>0.40434722883703161</v>
+      </c>
       <c r="F37" s="2" t="s">
         <v>11</v>
       </c>
@@ -20417,11 +21120,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" ht="17.5">
       <c r="C38" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="90"/>
+      <c r="E38" s="90">
+        <f>E34*E34</f>
+        <v>0.4043472288370315</v>
+      </c>
       <c r="F38" s="2" t="s">
         <v>12</v>
       </c>
@@ -20429,22 +21135,22 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8">
       <c r="B41" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="17.5">
       <c r="B51" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="B52" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54" s="73" t="s">
         <v>86</v>
       </c>
@@ -20454,7 +21160,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="B55" t="s">
         <v>277</v>
       </c>
@@ -20465,27 +21171,27 @@
       <c r="H55" s="67"/>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="B56" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="B57" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="B58" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33">
       <c r="P71" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33">
       <c r="P72" t="s">
         <v>104</v>
       </c>
@@ -20493,7 +21199,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33">
       <c r="P73" t="s">
         <v>201</v>
       </c>
@@ -20501,7 +21207,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33">
       <c r="P74" t="s">
         <v>202</v>
       </c>
@@ -20509,7 +21215,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33">
       <c r="A75" s="73" t="s">
         <v>88</v>
       </c>
@@ -20529,7 +21235,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33">
       <c r="B76" s="95" t="s">
         <v>471</v>
       </c>
@@ -20539,7 +21245,7 @@
       <c r="F76" s="95"/>
       <c r="G76" s="15"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33">
       <c r="B77" s="95" t="s">
         <v>474</v>
       </c>
@@ -20561,7 +21267,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33">
       <c r="A78" s="73" t="s">
         <v>89</v>
       </c>
@@ -20572,27 +21278,27 @@
         <v>491</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33">
       <c r="B79" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:33">
       <c r="B80" t="s">
         <v>475</v>
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:35">
       <c r="B81" t="s">
         <v>90</v>
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="83" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:35">
       <c r="H83" s="4"/>
     </row>
-    <row r="87" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:35">
       <c r="U87" s="22" t="s">
         <v>100</v>
       </c>
@@ -20600,16 +21306,16 @@
         <v>487</v>
       </c>
     </row>
-    <row r="88" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:35">
       <c r="V88" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="89" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:35" ht="15" customHeight="1"/>
+    <row r="90" spans="2:35">
       <c r="B90" s="8"/>
     </row>
-    <row r="91" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:35">
       <c r="AH91" s="22" t="s">
         <v>102</v>
       </c>
@@ -20617,7 +21323,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10">
       <c r="A98" s="72" t="s">
         <v>95</v>
       </c>
@@ -20628,44 +21334,44 @@
       <c r="F98" s="73"/>
       <c r="G98" s="73"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10">
       <c r="B99" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10">
       <c r="B100" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10">
       <c r="B101" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10">
       <c r="B102" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10">
       <c r="B104" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" ht="16" thickBot="1"/>
+    <row r="106" spans="1:10">
       <c r="B106" s="16" t="s">
         <v>36</v>
       </c>
       <c r="C106" s="16"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10">
       <c r="B107" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10">
       <c r="A108" s="65">
         <f>C108</f>
         <v>0</v>
@@ -20675,7 +21381,7 @@
       </c>
       <c r="J108" s="75"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10">
       <c r="A109" s="76">
         <f>C109</f>
         <v>0</v>
@@ -20684,23 +21390,23 @@
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10">
       <c r="B110" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="16" thickBot="1">
       <c r="B111" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C111" s="17"/>
     </row>
-    <row r="113" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="16" thickBot="1">
       <c r="B113" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12">
       <c r="B114" s="18"/>
       <c r="C114" s="18" t="s">
         <v>43</v>
@@ -20721,7 +21427,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12">
       <c r="B115" t="s">
         <v>8</v>
       </c>
@@ -20730,7 +21436,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12">
       <c r="B116" t="s">
         <v>48</v>
       </c>
@@ -20739,7 +21445,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="16" thickBot="1">
       <c r="B117" s="17" t="s">
         <v>49</v>
       </c>
@@ -20749,8 +21455,8 @@
       <c r="F117" s="17"/>
       <c r="G117" s="17"/>
     </row>
-    <row r="118" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="16" thickBot="1"/>
+    <row r="119" spans="1:12">
       <c r="B119" s="18"/>
       <c r="C119" s="18" t="s">
         <v>50</v>
@@ -20777,7 +21483,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12">
       <c r="B120" t="s">
         <v>57</v>
       </c>
@@ -20785,7 +21491,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="16" thickBot="1">
       <c r="A121" s="19" t="s">
         <v>93</v>
       </c>
@@ -20801,7 +21507,7 @@
       <c r="I121" s="17"/>
       <c r="J121" s="17"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12">
       <c r="A124" s="72" t="s">
         <v>94</v>
       </c>
@@ -20814,44 +21520,44 @@
       <c r="H124" s="73"/>
       <c r="I124" s="73"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12">
       <c r="B125" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12">
       <c r="B126" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12">
       <c r="B127" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12">
       <c r="B128" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10">
       <c r="B130" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" ht="16" thickBot="1"/>
+    <row r="132" spans="1:10">
       <c r="B132" s="16" t="s">
         <v>36</v>
       </c>
       <c r="C132" s="16"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10">
       <c r="B133" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10">
       <c r="A134" s="65">
         <f>C134</f>
         <v>0</v>
@@ -20860,7 +21566,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10">
       <c r="A135" s="76">
         <f>C135</f>
         <v>0</v>
@@ -20869,7 +21575,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10">
       <c r="B136" t="s">
         <v>40</v>
       </c>
@@ -20877,18 +21583,18 @@
         <v>288</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="16" thickBot="1">
       <c r="B137" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C137" s="17"/>
     </row>
-    <row r="139" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="16" thickBot="1">
       <c r="B139" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10">
       <c r="B140" s="18"/>
       <c r="C140" s="18" t="s">
         <v>43</v>
@@ -20906,17 +21612,17 @@
         <v>47</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10">
       <c r="B141" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10">
       <c r="B142" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="16" thickBot="1">
       <c r="B143" s="17" t="s">
         <v>49</v>
       </c>
@@ -20926,8 +21632,8 @@
       <c r="F143" s="17"/>
       <c r="G143" s="17"/>
     </row>
-    <row r="144" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" ht="16" thickBot="1"/>
+    <row r="145" spans="1:10">
       <c r="B145" s="18"/>
       <c r="C145" s="18" t="s">
         <v>50</v>
@@ -20954,12 +21660,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10">
       <c r="B146" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10">
       <c r="A147" s="54" t="s">
         <v>204</v>
       </c>
@@ -20967,7 +21673,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10">
       <c r="A148" s="54" t="s">
         <v>228</v>
       </c>
@@ -20975,7 +21681,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="16" thickBot="1">
       <c r="A149" s="54" t="s">
         <v>229</v>
       </c>
@@ -20991,7 +21697,7 @@
       <c r="I149" s="17"/>
       <c r="J149" s="17"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10">
       <c r="A152" s="72" t="s">
         <v>293</v>
       </c>
@@ -21002,49 +21708,49 @@
       <c r="F152" s="73"/>
       <c r="G152" s="73"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10">
       <c r="B153" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10">
       <c r="B154" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10">
       <c r="B155" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10">
       <c r="B156" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10">
       <c r="B157" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10">
       <c r="B159" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" ht="16" thickBot="1"/>
+    <row r="161" spans="1:12">
       <c r="B161" s="16" t="s">
         <v>36</v>
       </c>
       <c r="C161" s="16"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12">
       <c r="B162" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12">
       <c r="A163" s="65">
         <f>C163</f>
         <v>0</v>
@@ -21053,7 +21759,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12">
       <c r="A164" s="76">
         <f>C164</f>
         <v>0</v>
@@ -21062,23 +21768,23 @@
         <v>39</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12">
       <c r="B165" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="16" thickBot="1">
       <c r="B166" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C166" s="17"/>
     </row>
-    <row r="168" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" ht="16" thickBot="1">
       <c r="B168" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12">
       <c r="B169" s="18"/>
       <c r="C169" s="18" t="s">
         <v>43</v>
@@ -21099,7 +21805,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12">
       <c r="B170" t="s">
         <v>8</v>
       </c>
@@ -21111,7 +21817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12">
       <c r="B171" t="s">
         <v>48</v>
       </c>
@@ -21123,7 +21829,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" ht="16" thickBot="1">
       <c r="B172" s="17" t="s">
         <v>49</v>
       </c>
@@ -21133,8 +21839,8 @@
       <c r="F172" s="17"/>
       <c r="G172" s="17"/>
     </row>
-    <row r="173" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="16" thickBot="1"/>
+    <row r="174" spans="1:12">
       <c r="B174" s="18"/>
       <c r="C174" s="18" t="s">
         <v>50</v>
@@ -21161,12 +21867,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12">
       <c r="B175" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" ht="16" thickBot="1">
       <c r="A176" s="54" t="s">
         <v>228</v>
       </c>
@@ -21182,7 +21888,7 @@
       <c r="I176" s="17"/>
       <c r="J176" s="17"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10">
       <c r="A179" s="72" t="s">
         <v>96</v>
       </c>
@@ -21195,7 +21901,7 @@
       <c r="H179" s="73"/>
       <c r="I179" s="73"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10">
       <c r="A180" t="s">
         <v>218</v>
       </c>
@@ -21206,22 +21912,22 @@
       <c r="I180" s="73"/>
       <c r="J180" s="73"/>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:34">
       <c r="A198" s="104" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:34">
       <c r="A199" s="105" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:34">
       <c r="A200" s="104" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="201" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:34" s="85" customFormat="1">
       <c r="A201"/>
       <c r="B201"/>
       <c r="C201"/>
@@ -21248,7 +21954,7 @@
       <c r="AG201"/>
       <c r="AH201"/>
     </row>
-    <row r="202" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:34" s="85" customFormat="1">
       <c r="A202"/>
       <c r="B202"/>
       <c r="C202"/>
@@ -21260,7 +21966,7 @@
       <c r="I202"/>
       <c r="J202"/>
     </row>
-    <row r="203" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:34" s="85" customFormat="1">
       <c r="A203"/>
       <c r="B203"/>
       <c r="C203"/>
@@ -21272,7 +21978,7 @@
       <c r="I203"/>
       <c r="J203"/>
     </row>
-    <row r="204" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:34" s="85" customFormat="1">
       <c r="A204"/>
       <c r="B204"/>
       <c r="C204"/>
@@ -21284,7 +21990,7 @@
       <c r="I204"/>
       <c r="J204"/>
     </row>
-    <row r="205" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:34" s="85" customFormat="1">
       <c r="A205"/>
       <c r="B205"/>
       <c r="C205"/>
@@ -21296,7 +22002,7 @@
       <c r="I205"/>
       <c r="J205"/>
     </row>
-    <row r="206" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:34" s="85" customFormat="1">
       <c r="A206"/>
       <c r="B206"/>
       <c r="C206"/>
@@ -21308,7 +22014,7 @@
       <c r="I206"/>
       <c r="J206"/>
     </row>
-    <row r="207" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:34" s="85" customFormat="1">
       <c r="A207"/>
       <c r="B207"/>
       <c r="C207"/>
@@ -21320,7 +22026,7 @@
       <c r="I207"/>
       <c r="J207"/>
     </row>
-    <row r="208" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:34" s="85" customFormat="1">
       <c r="A208"/>
       <c r="B208"/>
       <c r="C208"/>
@@ -21332,7 +22038,7 @@
       <c r="I208"/>
       <c r="J208"/>
     </row>
-    <row r="209" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:34" s="85" customFormat="1">
       <c r="A209"/>
       <c r="B209"/>
       <c r="C209"/>
@@ -21344,7 +22050,7 @@
       <c r="I209"/>
       <c r="J209"/>
     </row>
-    <row r="210" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:34" s="85" customFormat="1">
       <c r="A210"/>
       <c r="B210"/>
       <c r="C210"/>
@@ -21356,7 +22062,7 @@
       <c r="I210"/>
       <c r="J210"/>
     </row>
-    <row r="211" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:34" s="85" customFormat="1">
       <c r="A211"/>
       <c r="B211"/>
       <c r="C211"/>
@@ -21368,7 +22074,7 @@
       <c r="I211"/>
       <c r="J211"/>
     </row>
-    <row r="212" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:34" s="85" customFormat="1">
       <c r="A212"/>
       <c r="B212"/>
       <c r="C212"/>
@@ -21380,7 +22086,7 @@
       <c r="I212"/>
       <c r="J212"/>
     </row>
-    <row r="213" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:34" s="85" customFormat="1">
       <c r="A213"/>
       <c r="B213"/>
       <c r="C213"/>
@@ -21392,7 +22098,7 @@
       <c r="I213"/>
       <c r="J213"/>
     </row>
-    <row r="214" spans="1:34" s="85" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:34" s="85" customFormat="1">
       <c r="A214"/>
       <c r="B214"/>
       <c r="C214"/>
@@ -21404,7 +22110,7 @@
       <c r="I214"/>
       <c r="J214"/>
     </row>
-    <row r="215" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:34">
       <c r="T215" s="85"/>
       <c r="U215" s="85"/>
       <c r="V215" s="85"/>
@@ -21531,12 +22237,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5AA788E-F8A0-E540-9053-6299A31FAAED}">
   <dimension ref="A1:W164"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="45.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>329</v>
       </c>
@@ -21544,7 +22250,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="85" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="77.5">
       <c r="A2" s="12"/>
       <c r="B2" s="13" t="s">
         <v>71</v>
@@ -21586,7 +22292,7 @@
       <c r="V2" s="68"/>
       <c r="W2" s="68"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23">
       <c r="A3" s="3" t="s">
         <v>330</v>
       </c>
@@ -21612,7 +22318,7 @@
       <c r="V3" s="68"/>
       <c r="W3" s="68"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23">
       <c r="A4" s="3" t="s">
         <v>331</v>
       </c>
@@ -21638,7 +22344,7 @@
       <c r="V4" s="68"/>
       <c r="W4" s="68"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23">
       <c r="A5" s="3" t="s">
         <v>332</v>
       </c>
@@ -21664,7 +22370,7 @@
       <c r="V5" s="68"/>
       <c r="W5" s="68"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23">
       <c r="A6" s="3" t="s">
         <v>333</v>
       </c>
@@ -21690,7 +22396,7 @@
       <c r="V6" s="68"/>
       <c r="W6" s="68"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23">
       <c r="A7" s="3" t="s">
         <v>334</v>
       </c>
@@ -21716,7 +22422,7 @@
       <c r="V7" s="68"/>
       <c r="W7" s="68"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23">
       <c r="A8" s="3" t="s">
         <v>335</v>
       </c>
@@ -21742,7 +22448,7 @@
       <c r="V8" s="68"/>
       <c r="W8" s="68"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23">
       <c r="A9" s="3" t="s">
         <v>336</v>
       </c>
@@ -21768,7 +22474,7 @@
       <c r="V9" s="68"/>
       <c r="W9" s="68"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23">
       <c r="A10" s="3" t="s">
         <v>337</v>
       </c>
@@ -21794,7 +22500,7 @@
       <c r="V10" s="68"/>
       <c r="W10" s="68"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23">
       <c r="A11" s="3" t="s">
         <v>338</v>
       </c>
@@ -21820,7 +22526,7 @@
       <c r="V11" s="68"/>
       <c r="W11" s="68"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23">
       <c r="A12" s="3" t="s">
         <v>339</v>
       </c>
@@ -21846,7 +22552,7 @@
       <c r="V12" s="68"/>
       <c r="W12" s="68"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23">
       <c r="A13" s="3" t="s">
         <v>340</v>
       </c>
@@ -21872,7 +22578,7 @@
       <c r="V13" s="68"/>
       <c r="W13" s="68"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23">
       <c r="A14" s="3" t="s">
         <v>341</v>
       </c>
@@ -21898,7 +22604,7 @@
       <c r="V14" s="68"/>
       <c r="W14" s="68"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23">
       <c r="A15" s="3" t="s">
         <v>342</v>
       </c>
@@ -21924,7 +22630,7 @@
       <c r="V15" s="68"/>
       <c r="W15" s="68"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23">
       <c r="A16" s="3" t="s">
         <v>68</v>
       </c>
@@ -21950,7 +22656,7 @@
       <c r="V16" s="68"/>
       <c r="W16" s="68"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23">
       <c r="A17" s="3" t="s">
         <v>69</v>
       </c>
@@ -21976,7 +22682,7 @@
       <c r="V17" s="68"/>
       <c r="W17" s="68"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23">
       <c r="A18" s="3" t="s">
         <v>212</v>
       </c>
@@ -22002,7 +22708,7 @@
       <c r="V18" s="68"/>
       <c r="W18" s="68"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23">
       <c r="A19" s="3" t="s">
         <v>343</v>
       </c>
@@ -22028,7 +22734,7 @@
       <c r="V19" s="68"/>
       <c r="W19" s="68"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23">
       <c r="A20" s="3" t="s">
         <v>344</v>
       </c>
@@ -22054,7 +22760,7 @@
       <c r="V20" s="68"/>
       <c r="W20" s="68"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23">
       <c r="A21" s="3" t="s">
         <v>345</v>
       </c>
@@ -22080,7 +22786,7 @@
       <c r="V21" s="68"/>
       <c r="W21" s="68"/>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23">
       <c r="A22" s="3" t="s">
         <v>346</v>
       </c>
@@ -22106,7 +22812,7 @@
       <c r="V22" s="68"/>
       <c r="W22" s="68"/>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23">
       <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
@@ -22132,7 +22838,7 @@
       <c r="V23" s="68"/>
       <c r="W23" s="68"/>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23">
       <c r="A24" s="3" t="s">
         <v>347</v>
       </c>
@@ -22158,7 +22864,7 @@
       <c r="V24" s="68"/>
       <c r="W24" s="68"/>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23">
       <c r="A25" s="3" t="s">
         <v>67</v>
       </c>
@@ -22184,7 +22890,7 @@
       <c r="V25" s="68"/>
       <c r="W25" s="68"/>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23">
       <c r="A26" s="3" t="s">
         <v>66</v>
       </c>
@@ -22210,7 +22916,7 @@
       <c r="V26" s="68"/>
       <c r="W26" s="68"/>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23">
       <c r="A27" s="3" t="s">
         <v>80</v>
       </c>
@@ -22236,7 +22942,7 @@
       <c r="V27" s="68"/>
       <c r="W27" s="68"/>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23">
       <c r="A28" s="3" t="s">
         <v>348</v>
       </c>
@@ -22262,7 +22968,7 @@
       <c r="V28" s="68"/>
       <c r="W28" s="68"/>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23">
       <c r="A29" s="3" t="s">
         <v>349</v>
       </c>
@@ -22288,7 +22994,7 @@
       <c r="V29" s="68"/>
       <c r="W29" s="68"/>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23">
       <c r="A30" s="3" t="s">
         <v>350</v>
       </c>
@@ -22314,7 +23020,7 @@
       <c r="V30" s="68"/>
       <c r="W30" s="68"/>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23">
       <c r="A31" s="3" t="s">
         <v>351</v>
       </c>
@@ -22340,7 +23046,7 @@
       <c r="V31" s="68"/>
       <c r="W31" s="68"/>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23">
       <c r="A32" s="3" t="s">
         <v>352</v>
       </c>
@@ -22366,7 +23072,7 @@
       <c r="V32" s="68"/>
       <c r="W32" s="68"/>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23">
       <c r="A33" s="3" t="s">
         <v>353</v>
       </c>
@@ -22392,7 +23098,7 @@
       <c r="V33" s="68"/>
       <c r="W33" s="68"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23">
       <c r="A34" s="3" t="s">
         <v>354</v>
       </c>
@@ -22418,7 +23124,7 @@
       <c r="V34" s="68"/>
       <c r="W34" s="68"/>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23">
       <c r="A35" s="3" t="s">
         <v>355</v>
       </c>
@@ -22444,7 +23150,7 @@
       <c r="V35" s="68"/>
       <c r="W35" s="68"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23">
       <c r="A36" s="3" t="s">
         <v>356</v>
       </c>
@@ -22470,7 +23176,7 @@
       <c r="V36" s="68"/>
       <c r="W36" s="68"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23">
       <c r="A37" s="3" t="s">
         <v>357</v>
       </c>
@@ -22496,7 +23202,7 @@
       <c r="V37" s="68"/>
       <c r="W37" s="68"/>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23">
       <c r="A38" s="3" t="s">
         <v>358</v>
       </c>
@@ -22522,7 +23228,7 @@
       <c r="V38" s="68"/>
       <c r="W38" s="68"/>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23">
       <c r="A39" s="3" t="s">
         <v>359</v>
       </c>
@@ -22548,7 +23254,7 @@
       <c r="V39" s="68"/>
       <c r="W39" s="68"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23">
       <c r="A40" s="3" t="s">
         <v>360</v>
       </c>
@@ -22574,7 +23280,7 @@
       <c r="V40" s="68"/>
       <c r="W40" s="68"/>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23">
       <c r="A41" s="3" t="s">
         <v>361</v>
       </c>
@@ -22600,7 +23306,7 @@
       <c r="V41" s="68"/>
       <c r="W41" s="68"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23">
       <c r="A42" s="3" t="s">
         <v>362</v>
       </c>
@@ -22626,7 +23332,7 @@
       <c r="V42" s="68"/>
       <c r="W42" s="68"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23">
       <c r="A43" s="3" t="s">
         <v>363</v>
       </c>
@@ -22652,7 +23358,7 @@
       <c r="V43" s="68"/>
       <c r="W43" s="68"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23">
       <c r="A44" s="3" t="s">
         <v>364</v>
       </c>
@@ -22678,7 +23384,7 @@
       <c r="V44" s="68"/>
       <c r="W44" s="68"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23">
       <c r="A45" s="3" t="s">
         <v>365</v>
       </c>
@@ -22704,7 +23410,7 @@
       <c r="V45" s="68"/>
       <c r="W45" s="68"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23">
       <c r="A46" s="3" t="s">
         <v>366</v>
       </c>
@@ -22730,7 +23436,7 @@
       <c r="V46" s="68"/>
       <c r="W46" s="68"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23">
       <c r="A47" s="3" t="s">
         <v>367</v>
       </c>
@@ -22756,7 +23462,7 @@
       <c r="V47" s="68"/>
       <c r="W47" s="68"/>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23">
       <c r="A48" s="3" t="s">
         <v>368</v>
       </c>
@@ -22782,7 +23488,7 @@
       <c r="V48" s="68"/>
       <c r="W48" s="68"/>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23">
       <c r="A49" s="3" t="s">
         <v>369</v>
       </c>
@@ -22808,7 +23514,7 @@
       <c r="V49" s="68"/>
       <c r="W49" s="68"/>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23">
       <c r="A50" s="3" t="s">
         <v>370</v>
       </c>
@@ -22834,7 +23540,7 @@
       <c r="V50" s="68"/>
       <c r="W50" s="68"/>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23">
       <c r="A51" s="3" t="s">
         <v>371</v>
       </c>
@@ -22860,7 +23566,7 @@
       <c r="V51" s="68"/>
       <c r="W51" s="68"/>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23">
       <c r="A52" s="3" t="s">
         <v>372</v>
       </c>
@@ -22886,7 +23592,7 @@
       <c r="V52" s="68"/>
       <c r="W52" s="68"/>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23">
       <c r="A53" s="3" t="s">
         <v>373</v>
       </c>
@@ -22912,7 +23618,7 @@
       <c r="V53" s="68"/>
       <c r="W53" s="68"/>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23">
       <c r="A54" s="3" t="s">
         <v>374</v>
       </c>
@@ -22938,7 +23644,7 @@
       <c r="V54" s="68"/>
       <c r="W54" s="68"/>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23">
       <c r="A55" s="3" t="s">
         <v>375</v>
       </c>
@@ -22964,7 +23670,7 @@
       <c r="V55" s="68"/>
       <c r="W55" s="68"/>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23">
       <c r="A56" s="3" t="s">
         <v>376</v>
       </c>
@@ -22990,7 +23696,7 @@
       <c r="V56" s="68"/>
       <c r="W56" s="68"/>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23">
       <c r="A57" s="3" t="s">
         <v>377</v>
       </c>
@@ -23016,7 +23722,7 @@
       <c r="V57" s="68"/>
       <c r="W57" s="68"/>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23">
       <c r="A58" s="3" t="s">
         <v>378</v>
       </c>
@@ -23042,7 +23748,7 @@
       <c r="V58" s="68"/>
       <c r="W58" s="68"/>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23">
       <c r="A59" s="3" t="s">
         <v>379</v>
       </c>
@@ -23068,7 +23774,7 @@
       <c r="V59" s="68"/>
       <c r="W59" s="68"/>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23">
       <c r="A60" s="3" t="s">
         <v>380</v>
       </c>
@@ -23094,7 +23800,7 @@
       <c r="V60" s="68"/>
       <c r="W60" s="68"/>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23">
       <c r="A61" s="3" t="s">
         <v>381</v>
       </c>
@@ -23120,7 +23826,7 @@
       <c r="V61" s="68"/>
       <c r="W61" s="68"/>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23">
       <c r="A62" s="3" t="s">
         <v>382</v>
       </c>
@@ -23146,7 +23852,7 @@
       <c r="V62" s="68"/>
       <c r="W62" s="68"/>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23">
       <c r="A63" s="3" t="s">
         <v>383</v>
       </c>
@@ -23172,7 +23878,7 @@
       <c r="V63" s="68"/>
       <c r="W63" s="68"/>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23">
       <c r="A64" s="3" t="s">
         <v>384</v>
       </c>
@@ -23198,7 +23904,7 @@
       <c r="V64" s="68"/>
       <c r="W64" s="68"/>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23">
       <c r="A65" s="3" t="s">
         <v>385</v>
       </c>
@@ -23224,7 +23930,7 @@
       <c r="V65" s="68"/>
       <c r="W65" s="68"/>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23">
       <c r="A66" s="3" t="s">
         <v>386</v>
       </c>
@@ -23250,7 +23956,7 @@
       <c r="V66" s="68"/>
       <c r="W66" s="68"/>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23">
       <c r="A67" s="3" t="s">
         <v>387</v>
       </c>
@@ -23276,7 +23982,7 @@
       <c r="V67" s="68"/>
       <c r="W67" s="68"/>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23">
       <c r="A68" s="3" t="s">
         <v>388</v>
       </c>
@@ -23302,7 +24008,7 @@
       <c r="V68" s="68"/>
       <c r="W68" s="68"/>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23">
       <c r="A69" s="3" t="s">
         <v>389</v>
       </c>
@@ -23328,7 +24034,7 @@
       <c r="V69" s="68"/>
       <c r="W69" s="68"/>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23">
       <c r="A70" s="3" t="s">
         <v>390</v>
       </c>
@@ -23354,7 +24060,7 @@
       <c r="V70" s="68"/>
       <c r="W70" s="68"/>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23">
       <c r="A71" s="3" t="s">
         <v>391</v>
       </c>
@@ -23380,7 +24086,7 @@
       <c r="V71" s="68"/>
       <c r="W71" s="68"/>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23">
       <c r="A72" s="3" t="s">
         <v>81</v>
       </c>
@@ -23406,7 +24112,7 @@
       <c r="V72" s="68"/>
       <c r="W72" s="68"/>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23">
       <c r="A73" s="3" t="s">
         <v>392</v>
       </c>
@@ -23432,7 +24138,7 @@
       <c r="V73" s="68"/>
       <c r="W73" s="68"/>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23">
       <c r="A74" s="3" t="s">
         <v>393</v>
       </c>
@@ -23458,7 +24164,7 @@
       <c r="V74" s="68"/>
       <c r="W74" s="68"/>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23">
       <c r="A75" s="3" t="s">
         <v>394</v>
       </c>
@@ -23484,7 +24190,7 @@
       <c r="V75" s="68"/>
       <c r="W75" s="68"/>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23">
       <c r="A76" s="3" t="s">
         <v>395</v>
       </c>
@@ -23510,7 +24216,7 @@
       <c r="V76" s="68"/>
       <c r="W76" s="68"/>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23">
       <c r="A77" s="3" t="s">
         <v>396</v>
       </c>
@@ -23536,7 +24242,7 @@
       <c r="V77" s="68"/>
       <c r="W77" s="68"/>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23">
       <c r="A78" s="3" t="s">
         <v>213</v>
       </c>
@@ -23562,7 +24268,7 @@
       <c r="V78" s="68"/>
       <c r="W78" s="68"/>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23">
       <c r="A79" s="3" t="s">
         <v>397</v>
       </c>
@@ -23588,7 +24294,7 @@
       <c r="V79" s="68"/>
       <c r="W79" s="68"/>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23">
       <c r="A80" s="3" t="s">
         <v>214</v>
       </c>
@@ -23614,7 +24320,7 @@
       <c r="V80" s="68"/>
       <c r="W80" s="68"/>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23">
       <c r="A81" s="3" t="s">
         <v>208</v>
       </c>
@@ -23640,417 +24346,417 @@
       <c r="V81" s="68"/>
       <c r="W81" s="68"/>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23">
       <c r="A82" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23">
       <c r="A83" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23">
       <c r="A84" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23">
       <c r="A85" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23">
       <c r="A86" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23">
       <c r="A87" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23">
       <c r="A88" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23">
       <c r="A89" s="3" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23">
       <c r="A90" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23">
       <c r="A91" s="3" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23">
       <c r="A92" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:23">
       <c r="A93" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:23">
       <c r="A94" s="3" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:23">
       <c r="A95" s="3" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:23">
       <c r="A96" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1">
       <c r="A97" s="3" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1">
       <c r="A98" s="3" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1">
       <c r="A99" s="3" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1">
       <c r="A100" s="3" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1">
       <c r="A101" s="3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1">
       <c r="A102" s="3" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1">
       <c r="A103" s="3" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1">
       <c r="A104" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1">
       <c r="A105" s="3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1">
       <c r="A106" s="3" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1">
       <c r="A107" s="3" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1">
       <c r="A108" s="3" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1">
       <c r="A109" s="3" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1">
       <c r="A110" s="3" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1">
       <c r="A111" s="3" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1">
       <c r="A112" s="3" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1">
       <c r="A113" s="3" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1">
       <c r="A114" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1">
       <c r="A115" s="3" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1">
       <c r="A116" s="3" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1">
       <c r="A117" s="3" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1">
       <c r="A118" s="3" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1">
       <c r="A119" s="3" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1">
       <c r="A120" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1">
       <c r="A121" s="3" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1">
       <c r="A122" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1">
       <c r="A123" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1">
       <c r="A124" s="3" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1">
       <c r="A125" s="3" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1">
       <c r="A126" s="3" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1">
       <c r="A127" s="3" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1">
       <c r="A128" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1">
       <c r="A129" s="3" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1">
       <c r="A130" s="3" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:1">
       <c r="A131" s="3" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:1">
       <c r="A132" s="3" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:1">
       <c r="A133" s="3" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:1">
       <c r="A134" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:1">
       <c r="A135" s="3" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:1">
       <c r="A136" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:1">
       <c r="A137" s="3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:1">
       <c r="A138" s="3" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:1">
       <c r="A139" s="3" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:1">
       <c r="A140" s="3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:1">
       <c r="A141" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:1">
       <c r="A142" s="3" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:1">
       <c r="A143" s="3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:1">
       <c r="A144" s="3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:1">
       <c r="A145" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:1">
       <c r="A146" s="3" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:1">
       <c r="A147" s="3" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:1">
       <c r="A148" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:1">
       <c r="A149" s="3" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:1">
       <c r="A150" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:1">
       <c r="A151" s="3" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:1">
       <c r="A152" s="3" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:1">
       <c r="A153" s="3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:1">
       <c r="A154" s="3" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:1">
       <c r="A155" s="3" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:1">
       <c r="A156" s="3" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:1">
       <c r="A157" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:1">
       <c r="A158" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:1">
       <c r="A159" s="3" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:1">
       <c r="A160" s="3" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:1">
       <c r="A161" s="3" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:1">
       <c r="A162" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:1">
       <c r="A163" s="3" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:1">
       <c r="A164" s="3" t="s">
         <v>469</v>
       </c>
@@ -24065,7 +24771,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B308196B-8B7C-2D4A-9DD9-F91E3317D371}">
   <dimension ref="A1:AD330"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.5" style="21"/>
     <col min="2" max="2" width="14.1640625" style="21" customWidth="1"/>
@@ -24075,7 +24781,7 @@
     <col min="22" max="16384" width="11.5" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="26">
       <c r="A1" s="39" t="s">
         <v>192</v>
       </c>
@@ -24109,7 +24815,7 @@
       <c r="AC1" s="36"/>
       <c r="AD1" s="36"/>
     </row>
-    <row r="2" spans="1:30" ht="26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="26">
       <c r="A2" s="38" t="str">
         <f>'Lab 9'!A2</f>
         <v>Due date: 19 October</v>
@@ -24147,44 +24853,44 @@
       <c r="AC2" s="36"/>
       <c r="AD2" s="36"/>
     </row>
-    <row r="4" spans="1:30" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="15.5">
       <c r="A4" s="35" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:30">
       <c r="A5" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:30">
       <c r="A6" s="21" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:30">
       <c r="A7" s="21" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:30">
       <c r="A8" s="21" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:30" ht="13">
       <c r="A9" s="21" t="s">
         <v>309</v>
       </c>
       <c r="B9" s="24"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:30" ht="13">
       <c r="A10" s="26" t="s">
         <v>311</v>
       </c>
       <c r="B10" s="24"/>
     </row>
-    <row r="14" spans="1:30" ht="56" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:30" ht="37.5">
       <c r="A14" s="34"/>
       <c r="B14" s="62" t="s">
         <v>189</v>
@@ -24211,7 +24917,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:30">
       <c r="A15" s="21" t="s">
         <v>199</v>
       </c>
@@ -24232,7 +24938,7 @@
       <c r="H15" s="82"/>
       <c r="I15" s="82"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:30">
       <c r="A16" s="21" t="s">
         <v>185</v>
       </c>
@@ -24253,7 +24959,7 @@
       <c r="H16" s="82"/>
       <c r="I16" s="82"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:20">
       <c r="A17" s="21" t="s">
         <v>184</v>
       </c>
@@ -24274,7 +24980,7 @@
       <c r="H17" s="82"/>
       <c r="I17" s="82"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:20">
       <c r="A18" s="21" t="s">
         <v>183</v>
       </c>
@@ -24307,7 +25013,7 @@
       <c r="S18" s="70"/>
       <c r="T18" s="70"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:20" ht="13">
       <c r="A19" s="21" t="s">
         <v>182</v>
       </c>
@@ -24337,7 +25043,7 @@
       <c r="P19" s="70"/>
       <c r="Q19" s="70"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:20">
       <c r="A20" s="21" t="s">
         <v>181</v>
       </c>
@@ -24370,7 +25076,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="15.5">
       <c r="A21" s="21" t="s">
         <v>180</v>
       </c>
@@ -24412,7 +25118,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:20">
       <c r="A22" s="21" t="s">
         <v>177</v>
       </c>
@@ -24445,7 +25151,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:20">
       <c r="A23" s="21" t="s">
         <v>176</v>
       </c>
@@ -24478,7 +25184,7 @@
         <v>18.649999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:20">
       <c r="A24" s="21" t="s">
         <v>175</v>
       </c>
@@ -24511,7 +25217,7 @@
         <v>35.06</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:20">
       <c r="A25" s="21" t="s">
         <v>173</v>
       </c>
@@ -24544,7 +25250,7 @@
         <v>37.43</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:20">
       <c r="A26" s="21" t="s">
         <v>172</v>
       </c>
@@ -24577,7 +25283,7 @@
         <v>43.72</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:20">
       <c r="A27" s="21" t="s">
         <v>171</v>
       </c>
@@ -24610,7 +25316,7 @@
         <v>61.17</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:20">
       <c r="A28" s="21" t="s">
         <v>170</v>
       </c>
@@ -24643,7 +25349,7 @@
         <v>51.19</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:20">
       <c r="A29" s="21" t="s">
         <v>168</v>
       </c>
@@ -24676,7 +25382,7 @@
         <v>50.76</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:20">
       <c r="A30" s="21" t="s">
         <v>167</v>
       </c>
@@ -24709,7 +25415,7 @@
         <v>54.058999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:20">
       <c r="A31" s="21" t="s">
         <v>166</v>
       </c>
@@ -24742,7 +25448,7 @@
         <v>44.569000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:20">
       <c r="A32" s="21" t="s">
         <v>165</v>
       </c>
@@ -24775,7 +25481,7 @@
         <v>40.92</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:29">
       <c r="A33" s="21" t="s">
         <v>163</v>
       </c>
@@ -24808,7 +25514,7 @@
         <v>58.551000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:29">
       <c r="A34" s="21" t="s">
         <v>161</v>
       </c>
@@ -24841,7 +25547,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:29">
       <c r="A35" s="21" t="s">
         <v>160</v>
       </c>
@@ -24874,7 +25580,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:29">
       <c r="A36" s="21" t="s">
         <v>159</v>
       </c>
@@ -24907,7 +25613,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:29">
       <c r="A37" s="21" t="s">
         <v>158</v>
       </c>
@@ -24940,7 +25646,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:29">
       <c r="A38" s="21" t="s">
         <v>156</v>
       </c>
@@ -24964,7 +25670,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" ht="15.5">
       <c r="A39" s="21" t="s">
         <v>155</v>
       </c>
@@ -25000,7 +25706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:29">
       <c r="A40" s="21" t="s">
         <v>154</v>
       </c>
@@ -25021,7 +25727,7 @@
       <c r="H40" s="30"/>
       <c r="I40" s="58"/>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:29" ht="13">
       <c r="A41" s="21" t="s">
         <v>153</v>
       </c>
@@ -25052,7 +25758,7 @@
       <c r="U41" s="70"/>
       <c r="V41" s="70"/>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:29" ht="13">
       <c r="A42" s="21" t="s">
         <v>151</v>
       </c>
@@ -25075,7 +25781,7 @@
       <c r="K42" s="24"/>
       <c r="U42" s="24"/>
     </row>
-    <row r="43" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" ht="15.5">
       <c r="A43" s="21" t="s">
         <v>150</v>
       </c>
@@ -25118,7 +25824,7 @@
       <c r="AB43"/>
       <c r="AC43"/>
     </row>
-    <row r="44" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="16" thickBot="1">
       <c r="A44" s="21" t="s">
         <v>149</v>
       </c>
@@ -25157,7 +25863,7 @@
       <c r="AB44"/>
       <c r="AC44"/>
     </row>
-    <row r="45" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" ht="15.5">
       <c r="A45" s="21" t="s">
         <v>148</v>
       </c>
@@ -25200,7 +25906,7 @@
       <c r="AB45"/>
       <c r="AC45"/>
     </row>
-    <row r="46" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" ht="15.5">
       <c r="A46" s="21" t="s">
         <v>146</v>
       </c>
@@ -25243,7 +25949,7 @@
       <c r="AB46"/>
       <c r="AC46"/>
     </row>
-    <row r="47" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" ht="15.5">
       <c r="A47" s="21" t="s">
         <v>145</v>
       </c>
@@ -25286,7 +25992,7 @@
       <c r="AB47"/>
       <c r="AC47"/>
     </row>
-    <row r="48" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" ht="15.5">
       <c r="A48" s="21" t="s">
         <v>144</v>
       </c>
@@ -25329,7 +26035,7 @@
       <c r="AB48"/>
       <c r="AC48"/>
     </row>
-    <row r="49" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:29" ht="15.5">
       <c r="A49" s="21" t="s">
         <v>142</v>
       </c>
@@ -25372,7 +26078,7 @@
       <c r="AB49"/>
       <c r="AC49"/>
     </row>
-    <row r="50" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="16" thickBot="1">
       <c r="A50" s="21" t="s">
         <v>140</v>
       </c>
@@ -25415,7 +26121,7 @@
       <c r="AB50"/>
       <c r="AC50"/>
     </row>
-    <row r="51" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" ht="15.5">
       <c r="A51" s="21" t="s">
         <v>139</v>
       </c>
@@ -25454,7 +26160,7 @@
       <c r="AB51"/>
       <c r="AC51"/>
     </row>
-    <row r="52" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="16" thickBot="1">
       <c r="A52" s="21" t="s">
         <v>137</v>
       </c>
@@ -25497,7 +26203,7 @@
       <c r="AB52"/>
       <c r="AC52"/>
     </row>
-    <row r="53" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" ht="15.5">
       <c r="A53" s="21" t="s">
         <v>136</v>
       </c>
@@ -25536,7 +26242,7 @@
       <c r="AB53"/>
       <c r="AC53"/>
     </row>
-    <row r="54" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:29" ht="15.5">
       <c r="A54" s="21" t="s">
         <v>134</v>
       </c>
@@ -25579,7 +26285,7 @@
       <c r="AB54"/>
       <c r="AC54"/>
     </row>
-    <row r="55" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" ht="15.5">
       <c r="A55" s="21" t="s">
         <v>133</v>
       </c>
@@ -25622,7 +26328,7 @@
       <c r="AB55"/>
       <c r="AC55"/>
     </row>
-    <row r="56" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="16" thickBot="1">
       <c r="A56" s="21" t="s">
         <v>132</v>
       </c>
@@ -25665,7 +26371,7 @@
       <c r="AB56"/>
       <c r="AC56"/>
     </row>
-    <row r="57" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="16" thickBot="1">
       <c r="A57" s="21" t="s">
         <v>130</v>
       </c>
@@ -25704,7 +26410,7 @@
       <c r="AB57"/>
       <c r="AC57"/>
     </row>
-    <row r="58" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" ht="15.5">
       <c r="A58" s="21" t="s">
         <v>127</v>
       </c>
@@ -25743,7 +26449,7 @@
       <c r="AB58" s="18"/>
       <c r="AC58" s="18"/>
     </row>
-    <row r="59" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" ht="15.5">
       <c r="A59" s="21" t="s">
         <v>126</v>
       </c>
@@ -25786,7 +26492,7 @@
       <c r="AB59"/>
       <c r="AC59"/>
     </row>
-    <row r="60" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="16" thickBot="1">
       <c r="A60" s="21" t="s">
         <v>124</v>
       </c>
@@ -25829,7 +26535,7 @@
       <c r="AB60" s="17"/>
       <c r="AC60" s="17"/>
     </row>
-    <row r="61" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:29" ht="15.5">
       <c r="A61" s="21" t="s">
         <v>122</v>
       </c>
@@ -25868,7 +26574,7 @@
       <c r="AB61"/>
       <c r="AC61"/>
     </row>
-    <row r="62" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:29" ht="15.5">
       <c r="A62" s="21" t="s">
         <v>121</v>
       </c>
@@ -25907,7 +26613,7 @@
       <c r="AB62"/>
       <c r="AC62"/>
     </row>
-    <row r="63" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:29" ht="15.5">
       <c r="A63" s="21" t="s">
         <v>120</v>
       </c>
@@ -25946,7 +26652,7 @@
       <c r="AB63"/>
       <c r="AC63"/>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:29" ht="13">
       <c r="A64" s="21" t="s">
         <v>119</v>
       </c>
@@ -25981,7 +26687,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:24" ht="13">
       <c r="A65" s="21" t="s">
         <v>117</v>
       </c>
@@ -26008,7 +26714,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:24">
       <c r="A66" s="21" t="s">
         <v>196</v>
       </c>
@@ -26053,7 +26759,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:24">
       <c r="A67" s="21" t="s">
         <v>197</v>
       </c>
@@ -26106,7 +26812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:24">
       <c r="A68" s="21" t="s">
         <v>198</v>
       </c>
@@ -26127,7 +26833,7 @@
       <c r="H68" s="30"/>
       <c r="I68" s="58"/>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:24">
       <c r="A69" s="21" t="s">
         <v>227</v>
       </c>
@@ -26148,7 +26854,7 @@
       <c r="H69" s="30"/>
       <c r="I69" s="58"/>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:24">
       <c r="A70" s="21" t="s">
         <v>221</v>
       </c>
@@ -26169,7 +26875,7 @@
       <c r="H70" s="30"/>
       <c r="I70" s="58"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:24">
       <c r="A71" s="21" t="s">
         <v>222</v>
       </c>
@@ -26190,7 +26896,7 @@
       <c r="H71" s="30"/>
       <c r="I71" s="58"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:24">
       <c r="A72" s="21" t="s">
         <v>223</v>
       </c>
@@ -26211,7 +26917,7 @@
       <c r="H72" s="30"/>
       <c r="I72" s="58"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:24">
       <c r="A73" s="21" t="s">
         <v>226</v>
       </c>
@@ -26232,7 +26938,7 @@
       <c r="H73" s="30"/>
       <c r="I73" s="58"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:24">
       <c r="A74" s="21" t="s">
         <v>224</v>
       </c>
@@ -26253,7 +26959,7 @@
       <c r="H74" s="30"/>
       <c r="I74" s="58"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:24">
       <c r="A75" s="21" t="s">
         <v>225</v>
       </c>
@@ -26274,7 +26980,7 @@
       <c r="H75" s="30"/>
       <c r="I75" s="58"/>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:24">
       <c r="A76" s="21" t="s">
         <v>241</v>
       </c>
@@ -26295,7 +27001,7 @@
       <c r="H76" s="30"/>
       <c r="I76" s="58"/>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:24">
       <c r="A77" s="21" t="s">
         <v>238</v>
       </c>
@@ -26316,7 +27022,7 @@
       <c r="H77" s="30"/>
       <c r="I77" s="58"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:24">
       <c r="A78" s="21" t="s">
         <v>239</v>
       </c>
@@ -26337,7 +27043,7 @@
       <c r="H78" s="30"/>
       <c r="I78" s="58"/>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:24">
       <c r="A79" s="21" t="s">
         <v>240</v>
       </c>
@@ -26358,7 +27064,7 @@
       <c r="H79" s="30"/>
       <c r="I79" s="58"/>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:24">
       <c r="A80" s="21" t="s">
         <v>250</v>
       </c>
@@ -26379,7 +27085,7 @@
       <c r="H80" s="30"/>
       <c r="I80" s="58"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" ht="13">
       <c r="A81" s="21" t="s">
         <v>251</v>
       </c>
@@ -26400,7 +27106,7 @@
       <c r="H81" s="30"/>
       <c r="I81" s="58"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" ht="13">
       <c r="A82" s="21" t="s">
         <v>252</v>
       </c>
@@ -26421,7 +27127,7 @@
       <c r="H82" s="30"/>
       <c r="I82" s="58"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9">
       <c r="A83" s="21" t="s">
         <v>253</v>
       </c>
@@ -26442,7 +27148,7 @@
       <c r="H83" s="30"/>
       <c r="I83" s="58"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" ht="13">
       <c r="A84" s="21" t="s">
         <v>261</v>
       </c>
@@ -26463,7 +27169,7 @@
       <c r="H84" s="30"/>
       <c r="I84" s="58"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" ht="13">
       <c r="A85" s="21" t="s">
         <v>262</v>
       </c>
@@ -26484,7 +27190,7 @@
       <c r="H85" s="30"/>
       <c r="I85" s="58"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" ht="13">
       <c r="A86" s="21" t="s">
         <v>295</v>
       </c>
@@ -26505,7 +27211,7 @@
       <c r="H86" s="30"/>
       <c r="I86" s="58"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" ht="13">
       <c r="A87" s="21" t="s">
         <v>296</v>
       </c>
@@ -26526,7 +27232,7 @@
       <c r="H87" s="30"/>
       <c r="I87" s="58"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" ht="13">
       <c r="A88" s="21" t="s">
         <v>297</v>
       </c>
@@ -26547,7 +27253,7 @@
       <c r="H88" s="30"/>
       <c r="I88" s="58"/>
     </row>
-    <row r="89" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="15.5">
       <c r="A89" s="21" t="s">
         <v>298</v>
       </c>
@@ -26569,7 +27275,7 @@
       <c r="H89" s="99"/>
       <c r="I89" s="64"/>
     </row>
-    <row r="90" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="15.5">
       <c r="A90" s="21" t="s">
         <v>299</v>
       </c>
@@ -26595,10 +27301,10 @@
       <c r="H90" s="30"/>
       <c r="I90" s="78"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9">
       <c r="C91" s="28"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9">
       <c r="A93" s="27" t="s">
         <v>114</v>
       </c>
@@ -26606,54 +27312,54 @@
         <v>113</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9">
       <c r="A94" s="26"/>
       <c r="B94" s="26" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9">
       <c r="A95" s="26"/>
       <c r="B95" s="26" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9">
       <c r="B96" s="26"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:10">
       <c r="B97" s="26"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:10">
       <c r="A99" s="70" t="s">
         <v>303</v>
       </c>
       <c r="B99" s="70"/>
       <c r="C99" s="70"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:10" ht="13">
       <c r="B100" s="21" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:10" ht="13">
       <c r="B101" s="21" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:10">
       <c r="B102" s="21" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:10" ht="13">
       <c r="A103" s="71" t="s">
         <v>112</v>
       </c>
       <c r="B103" s="70"/>
       <c r="C103" s="70"/>
     </row>
-    <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" ht="15.5">
       <c r="B105" t="s">
         <v>35</v>
       </c>
@@ -26664,7 +27370,7 @@
       <c r="I105"/>
       <c r="J105"/>
     </row>
-    <row r="106" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="16" thickBot="1">
       <c r="B106"/>
       <c r="C106"/>
       <c r="D106"/>
@@ -26675,7 +27381,7 @@
       <c r="I106"/>
       <c r="J106"/>
     </row>
-    <row r="107" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" ht="15.5">
       <c r="B107" s="16" t="s">
         <v>36</v>
       </c>
@@ -26688,7 +27394,7 @@
       <c r="I107"/>
       <c r="J107"/>
     </row>
-    <row r="108" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="15.5">
       <c r="B108" t="s">
         <v>37</v>
       </c>
@@ -26701,7 +27407,7 @@
       <c r="I108"/>
       <c r="J108"/>
     </row>
-    <row r="109" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="15.5">
       <c r="A109" s="78">
         <f>C109</f>
         <v>0</v>
@@ -26718,7 +27424,7 @@
       <c r="I109"/>
       <c r="J109"/>
     </row>
-    <row r="110" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="15.5">
       <c r="A110" s="64">
         <f>C110</f>
         <v>0</v>
@@ -26735,7 +27441,7 @@
       <c r="I110"/>
       <c r="J110"/>
     </row>
-    <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="15.5">
       <c r="B111" t="s">
         <v>40</v>
       </c>
@@ -26748,7 +27454,7 @@
       <c r="I111"/>
       <c r="J111"/>
     </row>
-    <row r="112" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="16" thickBot="1">
       <c r="B112" s="17" t="s">
         <v>41</v>
       </c>
@@ -26761,7 +27467,7 @@
       <c r="I112"/>
       <c r="J112"/>
     </row>
-    <row r="113" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:10" ht="15.5">
       <c r="B113"/>
       <c r="C113"/>
       <c r="D113"/>
@@ -26772,7 +27478,7 @@
       <c r="I113"/>
       <c r="J113"/>
     </row>
-    <row r="114" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:10" ht="16" thickBot="1">
       <c r="B114" t="s">
         <v>42</v>
       </c>
@@ -26785,7 +27491,7 @@
       <c r="I114"/>
       <c r="J114"/>
     </row>
-    <row r="115" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:10" ht="15.5">
       <c r="B115" s="18"/>
       <c r="C115" s="18"/>
       <c r="D115" s="18"/>
@@ -26796,7 +27502,7 @@
       <c r="I115"/>
       <c r="J115"/>
     </row>
-    <row r="116" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:10" ht="15.5">
       <c r="B116" t="s">
         <v>8</v>
       </c>
@@ -26809,7 +27515,7 @@
       <c r="I116"/>
       <c r="J116"/>
     </row>
-    <row r="117" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:10" ht="15.5">
       <c r="B117" t="s">
         <v>48</v>
       </c>
@@ -26822,7 +27528,7 @@
       <c r="I117"/>
       <c r="J117"/>
     </row>
-    <row r="118" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:10" ht="16" thickBot="1">
       <c r="B118" s="17" t="s">
         <v>49</v>
       </c>
@@ -26835,7 +27541,7 @@
       <c r="I118"/>
       <c r="J118"/>
     </row>
-    <row r="119" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:10" ht="16" thickBot="1">
       <c r="B119"/>
       <c r="C119"/>
       <c r="D119"/>
@@ -26846,7 +27552,7 @@
       <c r="I119"/>
       <c r="J119"/>
     </row>
-    <row r="120" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:10" ht="15.5">
       <c r="B120" s="18"/>
       <c r="C120" s="18"/>
       <c r="D120" s="18"/>
@@ -26857,7 +27563,7 @@
       <c r="I120" s="18"/>
       <c r="J120" s="18"/>
     </row>
-    <row r="121" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:10" ht="15.5">
       <c r="B121" t="s">
         <v>57</v>
       </c>
@@ -26870,7 +27576,7 @@
       <c r="I121"/>
       <c r="J121"/>
     </row>
-    <row r="122" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:10" ht="16" thickBot="1">
       <c r="B122" s="17" t="s">
         <v>58</v>
       </c>
@@ -26883,7 +27589,7 @@
       <c r="I122" s="17"/>
       <c r="J122" s="17"/>
     </row>
-    <row r="123" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:10" ht="15.5">
       <c r="B123"/>
       <c r="C123"/>
       <c r="D123"/>
@@ -26894,7 +27600,7 @@
       <c r="I123"/>
       <c r="J123"/>
     </row>
-    <row r="124" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:10" ht="15.5">
       <c r="B124"/>
       <c r="C124"/>
       <c r="D124"/>
@@ -26905,7 +27611,7 @@
       <c r="I124"/>
       <c r="J124"/>
     </row>
-    <row r="125" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:10" ht="15.5">
       <c r="B125"/>
       <c r="C125"/>
       <c r="D125"/>
@@ -26916,7 +27622,7 @@
       <c r="I125"/>
       <c r="J125"/>
     </row>
-    <row r="126" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:10" ht="15.5">
       <c r="B126" s="70" t="s">
         <v>111</v>
       </c>
@@ -26937,7 +27643,7 @@
       </c>
       <c r="J126"/>
     </row>
-    <row r="127" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:10" ht="15.5">
       <c r="E127" s="77">
         <f>F127+G127*H127</f>
         <v>0</v>
@@ -26956,17 +27662,17 @@
       </c>
       <c r="J127"/>
     </row>
-    <row r="128" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:10" ht="15.5">
       <c r="J128"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:10" ht="13">
       <c r="A130" s="71" t="s">
         <v>109</v>
       </c>
       <c r="B130" s="70"/>
       <c r="C130" s="70"/>
     </row>
-    <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" ht="15.5">
       <c r="B132" t="s">
         <v>35</v>
       </c>
@@ -26979,7 +27685,7 @@
       <c r="I132"/>
       <c r="J132"/>
     </row>
-    <row r="133" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="16" thickBot="1">
       <c r="B133"/>
       <c r="C133"/>
       <c r="D133"/>
@@ -26990,7 +27696,7 @@
       <c r="I133"/>
       <c r="J133"/>
     </row>
-    <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" ht="15.5">
       <c r="B134" s="16" t="s">
         <v>36</v>
       </c>
@@ -27003,7 +27709,7 @@
       <c r="I134"/>
       <c r="J134"/>
     </row>
-    <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" ht="15.5">
       <c r="B135" t="s">
         <v>37</v>
       </c>
@@ -27016,7 +27722,7 @@
       <c r="I135"/>
       <c r="J135"/>
     </row>
-    <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" ht="15.5">
       <c r="A136" s="64">
         <f>C136</f>
         <v>0</v>
@@ -27033,7 +27739,7 @@
       <c r="I136"/>
       <c r="J136"/>
     </row>
-    <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" ht="15.5">
       <c r="A137" s="78">
         <f>C137</f>
         <v>0</v>
@@ -27050,7 +27756,7 @@
       <c r="I137"/>
       <c r="J137"/>
     </row>
-    <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" ht="15.5">
       <c r="B138" t="s">
         <v>40</v>
       </c>
@@ -27063,7 +27769,7 @@
       <c r="I138"/>
       <c r="J138"/>
     </row>
-    <row r="139" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="16" thickBot="1">
       <c r="B139" s="17" t="s">
         <v>41</v>
       </c>
@@ -27076,7 +27782,7 @@
       <c r="I139"/>
       <c r="J139"/>
     </row>
-    <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" ht="15.5">
       <c r="B140"/>
       <c r="C140"/>
       <c r="D140"/>
@@ -27087,7 +27793,7 @@
       <c r="I140"/>
       <c r="J140"/>
     </row>
-    <row r="141" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="16" thickBot="1">
       <c r="B141" t="s">
         <v>42</v>
       </c>
@@ -27100,7 +27806,7 @@
       <c r="I141"/>
       <c r="J141"/>
     </row>
-    <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" ht="15.5">
       <c r="B142" s="18"/>
       <c r="C142" s="18"/>
       <c r="D142" s="18"/>
@@ -27111,7 +27817,7 @@
       <c r="I142"/>
       <c r="J142"/>
     </row>
-    <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" ht="15.5">
       <c r="B143" t="s">
         <v>8</v>
       </c>
@@ -27124,7 +27830,7 @@
       <c r="I143"/>
       <c r="J143"/>
     </row>
-    <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" ht="15.5">
       <c r="B144" t="s">
         <v>48</v>
       </c>
@@ -27137,7 +27843,7 @@
       <c r="I144"/>
       <c r="J144"/>
     </row>
-    <row r="145" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="16" thickBot="1">
       <c r="B145" s="17" t="s">
         <v>49</v>
       </c>
@@ -27150,7 +27856,7 @@
       <c r="I145"/>
       <c r="J145"/>
     </row>
-    <row r="146" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="16" thickBot="1">
       <c r="B146"/>
       <c r="C146"/>
       <c r="D146"/>
@@ -27161,7 +27867,7 @@
       <c r="I146"/>
       <c r="J146"/>
     </row>
-    <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" ht="15.5">
       <c r="B147" s="18"/>
       <c r="C147" s="18"/>
       <c r="D147" s="18"/>
@@ -27172,7 +27878,7 @@
       <c r="I147" s="18"/>
       <c r="J147" s="18"/>
     </row>
-    <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" ht="15.5">
       <c r="B148" t="s">
         <v>57</v>
       </c>
@@ -27185,7 +27891,7 @@
       <c r="I148"/>
       <c r="J148"/>
     </row>
-    <row r="149" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="16" thickBot="1">
       <c r="B149" s="17" t="s">
         <v>58</v>
       </c>
@@ -27198,7 +27904,7 @@
       <c r="I149" s="17"/>
       <c r="J149" s="17"/>
     </row>
-    <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" ht="15.5">
       <c r="B150"/>
       <c r="C150"/>
       <c r="D150"/>
@@ -27209,7 +27915,7 @@
       <c r="I150"/>
       <c r="J150"/>
     </row>
-    <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" ht="15.5">
       <c r="B151"/>
       <c r="C151"/>
       <c r="D151"/>
@@ -27220,7 +27926,7 @@
       <c r="I151"/>
       <c r="J151"/>
     </row>
-    <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" ht="15.5">
       <c r="B152"/>
       <c r="C152"/>
       <c r="D152"/>
@@ -27231,7 +27937,7 @@
       <c r="I152"/>
       <c r="J152"/>
     </row>
-    <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" ht="15.5">
       <c r="B153" s="70" t="s">
         <v>108</v>
       </c>
@@ -27252,7 +27958,7 @@
       </c>
       <c r="J153"/>
     </row>
-    <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" ht="15.5">
       <c r="E154" s="77">
         <f>F154+G154*H154</f>
         <v>0</v>
@@ -27271,7 +27977,7 @@
       </c>
       <c r="J154"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:10">
       <c r="A157" s="70" t="s">
         <v>317</v>
       </c>
@@ -27285,7 +27991,7 @@
       <c r="I157" s="70"/>
       <c r="J157" s="70"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:10">
       <c r="A158" s="70" t="s">
         <v>255</v>
       </c>
@@ -27300,12 +28006,12 @@
         <v>257</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:10">
       <c r="D160" s="70" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:28" ht="13">
       <c r="A179" s="71" t="s">
         <v>493</v>
       </c>
@@ -27317,7 +28023,7 @@
       <c r="G179" s="70"/>
       <c r="H179" s="70"/>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:28" ht="13">
       <c r="A180" s="21" t="s">
         <v>320</v>
       </c>
@@ -27340,7 +28046,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:28" ht="13">
       <c r="A181" s="24" t="s">
         <v>101</v>
       </c>
@@ -27353,15 +28059,15 @@
         <v>484</v>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:28">
       <c r="A182" s="25" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:28" ht="13">
       <c r="K187" s="22"/>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:28" ht="13">
       <c r="K189" s="22" t="s">
         <v>100</v>
       </c>
@@ -27369,24 +28075,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="191" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:28" ht="25">
       <c r="I191" s="59"/>
     </row>
-    <row r="192" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:28" ht="25">
       <c r="I192" s="59"/>
       <c r="T192" s="23"/>
     </row>
-    <row r="193" spans="8:21" ht="25" x14ac:dyDescent="0.25">
+    <row r="193" spans="8:21" ht="25">
       <c r="H193" s="59"/>
       <c r="I193" s="59"/>
     </row>
-    <row r="194" spans="8:21" ht="25" x14ac:dyDescent="0.25">
+    <row r="194" spans="8:21" ht="25">
       <c r="I194" s="59"/>
     </row>
-    <row r="195" spans="8:21" ht="17" x14ac:dyDescent="0.2">
+    <row r="195" spans="8:21" ht="16.5">
       <c r="I195" s="60"/>
     </row>
-    <row r="196" spans="8:21" x14ac:dyDescent="0.15">
+    <row r="196" spans="8:21" ht="13">
       <c r="T196" s="22" t="s">
         <v>98</v>
       </c>
@@ -27394,12 +28100,12 @@
         <v>492</v>
       </c>
     </row>
-    <row r="197" spans="8:21" x14ac:dyDescent="0.15">
+    <row r="197" spans="8:21">
       <c r="U197" s="25" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="212" spans="20:22" x14ac:dyDescent="0.15">
+    <row r="212" spans="20:22">
       <c r="T212" s="102" t="s">
         <v>322</v>
       </c>
@@ -27407,22 +28113,22 @@
         <v>323</v>
       </c>
     </row>
-    <row r="213" spans="20:22" x14ac:dyDescent="0.15">
+    <row r="213" spans="20:22">
       <c r="V213" s="26" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="214" spans="20:22" x14ac:dyDescent="0.15">
+    <row r="214" spans="20:22">
       <c r="V214" s="26" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.15">
+    <row r="235" spans="8:8">
       <c r="H235" s="21" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:9" ht="13">
       <c r="A266" s="71" t="s">
         <v>1022</v>
       </c>
@@ -27435,7 +28141,7 @@
       <c r="H266" s="70"/>
       <c r="I266" s="70"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:6" ht="13">
       <c r="A288" s="71" t="s">
         <v>1018</v>
       </c>
@@ -27445,42 +28151,42 @@
       <c r="E288" s="70"/>
       <c r="F288" s="70"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:9">
       <c r="A289" s="21" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:9">
       <c r="A290" s="21" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:9">
       <c r="A291" s="21" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:9">
       <c r="A292" s="21" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:9">
       <c r="A293" s="61" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:9" ht="13">
       <c r="A294" s="24" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:9" ht="13">
       <c r="A295" s="24" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9" ht="15.5">
       <c r="D296" s="72" t="s">
         <v>1019</v>
       </c>
@@ -27490,35 +28196,35 @@
       <c r="H296" s="73"/>
       <c r="I296" s="73"/>
     </row>
-    <row r="324" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:3" ht="14.5">
       <c r="A324" s="104" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:3" ht="15.5">
       <c r="A325" s="105" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:3" ht="14.5">
       <c r="A326" s="104" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:3" ht="14.5">
       <c r="A327" s="106"/>
       <c r="B327" s="106"/>
       <c r="C327" s="106"/>
     </row>
-    <row r="328" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:3" ht="14.5">
       <c r="A328" s="106"/>
       <c r="B328" s="86"/>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:3">
       <c r="A329" s="85"/>
       <c r="B329" s="85"/>
     </row>
-    <row r="330" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:3" ht="14.5">
       <c r="A330" s="106"/>
       <c r="B330" s="86"/>
     </row>
@@ -27647,14 +28353,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F3FFB1-411A-D24C-A8B9-430EEF15FB6C}">
   <dimension ref="A1:O522"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="7" width="11.5" style="21"/>
     <col min="8" max="8" width="3.1640625" style="21" customWidth="1"/>
     <col min="9" max="16384" width="11.5" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="15.5">
       <c r="B1"/>
       <c r="C1" s="42" t="s">
         <v>381</v>
@@ -27671,7 +28377,7 @@
       <c r="L1" s="41"/>
       <c r="M1" s="40"/>
     </row>
-    <row r="2" spans="1:15" s="44" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" s="44" customFormat="1" ht="38">
       <c r="A2" s="47" t="s">
         <v>195</v>
       </c>
@@ -27707,7 +28413,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="15.5">
       <c r="A3" s="43" t="s">
         <v>72</v>
       </c>
@@ -27727,7 +28433,7 @@
       <c r="M3" s="114"/>
       <c r="O3" s="23"/>
     </row>
-    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="15.5">
       <c r="B4" s="118" t="s">
         <v>498</v>
       </c>
@@ -27744,7 +28450,7 @@
       <c r="M4" s="119"/>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="15.5">
       <c r="B5" s="118" t="s">
         <v>499</v>
       </c>
@@ -27761,7 +28467,7 @@
       <c r="M5" s="119"/>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="15.5">
       <c r="B6" s="118" t="s">
         <v>500</v>
       </c>
@@ -27778,7 +28484,7 @@
       <c r="M6" s="119"/>
       <c r="O6" s="23"/>
     </row>
-    <row r="7" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="15.5">
       <c r="B7" s="118" t="s">
         <v>501</v>
       </c>
@@ -27795,7 +28501,7 @@
       <c r="M7" s="119"/>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="15.5">
       <c r="B8" s="118" t="s">
         <v>502</v>
       </c>
@@ -27812,7 +28518,7 @@
       <c r="M8" s="119"/>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="15.5">
       <c r="B9" s="118" t="s">
         <v>503</v>
       </c>
@@ -27829,7 +28535,7 @@
       <c r="M9" s="119"/>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="15.5">
       <c r="B10" s="118" t="s">
         <v>504</v>
       </c>
@@ -27846,7 +28552,7 @@
       <c r="M10" s="121"/>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="15.5">
       <c r="B11" s="118" t="s">
         <v>505</v>
       </c>
@@ -27863,7 +28569,7 @@
       <c r="M11" s="121"/>
       <c r="O11" s="23"/>
     </row>
-    <row r="12" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="15.5">
       <c r="B12" s="118" t="s">
         <v>506</v>
       </c>
@@ -27880,7 +28586,7 @@
       <c r="M12" s="121"/>
       <c r="O12" s="23"/>
     </row>
-    <row r="13" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="15.5">
       <c r="B13" s="118" t="s">
         <v>507</v>
       </c>
@@ -27897,7 +28603,7 @@
       <c r="M13" s="121"/>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="15.5">
       <c r="B14" s="118" t="s">
         <v>508</v>
       </c>
@@ -27914,7 +28620,7 @@
       <c r="M14" s="121"/>
       <c r="O14" s="23"/>
     </row>
-    <row r="15" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="15.5">
       <c r="B15" s="118" t="s">
         <v>509</v>
       </c>
@@ -27931,7 +28637,7 @@
       <c r="M15" s="121"/>
       <c r="O15" s="23"/>
     </row>
-    <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="15.5">
       <c r="B16" s="118" t="s">
         <v>510</v>
       </c>
@@ -27948,7 +28654,7 @@
       <c r="M16" s="121"/>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" ht="15.5">
       <c r="B17" s="118" t="s">
         <v>511</v>
       </c>
@@ -27965,7 +28671,7 @@
       <c r="M17" s="121"/>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" ht="15.5">
       <c r="B18" s="118" t="s">
         <v>512</v>
       </c>
@@ -27982,7 +28688,7 @@
       <c r="M18" s="121"/>
       <c r="O18" s="23"/>
     </row>
-    <row r="19" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" ht="15.5">
       <c r="B19" s="118" t="s">
         <v>513</v>
       </c>
@@ -27999,7 +28705,7 @@
       <c r="M19" s="121"/>
       <c r="O19" s="23"/>
     </row>
-    <row r="20" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" ht="15.5">
       <c r="B20" s="118" t="s">
         <v>514</v>
       </c>
@@ -28016,7 +28722,7 @@
       <c r="M20" s="121"/>
       <c r="O20" s="23"/>
     </row>
-    <row r="21" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" ht="15.5">
       <c r="B21" s="118" t="s">
         <v>515</v>
       </c>
@@ -28033,7 +28739,7 @@
       <c r="M21" s="121"/>
       <c r="O21" s="23"/>
     </row>
-    <row r="22" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" ht="15.5">
       <c r="B22" s="118" t="s">
         <v>516</v>
       </c>
@@ -28050,7 +28756,7 @@
       <c r="M22" s="121"/>
       <c r="O22" s="23"/>
     </row>
-    <row r="23" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" ht="15.5">
       <c r="B23" s="118" t="s">
         <v>517</v>
       </c>
@@ -28067,7 +28773,7 @@
       <c r="M23" s="121"/>
       <c r="O23" s="23"/>
     </row>
-    <row r="24" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" ht="15.5">
       <c r="B24" s="118" t="s">
         <v>518</v>
       </c>
@@ -28084,7 +28790,7 @@
       <c r="M24" s="121"/>
       <c r="O24" s="23"/>
     </row>
-    <row r="25" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" ht="15.5">
       <c r="B25" s="118" t="s">
         <v>519</v>
       </c>
@@ -28101,7 +28807,7 @@
       <c r="M25" s="121"/>
       <c r="O25" s="23"/>
     </row>
-    <row r="26" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" ht="15.5">
       <c r="B26" s="118" t="s">
         <v>520</v>
       </c>
@@ -28118,7 +28824,7 @@
       <c r="M26" s="121"/>
       <c r="O26" s="23"/>
     </row>
-    <row r="27" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" ht="15.5">
       <c r="B27" s="118" t="s">
         <v>521</v>
       </c>
@@ -28135,7 +28841,7 @@
       <c r="M27" s="121"/>
       <c r="O27" s="23"/>
     </row>
-    <row r="28" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" ht="15.5">
       <c r="B28" s="118" t="s">
         <v>522</v>
       </c>
@@ -28152,7 +28858,7 @@
       <c r="M28" s="121"/>
       <c r="O28" s="23"/>
     </row>
-    <row r="29" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" ht="15.5">
       <c r="B29" s="118" t="s">
         <v>523</v>
       </c>
@@ -28169,7 +28875,7 @@
       <c r="M29" s="121"/>
       <c r="O29" s="23"/>
     </row>
-    <row r="30" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15" ht="15.5">
       <c r="B30" s="118" t="s">
         <v>524</v>
       </c>
@@ -28186,7 +28892,7 @@
       <c r="M30" s="121"/>
       <c r="O30" s="23"/>
     </row>
-    <row r="31" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" ht="15.5">
       <c r="B31" s="118" t="s">
         <v>525</v>
       </c>
@@ -28203,7 +28909,7 @@
       <c r="M31" s="121"/>
       <c r="O31" s="23"/>
     </row>
-    <row r="32" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:15" ht="15.5">
       <c r="B32" s="118" t="s">
         <v>526</v>
       </c>
@@ -28220,7 +28926,7 @@
       <c r="M32" s="121"/>
       <c r="O32" s="23"/>
     </row>
-    <row r="33" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" ht="15.5">
       <c r="B33" s="118" t="s">
         <v>527</v>
       </c>
@@ -28237,7 +28943,7 @@
       <c r="M33" s="121"/>
       <c r="O33" s="23"/>
     </row>
-    <row r="34" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" ht="15.5">
       <c r="B34" s="118" t="s">
         <v>528</v>
       </c>
@@ -28254,7 +28960,7 @@
       <c r="M34" s="121"/>
       <c r="O34" s="23"/>
     </row>
-    <row r="35" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:15" ht="15.5">
       <c r="B35" s="118" t="s">
         <v>529</v>
       </c>
@@ -28271,7 +28977,7 @@
       <c r="M35" s="121"/>
       <c r="O35" s="23"/>
     </row>
-    <row r="36" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:15" ht="15.5">
       <c r="B36" s="118" t="s">
         <v>530</v>
       </c>
@@ -28288,7 +28994,7 @@
       <c r="M36" s="121"/>
       <c r="O36" s="23"/>
     </row>
-    <row r="37" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" ht="15.5">
       <c r="B37" s="118" t="s">
         <v>531</v>
       </c>
@@ -28305,7 +29011,7 @@
       <c r="M37" s="121"/>
       <c r="O37" s="23"/>
     </row>
-    <row r="38" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" ht="15.5">
       <c r="B38" s="118" t="s">
         <v>532</v>
       </c>
@@ -28322,7 +29028,7 @@
       <c r="M38" s="121"/>
       <c r="O38" s="23"/>
     </row>
-    <row r="39" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" ht="15.5">
       <c r="B39" s="118" t="s">
         <v>533</v>
       </c>
@@ -28339,7 +29045,7 @@
       <c r="M39" s="121"/>
       <c r="O39" s="23"/>
     </row>
-    <row r="40" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:15" ht="15.5">
       <c r="B40" s="118" t="s">
         <v>534</v>
       </c>
@@ -28356,7 +29062,7 @@
       <c r="M40" s="121"/>
       <c r="O40" s="23"/>
     </row>
-    <row r="41" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:15" ht="15.5">
       <c r="B41" s="118" t="s">
         <v>535</v>
       </c>
@@ -28373,7 +29079,7 @@
       <c r="M41" s="121"/>
       <c r="O41" s="23"/>
     </row>
-    <row r="42" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" ht="15.5">
       <c r="B42" s="118" t="s">
         <v>536</v>
       </c>
@@ -28390,7 +29096,7 @@
       <c r="M42" s="121"/>
       <c r="O42" s="23"/>
     </row>
-    <row r="43" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" ht="15.5">
       <c r="B43" s="118" t="s">
         <v>537</v>
       </c>
@@ -28407,7 +29113,7 @@
       <c r="M43" s="121"/>
       <c r="O43" s="23"/>
     </row>
-    <row r="44" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" ht="15.5">
       <c r="B44" s="118" t="s">
         <v>538</v>
       </c>
@@ -28424,7 +29130,7 @@
       <c r="M44" s="121"/>
       <c r="O44" s="23"/>
     </row>
-    <row r="45" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" ht="15.5">
       <c r="B45" s="118" t="s">
         <v>539</v>
       </c>
@@ -28441,7 +29147,7 @@
       <c r="M45" s="121"/>
       <c r="O45" s="23"/>
     </row>
-    <row r="46" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" ht="15.5">
       <c r="B46" s="118" t="s">
         <v>540</v>
       </c>
@@ -28458,7 +29164,7 @@
       <c r="M46" s="121"/>
       <c r="O46" s="23"/>
     </row>
-    <row r="47" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" ht="15.5">
       <c r="B47" s="118" t="s">
         <v>541</v>
       </c>
@@ -28475,7 +29181,7 @@
       <c r="M47" s="121"/>
       <c r="O47" s="23"/>
     </row>
-    <row r="48" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" ht="15.5">
       <c r="B48" s="118" t="s">
         <v>542</v>
       </c>
@@ -28492,7 +29198,7 @@
       <c r="M48" s="121"/>
       <c r="O48" s="23"/>
     </row>
-    <row r="49" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:15" ht="15.5">
       <c r="B49" s="118" t="s">
         <v>543</v>
       </c>
@@ -28509,7 +29215,7 @@
       <c r="M49" s="121"/>
       <c r="O49" s="23"/>
     </row>
-    <row r="50" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:15" ht="15.5">
       <c r="B50" s="118" t="s">
         <v>544</v>
       </c>
@@ -28526,7 +29232,7 @@
       <c r="M50" s="121"/>
       <c r="O50" s="23"/>
     </row>
-    <row r="51" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:15" ht="15.5">
       <c r="B51" s="118" t="s">
         <v>545</v>
       </c>
@@ -28543,7 +29249,7 @@
       <c r="M51" s="121"/>
       <c r="O51" s="23"/>
     </row>
-    <row r="52" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:15" ht="15.5">
       <c r="B52" s="118" t="s">
         <v>546</v>
       </c>
@@ -28560,7 +29266,7 @@
       <c r="M52" s="121"/>
       <c r="O52" s="23"/>
     </row>
-    <row r="53" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:15" ht="15.5">
       <c r="B53" s="118" t="s">
         <v>547</v>
       </c>
@@ -28577,7 +29283,7 @@
       <c r="M53" s="121"/>
       <c r="O53" s="23"/>
     </row>
-    <row r="54" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:15" ht="15.5">
       <c r="B54" s="118" t="s">
         <v>548</v>
       </c>
@@ -28594,7 +29300,7 @@
       <c r="M54" s="121"/>
       <c r="O54" s="23"/>
     </row>
-    <row r="55" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:15" ht="15.5">
       <c r="B55" s="118" t="s">
         <v>549</v>
       </c>
@@ -28611,7 +29317,7 @@
       <c r="M55" s="121"/>
       <c r="O55" s="23"/>
     </row>
-    <row r="56" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:15" ht="15.5">
       <c r="B56" s="118" t="s">
         <v>550</v>
       </c>
@@ -28628,7 +29334,7 @@
       <c r="M56" s="121"/>
       <c r="O56" s="23"/>
     </row>
-    <row r="57" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:15" ht="15.5">
       <c r="B57" s="118" t="s">
         <v>551</v>
       </c>
@@ -28645,7 +29351,7 @@
       <c r="M57" s="121"/>
       <c r="O57" s="23"/>
     </row>
-    <row r="58" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:15" ht="15.5">
       <c r="B58" s="118" t="s">
         <v>552</v>
       </c>
@@ -28662,7 +29368,7 @@
       <c r="M58" s="121"/>
       <c r="O58" s="23"/>
     </row>
-    <row r="59" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:15" ht="15.5">
       <c r="B59" s="118" t="s">
         <v>553</v>
       </c>
@@ -28679,7 +29385,7 @@
       <c r="M59" s="121"/>
       <c r="O59" s="23"/>
     </row>
-    <row r="60" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:15" ht="15.5">
       <c r="B60" s="118" t="s">
         <v>554</v>
       </c>
@@ -28696,7 +29402,7 @@
       <c r="M60" s="121"/>
       <c r="O60" s="23"/>
     </row>
-    <row r="61" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:15" ht="15.5">
       <c r="B61" s="118" t="s">
         <v>555</v>
       </c>
@@ -28713,7 +29419,7 @@
       <c r="M61" s="121"/>
       <c r="O61" s="23"/>
     </row>
-    <row r="62" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:15" ht="15.5">
       <c r="B62" s="118" t="s">
         <v>556</v>
       </c>
@@ -28730,7 +29436,7 @@
       <c r="M62" s="121"/>
       <c r="O62" s="23"/>
     </row>
-    <row r="63" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:15" ht="15.5">
       <c r="B63" s="118" t="s">
         <v>557</v>
       </c>
@@ -28747,7 +29453,7 @@
       <c r="M63" s="121"/>
       <c r="O63" s="23"/>
     </row>
-    <row r="64" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:15" ht="15.5">
       <c r="B64" s="118" t="s">
         <v>558</v>
       </c>
@@ -28764,7 +29470,7 @@
       <c r="M64" s="121"/>
       <c r="O64" s="23"/>
     </row>
-    <row r="65" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:15" ht="15.5">
       <c r="B65" s="118" t="s">
         <v>559</v>
       </c>
@@ -28781,7 +29487,7 @@
       <c r="M65" s="121"/>
       <c r="O65" s="23"/>
     </row>
-    <row r="66" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:15" ht="15.5">
       <c r="B66" s="118" t="s">
         <v>560</v>
       </c>
@@ -28798,7 +29504,7 @@
       <c r="M66" s="121"/>
       <c r="O66" s="23"/>
     </row>
-    <row r="67" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" ht="15.5">
       <c r="B67" s="118" t="s">
         <v>561</v>
       </c>
@@ -28815,7 +29521,7 @@
       <c r="M67" s="121"/>
       <c r="O67" s="23"/>
     </row>
-    <row r="68" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:15" ht="15.5">
       <c r="B68" s="118" t="s">
         <v>562</v>
       </c>
@@ -28832,7 +29538,7 @@
       <c r="M68" s="121"/>
       <c r="O68" s="23"/>
     </row>
-    <row r="69" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:15" ht="15.5">
       <c r="B69" s="118" t="s">
         <v>563</v>
       </c>
@@ -28849,7 +29555,7 @@
       <c r="M69" s="121"/>
       <c r="O69" s="23"/>
     </row>
-    <row r="70" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:15" ht="15.5">
       <c r="B70" s="118" t="s">
         <v>564</v>
       </c>
@@ -28866,7 +29572,7 @@
       <c r="M70" s="121"/>
       <c r="O70" s="23"/>
     </row>
-    <row r="71" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:15" ht="15.5">
       <c r="B71" s="118" t="s">
         <v>565</v>
       </c>
@@ -28883,7 +29589,7 @@
       <c r="M71" s="121"/>
       <c r="O71" s="23"/>
     </row>
-    <row r="72" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:15" ht="15.5">
       <c r="B72" s="118" t="s">
         <v>566</v>
       </c>
@@ -28900,7 +29606,7 @@
       <c r="M72" s="121"/>
       <c r="O72" s="23"/>
     </row>
-    <row r="73" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" ht="15.5">
       <c r="B73" s="118" t="s">
         <v>567</v>
       </c>
@@ -28917,7 +29623,7 @@
       <c r="M73" s="121"/>
       <c r="O73" s="23"/>
     </row>
-    <row r="74" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:15" ht="15.5">
       <c r="B74" s="118" t="s">
         <v>568</v>
       </c>
@@ -28934,7 +29640,7 @@
       <c r="M74" s="121"/>
       <c r="O74" s="23"/>
     </row>
-    <row r="75" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:15" ht="15.5">
       <c r="B75" s="118" t="s">
         <v>569</v>
       </c>
@@ -28951,7 +29657,7 @@
       <c r="M75" s="121"/>
       <c r="O75" s="23"/>
     </row>
-    <row r="76" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:15" ht="15.5">
       <c r="B76" s="118" t="s">
         <v>570</v>
       </c>
@@ -28968,7 +29674,7 @@
       <c r="M76" s="121"/>
       <c r="O76" s="23"/>
     </row>
-    <row r="77" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" ht="15.5">
       <c r="B77" s="118" t="s">
         <v>571</v>
       </c>
@@ -28985,7 +29691,7 @@
       <c r="M77" s="121"/>
       <c r="O77" s="23"/>
     </row>
-    <row r="78" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:15" ht="15.5">
       <c r="B78" s="118" t="s">
         <v>572</v>
       </c>
@@ -29002,7 +29708,7 @@
       <c r="M78" s="121"/>
       <c r="O78" s="23"/>
     </row>
-    <row r="79" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:15" ht="15.5">
       <c r="B79" s="118" t="s">
         <v>573</v>
       </c>
@@ -29019,7 +29725,7 @@
       <c r="M79" s="121"/>
       <c r="O79" s="23"/>
     </row>
-    <row r="80" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" ht="15.5">
       <c r="B80" s="118" t="s">
         <v>574</v>
       </c>
@@ -29036,7 +29742,7 @@
       <c r="M80" s="121"/>
       <c r="O80" s="23"/>
     </row>
-    <row r="81" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:15" ht="15.5">
       <c r="B81" s="118" t="s">
         <v>575</v>
       </c>
@@ -29053,7 +29759,7 @@
       <c r="M81" s="121"/>
       <c r="O81" s="23"/>
     </row>
-    <row r="82" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:15" ht="15.5">
       <c r="B82" s="118" t="s">
         <v>576</v>
       </c>
@@ -29070,7 +29776,7 @@
       <c r="M82" s="121"/>
       <c r="O82" s="23"/>
     </row>
-    <row r="83" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:15" ht="15.5">
       <c r="B83" s="118" t="s">
         <v>577</v>
       </c>
@@ -29087,7 +29793,7 @@
       <c r="M83" s="121"/>
       <c r="O83" s="23"/>
     </row>
-    <row r="84" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:15" ht="15.5">
       <c r="B84" s="118" t="s">
         <v>578</v>
       </c>
@@ -29104,7 +29810,7 @@
       <c r="M84" s="121"/>
       <c r="O84" s="23"/>
     </row>
-    <row r="85" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:15" ht="15.5">
       <c r="B85" s="118" t="s">
         <v>579</v>
       </c>
@@ -29121,7 +29827,7 @@
       <c r="M85" s="121"/>
       <c r="O85" s="23"/>
     </row>
-    <row r="86" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:15" ht="15.5">
       <c r="B86" s="118" t="s">
         <v>580</v>
       </c>
@@ -29138,7 +29844,7 @@
       <c r="M86" s="121"/>
       <c r="O86" s="23"/>
     </row>
-    <row r="87" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:15" ht="15.5">
       <c r="B87" s="118" t="s">
         <v>581</v>
       </c>
@@ -29155,7 +29861,7 @@
       <c r="M87" s="121"/>
       <c r="O87" s="23"/>
     </row>
-    <row r="88" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:15" ht="15.5">
       <c r="B88" s="118" t="s">
         <v>582</v>
       </c>
@@ -29172,7 +29878,7 @@
       <c r="M88" s="121"/>
       <c r="O88" s="23"/>
     </row>
-    <row r="89" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:15" ht="15.5">
       <c r="B89" s="118" t="s">
         <v>583</v>
       </c>
@@ -29189,7 +29895,7 @@
       <c r="M89" s="121"/>
       <c r="O89" s="23"/>
     </row>
-    <row r="90" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:15" ht="15.5">
       <c r="B90" s="118" t="s">
         <v>584</v>
       </c>
@@ -29206,7 +29912,7 @@
       <c r="M90" s="121"/>
       <c r="O90" s="23"/>
     </row>
-    <row r="91" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:15" ht="15.5">
       <c r="B91" s="118" t="s">
         <v>585</v>
       </c>
@@ -29223,7 +29929,7 @@
       <c r="M91" s="121"/>
       <c r="O91" s="23"/>
     </row>
-    <row r="92" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:15" ht="15.5">
       <c r="B92" s="118" t="s">
         <v>586</v>
       </c>
@@ -29240,7 +29946,7 @@
       <c r="M92" s="121"/>
       <c r="O92" s="23"/>
     </row>
-    <row r="93" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:15" ht="15.5">
       <c r="B93" s="118" t="s">
         <v>587</v>
       </c>
@@ -29257,7 +29963,7 @@
       <c r="M93" s="121"/>
       <c r="O93" s="23"/>
     </row>
-    <row r="94" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:15" ht="15.5">
       <c r="B94" s="118" t="s">
         <v>588</v>
       </c>
@@ -29274,7 +29980,7 @@
       <c r="M94" s="121"/>
       <c r="O94" s="23"/>
     </row>
-    <row r="95" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:15" ht="15.5">
       <c r="B95" s="118" t="s">
         <v>589</v>
       </c>
@@ -29291,7 +29997,7 @@
       <c r="M95" s="121"/>
       <c r="O95" s="23"/>
     </row>
-    <row r="96" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:15" ht="15.5">
       <c r="B96" s="118" t="s">
         <v>590</v>
       </c>
@@ -29308,7 +30014,7 @@
       <c r="M96" s="121"/>
       <c r="O96" s="23"/>
     </row>
-    <row r="97" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:15" ht="15.5">
       <c r="B97" s="118" t="s">
         <v>591</v>
       </c>
@@ -29325,7 +30031,7 @@
       <c r="M97" s="121"/>
       <c r="O97" s="23"/>
     </row>
-    <row r="98" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:15" ht="15.5">
       <c r="B98" s="118" t="s">
         <v>592</v>
       </c>
@@ -29342,7 +30048,7 @@
       <c r="M98" s="121"/>
       <c r="O98" s="23"/>
     </row>
-    <row r="99" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:15" ht="15.5">
       <c r="B99" s="118" t="s">
         <v>593</v>
       </c>
@@ -29359,7 +30065,7 @@
       <c r="M99" s="121"/>
       <c r="O99" s="23"/>
     </row>
-    <row r="100" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:15" ht="15.5">
       <c r="B100" s="118" t="s">
         <v>594</v>
       </c>
@@ -29376,7 +30082,7 @@
       <c r="M100" s="121"/>
       <c r="O100" s="23"/>
     </row>
-    <row r="101" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:15" ht="15.5">
       <c r="B101" s="118" t="s">
         <v>595</v>
       </c>
@@ -29393,7 +30099,7 @@
       <c r="M101" s="121"/>
       <c r="O101" s="23"/>
     </row>
-    <row r="102" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:15" ht="15.5">
       <c r="B102" s="118" t="s">
         <v>596</v>
       </c>
@@ -29410,7 +30116,7 @@
       <c r="M102" s="121"/>
       <c r="O102" s="23"/>
     </row>
-    <row r="103" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:15" ht="15.5">
       <c r="B103" s="118" t="s">
         <v>597</v>
       </c>
@@ -29427,7 +30133,7 @@
       <c r="M103" s="121"/>
       <c r="O103" s="23"/>
     </row>
-    <row r="104" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:15" ht="15.5">
       <c r="B104" s="118" t="s">
         <v>598</v>
       </c>
@@ -29444,7 +30150,7 @@
       <c r="M104" s="121"/>
       <c r="O104" s="23"/>
     </row>
-    <row r="105" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:15" ht="15.5">
       <c r="B105" s="118" t="s">
         <v>599</v>
       </c>
@@ -29461,7 +30167,7 @@
       <c r="M105" s="121"/>
       <c r="O105" s="23"/>
     </row>
-    <row r="106" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:15" ht="15.5">
       <c r="B106" s="118" t="s">
         <v>600</v>
       </c>
@@ -29478,7 +30184,7 @@
       <c r="M106" s="121"/>
       <c r="O106" s="23"/>
     </row>
-    <row r="107" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:15" ht="15.5">
       <c r="B107" s="118" t="s">
         <v>601</v>
       </c>
@@ -29495,7 +30201,7 @@
       <c r="M107" s="121"/>
       <c r="O107" s="23"/>
     </row>
-    <row r="108" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:15" ht="15.5">
       <c r="B108" s="118" t="s">
         <v>602</v>
       </c>
@@ -29512,7 +30218,7 @@
       <c r="M108" s="121"/>
       <c r="O108" s="23"/>
     </row>
-    <row r="109" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:15" ht="15.5">
       <c r="B109" s="118" t="s">
         <v>603</v>
       </c>
@@ -29529,7 +30235,7 @@
       <c r="M109" s="121"/>
       <c r="O109" s="23"/>
     </row>
-    <row r="110" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:15" ht="15.5">
       <c r="B110" s="118" t="s">
         <v>604</v>
       </c>
@@ -29546,7 +30252,7 @@
       <c r="M110" s="121"/>
       <c r="O110" s="23"/>
     </row>
-    <row r="111" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:15" ht="15.5">
       <c r="B111" s="118" t="s">
         <v>605</v>
       </c>
@@ -29563,7 +30269,7 @@
       <c r="M111" s="121"/>
       <c r="O111" s="23"/>
     </row>
-    <row r="112" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:15" ht="15.5">
       <c r="B112" s="118" t="s">
         <v>606</v>
       </c>
@@ -29580,7 +30286,7 @@
       <c r="M112" s="121"/>
       <c r="O112" s="23"/>
     </row>
-    <row r="113" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:15" ht="15.5">
       <c r="B113" s="118" t="s">
         <v>607</v>
       </c>
@@ -29597,7 +30303,7 @@
       <c r="M113" s="121"/>
       <c r="O113" s="23"/>
     </row>
-    <row r="114" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:15" ht="15.5">
       <c r="B114" s="118" t="s">
         <v>608</v>
       </c>
@@ -29614,7 +30320,7 @@
       <c r="M114" s="121"/>
       <c r="O114" s="23"/>
     </row>
-    <row r="115" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:15" ht="15.5">
       <c r="B115" s="118" t="s">
         <v>609</v>
       </c>
@@ -29631,7 +30337,7 @@
       <c r="M115" s="121"/>
       <c r="O115" s="23"/>
     </row>
-    <row r="116" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:15" ht="15.5">
       <c r="B116" s="118" t="s">
         <v>610</v>
       </c>
@@ -29648,7 +30354,7 @@
       <c r="M116" s="121"/>
       <c r="O116" s="23"/>
     </row>
-    <row r="117" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:15" ht="15.5">
       <c r="B117" s="118" t="s">
         <v>611</v>
       </c>
@@ -29665,7 +30371,7 @@
       <c r="M117" s="121"/>
       <c r="O117" s="23"/>
     </row>
-    <row r="118" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:15" ht="15.5">
       <c r="B118" s="118" t="s">
         <v>612</v>
       </c>
@@ -29682,7 +30388,7 @@
       <c r="M118" s="121"/>
       <c r="O118" s="23"/>
     </row>
-    <row r="119" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:15" ht="15.5">
       <c r="B119" s="118" t="s">
         <v>613</v>
       </c>
@@ -29699,7 +30405,7 @@
       <c r="M119" s="121"/>
       <c r="O119" s="23"/>
     </row>
-    <row r="120" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:15" ht="15.5">
       <c r="B120" s="118" t="s">
         <v>614</v>
       </c>
@@ -29716,7 +30422,7 @@
       <c r="M120" s="121"/>
       <c r="O120" s="23"/>
     </row>
-    <row r="121" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:15" ht="15.5">
       <c r="B121" s="118" t="s">
         <v>615</v>
       </c>
@@ -29733,7 +30439,7 @@
       <c r="M121" s="121"/>
       <c r="O121" s="23"/>
     </row>
-    <row r="122" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:15" ht="15.5">
       <c r="B122" s="118" t="s">
         <v>616</v>
       </c>
@@ -29750,7 +30456,7 @@
       <c r="M122" s="121"/>
       <c r="O122" s="23"/>
     </row>
-    <row r="123" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:15" ht="15.5">
       <c r="B123" s="118" t="s">
         <v>617</v>
       </c>
@@ -29767,7 +30473,7 @@
       <c r="M123" s="121"/>
       <c r="O123" s="23"/>
     </row>
-    <row r="124" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:15" ht="15.5">
       <c r="B124" s="118" t="s">
         <v>618</v>
       </c>
@@ -29784,7 +30490,7 @@
       <c r="M124" s="121"/>
       <c r="O124" s="23"/>
     </row>
-    <row r="125" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:15" ht="15.5">
       <c r="B125" s="118" t="s">
         <v>619</v>
       </c>
@@ -29801,7 +30507,7 @@
       <c r="M125" s="121"/>
       <c r="O125" s="23"/>
     </row>
-    <row r="126" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:15" ht="15.5">
       <c r="B126" s="118" t="s">
         <v>620</v>
       </c>
@@ -29818,7 +30524,7 @@
       <c r="M126" s="121"/>
       <c r="O126" s="23"/>
     </row>
-    <row r="127" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:15" ht="15.5">
       <c r="B127" s="118" t="s">
         <v>621</v>
       </c>
@@ -29835,7 +30541,7 @@
       <c r="M127" s="121"/>
       <c r="O127" s="23"/>
     </row>
-    <row r="128" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:15" ht="15.5">
       <c r="B128" s="118" t="s">
         <v>622</v>
       </c>
@@ -29852,7 +30558,7 @@
       <c r="M128" s="121"/>
       <c r="O128" s="23"/>
     </row>
-    <row r="129" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:15" ht="15.5">
       <c r="B129" s="118" t="s">
         <v>623</v>
       </c>
@@ -29869,7 +30575,7 @@
       <c r="M129" s="121"/>
       <c r="O129" s="23"/>
     </row>
-    <row r="130" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:15" ht="15.5">
       <c r="B130" s="118" t="s">
         <v>624</v>
       </c>
@@ -29886,7 +30592,7 @@
       <c r="M130" s="121"/>
       <c r="O130" s="23"/>
     </row>
-    <row r="131" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:15" ht="15.5">
       <c r="B131" s="118" t="s">
         <v>625</v>
       </c>
@@ -29903,7 +30609,7 @@
       <c r="M131" s="121"/>
       <c r="O131" s="23"/>
     </row>
-    <row r="132" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:15" ht="15.5">
       <c r="B132" s="118" t="s">
         <v>626</v>
       </c>
@@ -29920,7 +30626,7 @@
       <c r="M132" s="121"/>
       <c r="O132" s="23"/>
     </row>
-    <row r="133" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:15" ht="15.5">
       <c r="B133" s="118" t="s">
         <v>627</v>
       </c>
@@ -29937,7 +30643,7 @@
       <c r="M133" s="121"/>
       <c r="O133" s="23"/>
     </row>
-    <row r="134" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:15" ht="15.5">
       <c r="B134" s="118" t="s">
         <v>628</v>
       </c>
@@ -29954,7 +30660,7 @@
       <c r="M134" s="121"/>
       <c r="O134" s="23"/>
     </row>
-    <row r="135" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:15" ht="15.5">
       <c r="B135" s="118" t="s">
         <v>629</v>
       </c>
@@ -29971,7 +30677,7 @@
       <c r="M135" s="121"/>
       <c r="O135" s="23"/>
     </row>
-    <row r="136" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:15" ht="15.5">
       <c r="B136" s="118" t="s">
         <v>630</v>
       </c>
@@ -29988,7 +30694,7 @@
       <c r="M136" s="121"/>
       <c r="O136" s="23"/>
     </row>
-    <row r="137" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:15" ht="15.5">
       <c r="B137" s="118" t="s">
         <v>631</v>
       </c>
@@ -30005,7 +30711,7 @@
       <c r="M137" s="121"/>
       <c r="O137" s="23"/>
     </row>
-    <row r="138" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:15" ht="15.5">
       <c r="B138" s="118" t="s">
         <v>632</v>
       </c>
@@ -30022,7 +30728,7 @@
       <c r="M138" s="121"/>
       <c r="O138" s="23"/>
     </row>
-    <row r="139" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:15" ht="15.5">
       <c r="B139" s="118" t="s">
         <v>633</v>
       </c>
@@ -30039,7 +30745,7 @@
       <c r="M139" s="121"/>
       <c r="O139" s="23"/>
     </row>
-    <row r="140" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:15" ht="15.5">
       <c r="B140" s="118" t="s">
         <v>634</v>
       </c>
@@ -30056,7 +30762,7 @@
       <c r="M140" s="121"/>
       <c r="O140" s="23"/>
     </row>
-    <row r="141" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:15" ht="15.5">
       <c r="B141" s="118" t="s">
         <v>635</v>
       </c>
@@ -30073,7 +30779,7 @@
       <c r="M141" s="121"/>
       <c r="O141" s="23"/>
     </row>
-    <row r="142" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:15" ht="15.5">
       <c r="B142" s="118" t="s">
         <v>636</v>
       </c>
@@ -30090,7 +30796,7 @@
       <c r="M142" s="121"/>
       <c r="O142" s="23"/>
     </row>
-    <row r="143" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:15" ht="15.5">
       <c r="B143" s="118" t="s">
         <v>637</v>
       </c>
@@ -30107,7 +30813,7 @@
       <c r="M143" s="121"/>
       <c r="O143" s="23"/>
     </row>
-    <row r="144" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:15" ht="15.5">
       <c r="B144" s="118" t="s">
         <v>638</v>
       </c>
@@ -30124,7 +30830,7 @@
       <c r="M144" s="121"/>
       <c r="O144" s="23"/>
     </row>
-    <row r="145" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:15" ht="15.5">
       <c r="B145" s="118" t="s">
         <v>639</v>
       </c>
@@ -30141,7 +30847,7 @@
       <c r="M145" s="121"/>
       <c r="O145" s="23"/>
     </row>
-    <row r="146" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:15" ht="15.5">
       <c r="B146" s="118" t="s">
         <v>640</v>
       </c>
@@ -30158,7 +30864,7 @@
       <c r="M146" s="121"/>
       <c r="O146" s="23"/>
     </row>
-    <row r="147" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:15" ht="15.5">
       <c r="B147" s="118" t="s">
         <v>641</v>
       </c>
@@ -30175,7 +30881,7 @@
       <c r="M147" s="121"/>
       <c r="O147" s="23"/>
     </row>
-    <row r="148" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:15" ht="15.5">
       <c r="B148" s="118" t="s">
         <v>642</v>
       </c>
@@ -30192,7 +30898,7 @@
       <c r="M148" s="121"/>
       <c r="O148" s="23"/>
     </row>
-    <row r="149" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:15" ht="15.5">
       <c r="B149" s="118" t="s">
         <v>643</v>
       </c>
@@ -30209,7 +30915,7 @@
       <c r="M149" s="121"/>
       <c r="O149" s="23"/>
     </row>
-    <row r="150" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:15" ht="15.5">
       <c r="B150" s="118" t="s">
         <v>644</v>
       </c>
@@ -30226,7 +30932,7 @@
       <c r="M150" s="121"/>
       <c r="O150" s="23"/>
     </row>
-    <row r="151" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:15" ht="15.5">
       <c r="B151" s="118" t="s">
         <v>645</v>
       </c>
@@ -30243,7 +30949,7 @@
       <c r="M151" s="121"/>
       <c r="O151" s="23"/>
     </row>
-    <row r="152" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:15" ht="15.5">
       <c r="B152" s="118" t="s">
         <v>646</v>
       </c>
@@ -30260,7 +30966,7 @@
       <c r="M152" s="121"/>
       <c r="O152" s="23"/>
     </row>
-    <row r="153" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:15" ht="15.5">
       <c r="B153" s="118" t="s">
         <v>647</v>
       </c>
@@ -30277,7 +30983,7 @@
       <c r="M153" s="121"/>
       <c r="O153" s="23"/>
     </row>
-    <row r="154" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:15" ht="15.5">
       <c r="B154" s="118" t="s">
         <v>648</v>
       </c>
@@ -30294,7 +31000,7 @@
       <c r="M154" s="121"/>
       <c r="O154" s="23"/>
     </row>
-    <row r="155" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:15" ht="15.5">
       <c r="B155" s="118" t="s">
         <v>649</v>
       </c>
@@ -30311,7 +31017,7 @@
       <c r="M155" s="121"/>
       <c r="O155" s="23"/>
     </row>
-    <row r="156" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:15" ht="15.5">
       <c r="B156" s="118" t="s">
         <v>650</v>
       </c>
@@ -30328,7 +31034,7 @@
       <c r="M156" s="121"/>
       <c r="O156" s="23"/>
     </row>
-    <row r="157" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:15" ht="15.5">
       <c r="B157" s="118" t="s">
         <v>651</v>
       </c>
@@ -30345,7 +31051,7 @@
       <c r="M157" s="121"/>
       <c r="O157" s="23"/>
     </row>
-    <row r="158" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:15" ht="15.5">
       <c r="B158" s="118" t="s">
         <v>652</v>
       </c>
@@ -30362,7 +31068,7 @@
       <c r="M158" s="121"/>
       <c r="O158" s="23"/>
     </row>
-    <row r="159" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:15" ht="15.5">
       <c r="B159" s="118" t="s">
         <v>653</v>
       </c>
@@ -30378,7 +31084,7 @@
       <c r="L159" s="120"/>
       <c r="M159" s="121"/>
     </row>
-    <row r="160" spans="2:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:15" ht="15.5">
       <c r="B160" s="118" t="s">
         <v>654</v>
       </c>
@@ -30394,7 +31100,7 @@
       <c r="L160" s="120"/>
       <c r="M160" s="121"/>
     </row>
-    <row r="161" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:13" ht="15.5">
       <c r="B161" s="118" t="s">
         <v>655</v>
       </c>
@@ -30410,7 +31116,7 @@
       <c r="L161" s="120"/>
       <c r="M161" s="121"/>
     </row>
-    <row r="162" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:13" ht="15.5">
       <c r="B162" s="118" t="s">
         <v>656</v>
       </c>
@@ -30426,7 +31132,7 @@
       <c r="L162" s="120"/>
       <c r="M162" s="121"/>
     </row>
-    <row r="163" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:13" ht="15.5">
       <c r="B163" s="118" t="s">
         <v>657</v>
       </c>
@@ -30442,7 +31148,7 @@
       <c r="L163" s="120"/>
       <c r="M163" s="121"/>
     </row>
-    <row r="164" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:13" ht="15.5">
       <c r="B164" s="118" t="s">
         <v>658</v>
       </c>
@@ -30458,7 +31164,7 @@
       <c r="L164" s="120"/>
       <c r="M164" s="121"/>
     </row>
-    <row r="165" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:13" ht="15.5">
       <c r="B165" s="118" t="s">
         <v>659</v>
       </c>
@@ -30474,7 +31180,7 @@
       <c r="L165" s="120"/>
       <c r="M165" s="121"/>
     </row>
-    <row r="166" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:13" ht="15.5">
       <c r="B166" s="118" t="s">
         <v>660</v>
       </c>
@@ -30490,7 +31196,7 @@
       <c r="L166" s="120"/>
       <c r="M166" s="121"/>
     </row>
-    <row r="167" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:13" ht="15.5">
       <c r="B167" s="118" t="s">
         <v>661</v>
       </c>
@@ -30506,7 +31212,7 @@
       <c r="L167" s="120"/>
       <c r="M167" s="121"/>
     </row>
-    <row r="168" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:13" ht="15.5">
       <c r="B168" s="118" t="s">
         <v>662</v>
       </c>
@@ -30522,7 +31228,7 @@
       <c r="L168" s="120"/>
       <c r="M168" s="121"/>
     </row>
-    <row r="169" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:13" ht="15.5">
       <c r="B169" s="118" t="s">
         <v>663</v>
       </c>
@@ -30538,7 +31244,7 @@
       <c r="L169" s="120"/>
       <c r="M169" s="121"/>
     </row>
-    <row r="170" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:13" ht="15.5">
       <c r="B170" s="118" t="s">
         <v>664</v>
       </c>
@@ -30554,7 +31260,7 @@
       <c r="L170" s="120"/>
       <c r="M170" s="121"/>
     </row>
-    <row r="171" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:13" ht="15.5">
       <c r="B171" s="118" t="s">
         <v>665</v>
       </c>
@@ -30570,7 +31276,7 @@
       <c r="L171" s="120"/>
       <c r="M171" s="121"/>
     </row>
-    <row r="172" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:13" ht="15.5">
       <c r="B172" s="118" t="s">
         <v>666</v>
       </c>
@@ -30586,7 +31292,7 @@
       <c r="L172" s="120"/>
       <c r="M172" s="121"/>
     </row>
-    <row r="173" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:13" ht="15.5">
       <c r="B173" s="118" t="s">
         <v>667</v>
       </c>
@@ -30602,7 +31308,7 @@
       <c r="L173" s="120"/>
       <c r="M173" s="121"/>
     </row>
-    <row r="174" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:13" ht="15.5">
       <c r="B174" s="118" t="s">
         <v>668</v>
       </c>
@@ -30618,7 +31324,7 @@
       <c r="L174" s="120"/>
       <c r="M174" s="121"/>
     </row>
-    <row r="175" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:13" ht="15.5">
       <c r="B175" s="118" t="s">
         <v>669</v>
       </c>
@@ -30634,7 +31340,7 @@
       <c r="L175" s="120"/>
       <c r="M175" s="121"/>
     </row>
-    <row r="176" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:13" ht="15.5">
       <c r="B176" s="118" t="s">
         <v>670</v>
       </c>
@@ -30650,7 +31356,7 @@
       <c r="L176" s="120"/>
       <c r="M176" s="121"/>
     </row>
-    <row r="177" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:13" ht="15.5">
       <c r="B177" s="118" t="s">
         <v>671</v>
       </c>
@@ -30666,7 +31372,7 @@
       <c r="L177" s="120"/>
       <c r="M177" s="121"/>
     </row>
-    <row r="178" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:13" ht="15.5">
       <c r="B178" s="118" t="s">
         <v>672</v>
       </c>
@@ -30682,7 +31388,7 @@
       <c r="L178" s="120"/>
       <c r="M178" s="121"/>
     </row>
-    <row r="179" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:13" ht="15.5">
       <c r="B179" s="118" t="s">
         <v>673</v>
       </c>
@@ -30698,7 +31404,7 @@
       <c r="L179" s="120"/>
       <c r="M179" s="121"/>
     </row>
-    <row r="180" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:13" ht="15.5">
       <c r="B180" s="118" t="s">
         <v>674</v>
       </c>
@@ -30714,7 +31420,7 @@
       <c r="L180" s="120"/>
       <c r="M180" s="121"/>
     </row>
-    <row r="181" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:13" ht="15.5">
       <c r="B181" s="118" t="s">
         <v>675</v>
       </c>
@@ -30730,7 +31436,7 @@
       <c r="L181" s="120"/>
       <c r="M181" s="121"/>
     </row>
-    <row r="182" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:13" ht="15.5">
       <c r="B182" s="118" t="s">
         <v>676</v>
       </c>
@@ -30746,7 +31452,7 @@
       <c r="L182" s="120"/>
       <c r="M182" s="121"/>
     </row>
-    <row r="183" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:13" ht="15.5">
       <c r="B183" s="118" t="s">
         <v>677</v>
       </c>
@@ -30762,7 +31468,7 @@
       <c r="L183" s="120"/>
       <c r="M183" s="121"/>
     </row>
-    <row r="184" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:13" ht="15.5">
       <c r="B184" s="118" t="s">
         <v>678</v>
       </c>
@@ -30778,7 +31484,7 @@
       <c r="L184" s="120"/>
       <c r="M184" s="121"/>
     </row>
-    <row r="185" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:13" ht="15.5">
       <c r="B185" s="118" t="s">
         <v>679</v>
       </c>
@@ -30794,7 +31500,7 @@
       <c r="L185" s="120"/>
       <c r="M185" s="121"/>
     </row>
-    <row r="186" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:13" ht="15.5">
       <c r="B186" s="118" t="s">
         <v>680</v>
       </c>
@@ -30810,7 +31516,7 @@
       <c r="L186" s="120"/>
       <c r="M186" s="121"/>
     </row>
-    <row r="187" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:13" ht="15.5">
       <c r="B187" s="118" t="s">
         <v>681</v>
       </c>
@@ -30826,7 +31532,7 @@
       <c r="L187" s="120"/>
       <c r="M187" s="121"/>
     </row>
-    <row r="188" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:13" ht="15.5">
       <c r="B188" s="118" t="s">
         <v>682</v>
       </c>
@@ -30842,7 +31548,7 @@
       <c r="L188" s="120"/>
       <c r="M188" s="121"/>
     </row>
-    <row r="189" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:13" ht="15.5">
       <c r="B189" s="118" t="s">
         <v>683</v>
       </c>
@@ -30858,7 +31564,7 @@
       <c r="L189" s="120"/>
       <c r="M189" s="121"/>
     </row>
-    <row r="190" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:13" ht="15.5">
       <c r="B190" s="118" t="s">
         <v>684</v>
       </c>
@@ -30874,7 +31580,7 @@
       <c r="L190" s="120"/>
       <c r="M190" s="121"/>
     </row>
-    <row r="191" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:13" ht="15.5">
       <c r="B191" s="118" t="s">
         <v>685</v>
       </c>
@@ -30890,7 +31596,7 @@
       <c r="L191" s="120"/>
       <c r="M191" s="121"/>
     </row>
-    <row r="192" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:13" ht="15.5">
       <c r="B192" s="118" t="s">
         <v>686</v>
       </c>
@@ -30906,7 +31612,7 @@
       <c r="L192" s="120"/>
       <c r="M192" s="121"/>
     </row>
-    <row r="193" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:13" ht="15.5">
       <c r="B193" s="118" t="s">
         <v>687</v>
       </c>
@@ -30922,7 +31628,7 @@
       <c r="L193" s="120"/>
       <c r="M193" s="121"/>
     </row>
-    <row r="194" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:13" ht="15.5">
       <c r="B194" s="118" t="s">
         <v>688</v>
       </c>
@@ -30938,7 +31644,7 @@
       <c r="L194" s="120"/>
       <c r="M194" s="121"/>
     </row>
-    <row r="195" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:13" ht="15.5">
       <c r="B195" s="118" t="s">
         <v>689</v>
       </c>
@@ -30954,7 +31660,7 @@
       <c r="L195" s="120"/>
       <c r="M195" s="121"/>
     </row>
-    <row r="196" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:13" ht="15.5">
       <c r="B196" s="118" t="s">
         <v>690</v>
       </c>
@@ -30970,7 +31676,7 @@
       <c r="L196" s="120"/>
       <c r="M196" s="121"/>
     </row>
-    <row r="197" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:13" ht="15.5">
       <c r="B197" s="118" t="s">
         <v>691</v>
       </c>
@@ -30986,7 +31692,7 @@
       <c r="L197" s="120"/>
       <c r="M197" s="121"/>
     </row>
-    <row r="198" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:13" ht="15.5">
       <c r="B198" s="118" t="s">
         <v>692</v>
       </c>
@@ -31002,7 +31708,7 @@
       <c r="L198" s="120"/>
       <c r="M198" s="121"/>
     </row>
-    <row r="199" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:13" ht="15.5">
       <c r="B199" s="118" t="s">
         <v>693</v>
       </c>
@@ -31018,7 +31724,7 @@
       <c r="L199" s="120"/>
       <c r="M199" s="121"/>
     </row>
-    <row r="200" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:13" ht="15.5">
       <c r="B200" s="118" t="s">
         <v>694</v>
       </c>
@@ -31034,7 +31740,7 @@
       <c r="L200" s="120"/>
       <c r="M200" s="121"/>
     </row>
-    <row r="201" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:13" ht="15.5">
       <c r="B201" s="118" t="s">
         <v>695</v>
       </c>
@@ -31050,7 +31756,7 @@
       <c r="L201" s="120"/>
       <c r="M201" s="121"/>
     </row>
-    <row r="202" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:13" ht="15.5">
       <c r="B202" s="118" t="s">
         <v>696</v>
       </c>
@@ -31066,7 +31772,7 @@
       <c r="L202" s="120"/>
       <c r="M202" s="121"/>
     </row>
-    <row r="203" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:13" ht="15.5">
       <c r="B203" s="118" t="s">
         <v>697</v>
       </c>
@@ -31082,7 +31788,7 @@
       <c r="L203" s="120"/>
       <c r="M203" s="121"/>
     </row>
-    <row r="204" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:13" ht="15.5">
       <c r="B204" s="118" t="s">
         <v>698</v>
       </c>
@@ -31098,7 +31804,7 @@
       <c r="L204" s="120"/>
       <c r="M204" s="121"/>
     </row>
-    <row r="205" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:13" ht="15.5">
       <c r="B205" s="118" t="s">
         <v>699</v>
       </c>
@@ -31114,7 +31820,7 @@
       <c r="L205" s="120"/>
       <c r="M205" s="121"/>
     </row>
-    <row r="206" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:13" ht="15.5">
       <c r="B206" s="118" t="s">
         <v>700</v>
       </c>
@@ -31130,7 +31836,7 @@
       <c r="L206" s="120"/>
       <c r="M206" s="121"/>
     </row>
-    <row r="207" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:13" ht="15.5">
       <c r="B207" s="118" t="s">
         <v>701</v>
       </c>
@@ -31146,7 +31852,7 @@
       <c r="L207" s="120"/>
       <c r="M207" s="121"/>
     </row>
-    <row r="208" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:13" ht="15.5">
       <c r="B208" s="118" t="s">
         <v>702</v>
       </c>
@@ -31162,7 +31868,7 @@
       <c r="L208" s="120"/>
       <c r="M208" s="121"/>
     </row>
-    <row r="209" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:13" ht="15.5">
       <c r="B209" s="118" t="s">
         <v>703</v>
       </c>
@@ -31178,7 +31884,7 @@
       <c r="L209" s="120"/>
       <c r="M209" s="121"/>
     </row>
-    <row r="210" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:13" ht="15.5">
       <c r="B210" s="118" t="s">
         <v>704</v>
       </c>
@@ -31194,7 +31900,7 @@
       <c r="L210" s="120"/>
       <c r="M210" s="121"/>
     </row>
-    <row r="211" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:13" ht="15.5">
       <c r="B211" s="118" t="s">
         <v>705</v>
       </c>
@@ -31210,7 +31916,7 @@
       <c r="L211" s="120"/>
       <c r="M211" s="121"/>
     </row>
-    <row r="212" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:13" ht="15.5">
       <c r="B212" s="118" t="s">
         <v>706</v>
       </c>
@@ -31226,7 +31932,7 @@
       <c r="L212" s="120"/>
       <c r="M212" s="121"/>
     </row>
-    <row r="213" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:13" ht="15.5">
       <c r="B213" s="118" t="s">
         <v>707</v>
       </c>
@@ -31242,7 +31948,7 @@
       <c r="L213" s="120"/>
       <c r="M213" s="121"/>
     </row>
-    <row r="214" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:13" ht="15.5">
       <c r="B214" s="118" t="s">
         <v>708</v>
       </c>
@@ -31258,7 +31964,7 @@
       <c r="L214" s="120"/>
       <c r="M214" s="121"/>
     </row>
-    <row r="215" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:13" ht="15.5">
       <c r="B215" s="118" t="s">
         <v>709</v>
       </c>
@@ -31274,7 +31980,7 @@
       <c r="L215" s="120"/>
       <c r="M215" s="121"/>
     </row>
-    <row r="216" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:13" ht="15.5">
       <c r="B216" s="118" t="s">
         <v>710</v>
       </c>
@@ -31290,7 +31996,7 @@
       <c r="L216" s="120"/>
       <c r="M216" s="121"/>
     </row>
-    <row r="217" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:13" ht="15.5">
       <c r="B217" s="118" t="s">
         <v>711</v>
       </c>
@@ -31306,7 +32012,7 @@
       <c r="L217" s="120"/>
       <c r="M217" s="121"/>
     </row>
-    <row r="218" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:13" ht="15.5">
       <c r="B218" s="118" t="s">
         <v>712</v>
       </c>
@@ -31322,7 +32028,7 @@
       <c r="L218" s="120"/>
       <c r="M218" s="121"/>
     </row>
-    <row r="219" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:13" ht="15.5">
       <c r="B219" s="118" t="s">
         <v>713</v>
       </c>
@@ -31338,7 +32044,7 @@
       <c r="L219" s="120"/>
       <c r="M219" s="121"/>
     </row>
-    <row r="220" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:13" ht="15.5">
       <c r="B220" s="118" t="s">
         <v>714</v>
       </c>
@@ -31354,7 +32060,7 @@
       <c r="L220" s="120"/>
       <c r="M220" s="121"/>
     </row>
-    <row r="221" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:13" ht="15.5">
       <c r="B221" s="118" t="s">
         <v>715</v>
       </c>
@@ -31370,7 +32076,7 @@
       <c r="L221" s="120"/>
       <c r="M221" s="121"/>
     </row>
-    <row r="222" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:13" ht="15.5">
       <c r="B222" s="118" t="s">
         <v>716</v>
       </c>
@@ -31386,7 +32092,7 @@
       <c r="L222" s="120"/>
       <c r="M222" s="121"/>
     </row>
-    <row r="223" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:13" ht="15.5">
       <c r="B223" s="118" t="s">
         <v>717</v>
       </c>
@@ -31402,7 +32108,7 @@
       <c r="L223" s="120"/>
       <c r="M223" s="121"/>
     </row>
-    <row r="224" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:13" ht="15.5">
       <c r="B224" s="118" t="s">
         <v>718</v>
       </c>
@@ -31418,7 +32124,7 @@
       <c r="L224" s="120"/>
       <c r="M224" s="121"/>
     </row>
-    <row r="225" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:13" ht="15.5">
       <c r="B225" s="118" t="s">
         <v>719</v>
       </c>
@@ -31434,7 +32140,7 @@
       <c r="L225" s="120"/>
       <c r="M225" s="121"/>
     </row>
-    <row r="226" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:13" ht="15.5">
       <c r="B226" s="118" t="s">
         <v>720</v>
       </c>
@@ -31450,7 +32156,7 @@
       <c r="L226" s="120"/>
       <c r="M226" s="121"/>
     </row>
-    <row r="227" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:13" ht="15.5">
       <c r="B227" s="118" t="s">
         <v>721</v>
       </c>
@@ -31466,7 +32172,7 @@
       <c r="L227" s="120"/>
       <c r="M227" s="121"/>
     </row>
-    <row r="228" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:13" ht="15.5">
       <c r="B228" s="118" t="s">
         <v>722</v>
       </c>
@@ -31482,7 +32188,7 @@
       <c r="L228" s="120"/>
       <c r="M228" s="121"/>
     </row>
-    <row r="229" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:13" ht="15.5">
       <c r="B229" s="118" t="s">
         <v>723</v>
       </c>
@@ -31498,7 +32204,7 @@
       <c r="L229" s="120"/>
       <c r="M229" s="121"/>
     </row>
-    <row r="230" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:13" ht="15.5">
       <c r="B230" s="118" t="s">
         <v>724</v>
       </c>
@@ -31514,7 +32220,7 @@
       <c r="L230" s="120"/>
       <c r="M230" s="121"/>
     </row>
-    <row r="231" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:13" ht="15.5">
       <c r="B231" s="118" t="s">
         <v>725</v>
       </c>
@@ -31530,7 +32236,7 @@
       <c r="L231" s="120"/>
       <c r="M231" s="121"/>
     </row>
-    <row r="232" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:13" ht="15.5">
       <c r="B232" s="118" t="s">
         <v>726</v>
       </c>
@@ -31546,7 +32252,7 @@
       <c r="L232" s="120"/>
       <c r="M232" s="121"/>
     </row>
-    <row r="233" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:13" ht="15.5">
       <c r="B233" s="118" t="s">
         <v>727</v>
       </c>
@@ -31562,7 +32268,7 @@
       <c r="L233" s="120"/>
       <c r="M233" s="121"/>
     </row>
-    <row r="234" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:13" ht="15.5">
       <c r="B234" s="118" t="s">
         <v>728</v>
       </c>
@@ -31578,7 +32284,7 @@
       <c r="L234" s="120"/>
       <c r="M234" s="121"/>
     </row>
-    <row r="235" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:13" ht="15.5">
       <c r="B235" s="118" t="s">
         <v>729</v>
       </c>
@@ -31594,7 +32300,7 @@
       <c r="L235" s="120"/>
       <c r="M235" s="121"/>
     </row>
-    <row r="236" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:13" ht="15.5">
       <c r="B236" s="118" t="s">
         <v>730</v>
       </c>
@@ -31610,7 +32316,7 @@
       <c r="L236" s="120"/>
       <c r="M236" s="121"/>
     </row>
-    <row r="237" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:13" ht="15.5">
       <c r="B237" s="118" t="s">
         <v>731</v>
       </c>
@@ -31626,7 +32332,7 @@
       <c r="L237" s="120"/>
       <c r="M237" s="121"/>
     </row>
-    <row r="238" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:13" ht="15.5">
       <c r="B238" s="118" t="s">
         <v>732</v>
       </c>
@@ -31642,7 +32348,7 @@
       <c r="L238" s="120"/>
       <c r="M238" s="121"/>
     </row>
-    <row r="239" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:13" ht="15.5">
       <c r="B239" s="118" t="s">
         <v>733</v>
       </c>
@@ -31658,7 +32364,7 @@
       <c r="L239" s="120"/>
       <c r="M239" s="121"/>
     </row>
-    <row r="240" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:13" ht="15.5">
       <c r="B240" s="118" t="s">
         <v>734</v>
       </c>
@@ -31674,7 +32380,7 @@
       <c r="L240" s="120"/>
       <c r="M240" s="121"/>
     </row>
-    <row r="241" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:13" ht="15.5">
       <c r="B241" s="118" t="s">
         <v>735</v>
       </c>
@@ -31690,7 +32396,7 @@
       <c r="L241" s="120"/>
       <c r="M241" s="121"/>
     </row>
-    <row r="242" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:13" ht="15.5">
       <c r="B242" s="118" t="s">
         <v>736</v>
       </c>
@@ -31706,7 +32412,7 @@
       <c r="L242" s="120"/>
       <c r="M242" s="121"/>
     </row>
-    <row r="243" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:13" ht="15.5">
       <c r="B243" s="118" t="s">
         <v>737</v>
       </c>
@@ -31722,7 +32428,7 @@
       <c r="L243" s="120"/>
       <c r="M243" s="121"/>
     </row>
-    <row r="244" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:13" ht="15.5">
       <c r="B244" s="118" t="s">
         <v>738</v>
       </c>
@@ -31738,7 +32444,7 @@
       <c r="L244" s="120"/>
       <c r="M244" s="121"/>
     </row>
-    <row r="245" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:13" ht="15.5">
       <c r="B245" s="118" t="s">
         <v>739</v>
       </c>
@@ -31754,7 +32460,7 @@
       <c r="L245" s="120"/>
       <c r="M245" s="121"/>
     </row>
-    <row r="246" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:13" ht="15.5">
       <c r="B246" s="118" t="s">
         <v>740</v>
       </c>
@@ -31770,7 +32476,7 @@
       <c r="L246" s="120"/>
       <c r="M246" s="121"/>
     </row>
-    <row r="247" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:13" ht="15.5">
       <c r="B247" s="118" t="s">
         <v>741</v>
       </c>
@@ -31786,7 +32492,7 @@
       <c r="L247" s="120"/>
       <c r="M247" s="121"/>
     </row>
-    <row r="248" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:13" ht="15.5">
       <c r="B248" s="118" t="s">
         <v>742</v>
       </c>
@@ -31802,7 +32508,7 @@
       <c r="L248" s="120"/>
       <c r="M248" s="121"/>
     </row>
-    <row r="249" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:13" ht="15.5">
       <c r="B249" s="118" t="s">
         <v>743</v>
       </c>
@@ -31818,7 +32524,7 @@
       <c r="L249" s="120"/>
       <c r="M249" s="121"/>
     </row>
-    <row r="250" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:13" ht="15.5">
       <c r="B250" s="118" t="s">
         <v>744</v>
       </c>
@@ -31834,7 +32540,7 @@
       <c r="L250" s="120"/>
       <c r="M250" s="121"/>
     </row>
-    <row r="251" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:13" ht="15.5">
       <c r="B251" s="118" t="s">
         <v>745</v>
       </c>
@@ -31850,7 +32556,7 @@
       <c r="L251" s="120"/>
       <c r="M251" s="121"/>
     </row>
-    <row r="252" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:13" ht="15.5">
       <c r="B252" s="118" t="s">
         <v>746</v>
       </c>
@@ -31866,7 +32572,7 @@
       <c r="L252" s="120"/>
       <c r="M252" s="121"/>
     </row>
-    <row r="253" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:13" ht="15.5">
       <c r="B253" s="118" t="s">
         <v>747</v>
       </c>
@@ -31882,7 +32588,7 @@
       <c r="L253" s="120"/>
       <c r="M253" s="121"/>
     </row>
-    <row r="254" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:13" ht="15.5">
       <c r="B254" s="118" t="s">
         <v>748</v>
       </c>
@@ -31898,7 +32604,7 @@
       <c r="L254" s="120"/>
       <c r="M254" s="121"/>
     </row>
-    <row r="255" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:13" ht="15.5">
       <c r="B255" s="118" t="s">
         <v>749</v>
       </c>
@@ -31914,7 +32620,7 @@
       <c r="L255" s="120"/>
       <c r="M255" s="121"/>
     </row>
-    <row r="256" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:13" ht="15.5">
       <c r="B256" s="118" t="s">
         <v>750</v>
       </c>
@@ -31930,7 +32636,7 @@
       <c r="L256" s="120"/>
       <c r="M256" s="121"/>
     </row>
-    <row r="257" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="257" spans="2:13" ht="15.5">
       <c r="B257" s="118" t="s">
         <v>751</v>
       </c>
@@ -31946,7 +32652,7 @@
       <c r="L257" s="120"/>
       <c r="M257" s="121"/>
     </row>
-    <row r="258" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="258" spans="2:13" ht="15.5">
       <c r="B258" s="118" t="s">
         <v>752</v>
       </c>
@@ -31962,7 +32668,7 @@
       <c r="L258" s="120"/>
       <c r="M258" s="121"/>
     </row>
-    <row r="259" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="259" spans="2:13" ht="15.5">
       <c r="B259" s="118" t="s">
         <v>753</v>
       </c>
@@ -31978,7 +32684,7 @@
       <c r="L259" s="120"/>
       <c r="M259" s="121"/>
     </row>
-    <row r="260" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:13" ht="15.5">
       <c r="B260" s="118" t="s">
         <v>754</v>
       </c>
@@ -31994,7 +32700,7 @@
       <c r="L260" s="120"/>
       <c r="M260" s="121"/>
     </row>
-    <row r="261" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:13" ht="15.5">
       <c r="B261" s="118" t="s">
         <v>755</v>
       </c>
@@ -32010,7 +32716,7 @@
       <c r="L261" s="120"/>
       <c r="M261" s="121"/>
     </row>
-    <row r="262" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="262" spans="2:13" ht="15.5">
       <c r="B262" s="118" t="s">
         <v>756</v>
       </c>
@@ -32026,7 +32732,7 @@
       <c r="L262" s="120"/>
       <c r="M262" s="121"/>
     </row>
-    <row r="263" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="263" spans="2:13" ht="15.5">
       <c r="B263" s="118" t="s">
         <v>757</v>
       </c>
@@ -32042,7 +32748,7 @@
       <c r="L263" s="120"/>
       <c r="M263" s="121"/>
     </row>
-    <row r="264" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="264" spans="2:13" ht="15.5">
       <c r="B264" s="118" t="s">
         <v>758</v>
       </c>
@@ -32058,7 +32764,7 @@
       <c r="L264" s="120"/>
       <c r="M264" s="121"/>
     </row>
-    <row r="265" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="265" spans="2:13" ht="15.5">
       <c r="B265" s="118" t="s">
         <v>759</v>
       </c>
@@ -32074,7 +32780,7 @@
       <c r="L265" s="120"/>
       <c r="M265" s="121"/>
     </row>
-    <row r="266" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="266" spans="2:13" ht="15.5">
       <c r="B266" s="118" t="s">
         <v>760</v>
       </c>
@@ -32090,7 +32796,7 @@
       <c r="L266" s="120"/>
       <c r="M266" s="121"/>
     </row>
-    <row r="267" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="267" spans="2:13" ht="15.5">
       <c r="B267" s="118" t="s">
         <v>761</v>
       </c>
@@ -32106,7 +32812,7 @@
       <c r="L267" s="120"/>
       <c r="M267" s="121"/>
     </row>
-    <row r="268" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:13" ht="15.5">
       <c r="B268" s="118" t="s">
         <v>762</v>
       </c>
@@ -32122,7 +32828,7 @@
       <c r="L268" s="120"/>
       <c r="M268" s="121"/>
     </row>
-    <row r="269" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:13" ht="15.5">
       <c r="B269" s="118" t="s">
         <v>763</v>
       </c>
@@ -32138,7 +32844,7 @@
       <c r="L269" s="120"/>
       <c r="M269" s="121"/>
     </row>
-    <row r="270" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:13" ht="15.5">
       <c r="B270" s="118" t="s">
         <v>764</v>
       </c>
@@ -32154,7 +32860,7 @@
       <c r="L270" s="120"/>
       <c r="M270" s="121"/>
     </row>
-    <row r="271" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:13" ht="15.5">
       <c r="B271" s="118" t="s">
         <v>765</v>
       </c>
@@ -32170,7 +32876,7 @@
       <c r="L271" s="120"/>
       <c r="M271" s="121"/>
     </row>
-    <row r="272" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:13" ht="15.5">
       <c r="B272" s="118" t="s">
         <v>766</v>
       </c>
@@ -32186,7 +32892,7 @@
       <c r="L272" s="120"/>
       <c r="M272" s="121"/>
     </row>
-    <row r="273" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="273" spans="2:13" ht="15.5">
       <c r="B273" s="118" t="s">
         <v>767</v>
       </c>
@@ -32202,7 +32908,7 @@
       <c r="L273" s="120"/>
       <c r="M273" s="121"/>
     </row>
-    <row r="274" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:13" ht="15.5">
       <c r="B274" s="118" t="s">
         <v>768</v>
       </c>
@@ -32218,7 +32924,7 @@
       <c r="L274" s="120"/>
       <c r="M274" s="121"/>
     </row>
-    <row r="275" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="275" spans="2:13" ht="15.5">
       <c r="B275" s="118" t="s">
         <v>769</v>
       </c>
@@ -32234,7 +32940,7 @@
       <c r="L275" s="120"/>
       <c r="M275" s="121"/>
     </row>
-    <row r="276" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="276" spans="2:13" ht="15.5">
       <c r="B276" s="118" t="s">
         <v>770</v>
       </c>
@@ -32250,7 +32956,7 @@
       <c r="L276" s="120"/>
       <c r="M276" s="121"/>
     </row>
-    <row r="277" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="277" spans="2:13" ht="15.5">
       <c r="B277" s="118" t="s">
         <v>771</v>
       </c>
@@ -32266,7 +32972,7 @@
       <c r="L277" s="120"/>
       <c r="M277" s="121"/>
     </row>
-    <row r="278" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="278" spans="2:13" ht="15.5">
       <c r="B278" s="118" t="s">
         <v>772</v>
       </c>
@@ -32282,7 +32988,7 @@
       <c r="L278" s="120"/>
       <c r="M278" s="121"/>
     </row>
-    <row r="279" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="279" spans="2:13" ht="15.5">
       <c r="B279" s="118" t="s">
         <v>773</v>
       </c>
@@ -32298,7 +33004,7 @@
       <c r="L279" s="120"/>
       <c r="M279" s="121"/>
     </row>
-    <row r="280" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:13" ht="15.5">
       <c r="B280" s="118" t="s">
         <v>774</v>
       </c>
@@ -32314,7 +33020,7 @@
       <c r="L280" s="120"/>
       <c r="M280" s="121"/>
     </row>
-    <row r="281" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="281" spans="2:13" ht="15.5">
       <c r="B281" s="118" t="s">
         <v>775</v>
       </c>
@@ -32330,7 +33036,7 @@
       <c r="L281" s="120"/>
       <c r="M281" s="121"/>
     </row>
-    <row r="282" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="282" spans="2:13" ht="15.5">
       <c r="B282" s="118" t="s">
         <v>776</v>
       </c>
@@ -32346,7 +33052,7 @@
       <c r="L282" s="120"/>
       <c r="M282" s="121"/>
     </row>
-    <row r="283" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="283" spans="2:13" ht="15.5">
       <c r="B283" s="118" t="s">
         <v>777</v>
       </c>
@@ -32362,7 +33068,7 @@
       <c r="L283" s="120"/>
       <c r="M283" s="121"/>
     </row>
-    <row r="284" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="284" spans="2:13" ht="15.5">
       <c r="B284" s="118" t="s">
         <v>778</v>
       </c>
@@ -32378,7 +33084,7 @@
       <c r="L284" s="120"/>
       <c r="M284" s="121"/>
     </row>
-    <row r="285" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="285" spans="2:13" ht="15.5">
       <c r="B285" s="118" t="s">
         <v>779</v>
       </c>
@@ -32394,7 +33100,7 @@
       <c r="L285" s="120"/>
       <c r="M285" s="121"/>
     </row>
-    <row r="286" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="286" spans="2:13" ht="15.5">
       <c r="B286" s="118" t="s">
         <v>780</v>
       </c>
@@ -32410,7 +33116,7 @@
       <c r="L286" s="120"/>
       <c r="M286" s="121"/>
     </row>
-    <row r="287" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="287" spans="2:13" ht="15.5">
       <c r="B287" s="118" t="s">
         <v>781</v>
       </c>
@@ -32426,7 +33132,7 @@
       <c r="L287" s="120"/>
       <c r="M287" s="121"/>
     </row>
-    <row r="288" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="288" spans="2:13" ht="15.5">
       <c r="B288" s="118" t="s">
         <v>782</v>
       </c>
@@ -32442,7 +33148,7 @@
       <c r="L288" s="120"/>
       <c r="M288" s="121"/>
     </row>
-    <row r="289" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="289" spans="2:13" ht="15.5">
       <c r="B289" s="118" t="s">
         <v>783</v>
       </c>
@@ -32458,7 +33164,7 @@
       <c r="L289" s="120"/>
       <c r="M289" s="121"/>
     </row>
-    <row r="290" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="290" spans="2:13" ht="15.5">
       <c r="B290" s="118" t="s">
         <v>784</v>
       </c>
@@ -32474,7 +33180,7 @@
       <c r="L290" s="120"/>
       <c r="M290" s="121"/>
     </row>
-    <row r="291" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="291" spans="2:13" ht="15.5">
       <c r="B291" s="118" t="s">
         <v>785</v>
       </c>
@@ -32490,7 +33196,7 @@
       <c r="L291" s="120"/>
       <c r="M291" s="121"/>
     </row>
-    <row r="292" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="292" spans="2:13" ht="15.5">
       <c r="B292" s="118" t="s">
         <v>786</v>
       </c>
@@ -32506,7 +33212,7 @@
       <c r="L292" s="120"/>
       <c r="M292" s="121"/>
     </row>
-    <row r="293" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="293" spans="2:13" ht="15.5">
       <c r="B293" s="118" t="s">
         <v>787</v>
       </c>
@@ -32522,7 +33228,7 @@
       <c r="L293" s="120"/>
       <c r="M293" s="121"/>
     </row>
-    <row r="294" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="294" spans="2:13" ht="15.5">
       <c r="B294" s="118" t="s">
         <v>788</v>
       </c>
@@ -32538,7 +33244,7 @@
       <c r="L294" s="120"/>
       <c r="M294" s="121"/>
     </row>
-    <row r="295" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="295" spans="2:13" ht="15.5">
       <c r="B295" s="118" t="s">
         <v>789</v>
       </c>
@@ -32554,7 +33260,7 @@
       <c r="L295" s="120"/>
       <c r="M295" s="121"/>
     </row>
-    <row r="296" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="296" spans="2:13" ht="15.5">
       <c r="B296" s="118" t="s">
         <v>790</v>
       </c>
@@ -32570,7 +33276,7 @@
       <c r="L296" s="120"/>
       <c r="M296" s="121"/>
     </row>
-    <row r="297" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="297" spans="2:13" ht="15.5">
       <c r="B297" s="118" t="s">
         <v>791</v>
       </c>
@@ -32586,7 +33292,7 @@
       <c r="L297" s="120"/>
       <c r="M297" s="121"/>
     </row>
-    <row r="298" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="298" spans="2:13" ht="15.5">
       <c r="B298" s="118" t="s">
         <v>792</v>
       </c>
@@ -32602,7 +33308,7 @@
       <c r="L298" s="120"/>
       <c r="M298" s="121"/>
     </row>
-    <row r="299" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="299" spans="2:13" ht="15.5">
       <c r="B299" s="118" t="s">
         <v>793</v>
       </c>
@@ -32618,7 +33324,7 @@
       <c r="L299" s="120"/>
       <c r="M299" s="121"/>
     </row>
-    <row r="300" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="300" spans="2:13" ht="15.5">
       <c r="B300" s="118" t="s">
         <v>794</v>
       </c>
@@ -32634,7 +33340,7 @@
       <c r="L300" s="120"/>
       <c r="M300" s="121"/>
     </row>
-    <row r="301" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="301" spans="2:13" ht="15.5">
       <c r="B301" s="118" t="s">
         <v>795</v>
       </c>
@@ -32650,7 +33356,7 @@
       <c r="L301" s="120"/>
       <c r="M301" s="121"/>
     </row>
-    <row r="302" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="302" spans="2:13" ht="15.5">
       <c r="B302" s="118" t="s">
         <v>796</v>
       </c>
@@ -32666,7 +33372,7 @@
       <c r="L302" s="120"/>
       <c r="M302" s="121"/>
     </row>
-    <row r="303" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="303" spans="2:13" ht="15.5">
       <c r="B303" s="118" t="s">
         <v>797</v>
       </c>
@@ -32682,7 +33388,7 @@
       <c r="L303" s="120"/>
       <c r="M303" s="121"/>
     </row>
-    <row r="304" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="304" spans="2:13" ht="15.5">
       <c r="B304" s="118" t="s">
         <v>798</v>
       </c>
@@ -32698,7 +33404,7 @@
       <c r="L304" s="120"/>
       <c r="M304" s="121"/>
     </row>
-    <row r="305" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="305" spans="2:13" ht="15.5">
       <c r="B305" s="118" t="s">
         <v>799</v>
       </c>
@@ -32714,7 +33420,7 @@
       <c r="L305" s="120"/>
       <c r="M305" s="121"/>
     </row>
-    <row r="306" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="306" spans="2:13" ht="15.5">
       <c r="B306" s="118" t="s">
         <v>800</v>
       </c>
@@ -32730,7 +33436,7 @@
       <c r="L306" s="120"/>
       <c r="M306" s="121"/>
     </row>
-    <row r="307" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="307" spans="2:13" ht="15.5">
       <c r="B307" s="118" t="s">
         <v>801</v>
       </c>
@@ -32746,7 +33452,7 @@
       <c r="L307" s="120"/>
       <c r="M307" s="121"/>
     </row>
-    <row r="308" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="308" spans="2:13" ht="15.5">
       <c r="B308" s="118" t="s">
         <v>802</v>
       </c>
@@ -32762,7 +33468,7 @@
       <c r="L308" s="120"/>
       <c r="M308" s="121"/>
     </row>
-    <row r="309" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="309" spans="2:13" ht="15.5">
       <c r="B309" s="118" t="s">
         <v>803</v>
       </c>
@@ -32778,7 +33484,7 @@
       <c r="L309" s="120"/>
       <c r="M309" s="121"/>
     </row>
-    <row r="310" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="310" spans="2:13" ht="15.5">
       <c r="B310" s="118" t="s">
         <v>804</v>
       </c>
@@ -32794,7 +33500,7 @@
       <c r="L310" s="120"/>
       <c r="M310" s="121"/>
     </row>
-    <row r="311" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="311" spans="2:13" ht="15.5">
       <c r="B311" s="118" t="s">
         <v>805</v>
       </c>
@@ -32810,7 +33516,7 @@
       <c r="L311" s="120"/>
       <c r="M311" s="121"/>
     </row>
-    <row r="312" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="312" spans="2:13" ht="15.5">
       <c r="B312" s="118" t="s">
         <v>806</v>
       </c>
@@ -32826,7 +33532,7 @@
       <c r="L312" s="120"/>
       <c r="M312" s="121"/>
     </row>
-    <row r="313" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="313" spans="2:13" ht="15.5">
       <c r="B313" s="118" t="s">
         <v>807</v>
       </c>
@@ -32842,7 +33548,7 @@
       <c r="L313" s="120"/>
       <c r="M313" s="121"/>
     </row>
-    <row r="314" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="314" spans="2:13" ht="15.5">
       <c r="B314" s="118" t="s">
         <v>808</v>
       </c>
@@ -32858,7 +33564,7 @@
       <c r="L314" s="120"/>
       <c r="M314" s="121"/>
     </row>
-    <row r="315" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="315" spans="2:13" ht="15.5">
       <c r="B315" s="118" t="s">
         <v>809</v>
       </c>
@@ -32874,7 +33580,7 @@
       <c r="L315" s="120"/>
       <c r="M315" s="121"/>
     </row>
-    <row r="316" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="316" spans="2:13" ht="15.5">
       <c r="B316" s="118" t="s">
         <v>810</v>
       </c>
@@ -32890,7 +33596,7 @@
       <c r="L316" s="120"/>
       <c r="M316" s="121"/>
     </row>
-    <row r="317" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="317" spans="2:13" ht="15.5">
       <c r="B317" s="118" t="s">
         <v>811</v>
       </c>
@@ -32906,7 +33612,7 @@
       <c r="L317" s="120"/>
       <c r="M317" s="121"/>
     </row>
-    <row r="318" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="318" spans="2:13" ht="15.5">
       <c r="B318" s="118" t="s">
         <v>812</v>
       </c>
@@ -32922,7 +33628,7 @@
       <c r="L318" s="120"/>
       <c r="M318" s="121"/>
     </row>
-    <row r="319" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="319" spans="2:13" ht="15.5">
       <c r="B319" s="118" t="s">
         <v>813</v>
       </c>
@@ -32938,7 +33644,7 @@
       <c r="L319" s="120"/>
       <c r="M319" s="121"/>
     </row>
-    <row r="320" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="320" spans="2:13" ht="15.5">
       <c r="B320" s="118" t="s">
         <v>814</v>
       </c>
@@ -32954,7 +33660,7 @@
       <c r="L320" s="120"/>
       <c r="M320" s="121"/>
     </row>
-    <row r="321" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="321" spans="2:13" ht="15.5">
       <c r="B321" s="118" t="s">
         <v>815</v>
       </c>
@@ -32970,7 +33676,7 @@
       <c r="L321" s="120"/>
       <c r="M321" s="121"/>
     </row>
-    <row r="322" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="322" spans="2:13" ht="15.5">
       <c r="B322" s="118" t="s">
         <v>816</v>
       </c>
@@ -32986,7 +33692,7 @@
       <c r="L322" s="120"/>
       <c r="M322" s="121"/>
     </row>
-    <row r="323" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="323" spans="2:13" ht="15.5">
       <c r="B323" s="118" t="s">
         <v>817</v>
       </c>
@@ -33002,7 +33708,7 @@
       <c r="L323" s="120"/>
       <c r="M323" s="121"/>
     </row>
-    <row r="324" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="324" spans="2:13" ht="15.5">
       <c r="B324" s="118" t="s">
         <v>818</v>
       </c>
@@ -33018,7 +33724,7 @@
       <c r="L324" s="120"/>
       <c r="M324" s="121"/>
     </row>
-    <row r="325" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="325" spans="2:13" ht="15.5">
       <c r="B325" s="118" t="s">
         <v>819</v>
       </c>
@@ -33034,7 +33740,7 @@
       <c r="L325" s="120"/>
       <c r="M325" s="121"/>
     </row>
-    <row r="326" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="326" spans="2:13" ht="15.5">
       <c r="B326" s="118" t="s">
         <v>820</v>
       </c>
@@ -33050,7 +33756,7 @@
       <c r="L326" s="120"/>
       <c r="M326" s="121"/>
     </row>
-    <row r="327" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="327" spans="2:13" ht="15.5">
       <c r="B327" s="118" t="s">
         <v>821</v>
       </c>
@@ -33066,7 +33772,7 @@
       <c r="L327" s="120"/>
       <c r="M327" s="121"/>
     </row>
-    <row r="328" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="328" spans="2:13" ht="15.5">
       <c r="B328" s="118" t="s">
         <v>822</v>
       </c>
@@ -33082,7 +33788,7 @@
       <c r="L328" s="120"/>
       <c r="M328" s="121"/>
     </row>
-    <row r="329" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="329" spans="2:13" ht="15.5">
       <c r="B329" s="118" t="s">
         <v>823</v>
       </c>
@@ -33098,7 +33804,7 @@
       <c r="L329" s="120"/>
       <c r="M329" s="121"/>
     </row>
-    <row r="330" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="330" spans="2:13" ht="15.5">
       <c r="B330" s="118" t="s">
         <v>824</v>
       </c>
@@ -33114,7 +33820,7 @@
       <c r="L330" s="120"/>
       <c r="M330" s="121"/>
     </row>
-    <row r="331" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="331" spans="2:13" ht="15.5">
       <c r="B331" s="118" t="s">
         <v>825</v>
       </c>
@@ -33130,7 +33836,7 @@
       <c r="L331" s="120"/>
       <c r="M331" s="121"/>
     </row>
-    <row r="332" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="332" spans="2:13" ht="15.5">
       <c r="B332" s="118" t="s">
         <v>826</v>
       </c>
@@ -33146,7 +33852,7 @@
       <c r="L332" s="120"/>
       <c r="M332" s="121"/>
     </row>
-    <row r="333" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="333" spans="2:13" ht="15.5">
       <c r="B333" s="118" t="s">
         <v>827</v>
       </c>
@@ -33162,7 +33868,7 @@
       <c r="L333" s="120"/>
       <c r="M333" s="121"/>
     </row>
-    <row r="334" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="334" spans="2:13" ht="15.5">
       <c r="B334" s="118" t="s">
         <v>828</v>
       </c>
@@ -33178,7 +33884,7 @@
       <c r="L334" s="120"/>
       <c r="M334" s="121"/>
     </row>
-    <row r="335" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="335" spans="2:13" ht="15.5">
       <c r="B335" s="118" t="s">
         <v>829</v>
       </c>
@@ -33194,7 +33900,7 @@
       <c r="L335" s="120"/>
       <c r="M335" s="121"/>
     </row>
-    <row r="336" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="336" spans="2:13" ht="15.5">
       <c r="B336" s="118" t="s">
         <v>830</v>
       </c>
@@ -33210,7 +33916,7 @@
       <c r="L336" s="120"/>
       <c r="M336" s="121"/>
     </row>
-    <row r="337" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="337" spans="2:13" ht="15.5">
       <c r="B337" s="118" t="s">
         <v>831</v>
       </c>
@@ -33226,7 +33932,7 @@
       <c r="L337" s="120"/>
       <c r="M337" s="121"/>
     </row>
-    <row r="338" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="338" spans="2:13" ht="15.5">
       <c r="B338" s="118" t="s">
         <v>832</v>
       </c>
@@ -33242,7 +33948,7 @@
       <c r="L338" s="120"/>
       <c r="M338" s="121"/>
     </row>
-    <row r="339" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="339" spans="2:13" ht="15.5">
       <c r="B339" s="118" t="s">
         <v>833</v>
       </c>
@@ -33258,7 +33964,7 @@
       <c r="L339" s="120"/>
       <c r="M339" s="121"/>
     </row>
-    <row r="340" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="340" spans="2:13" ht="15.5">
       <c r="B340" s="118" t="s">
         <v>834</v>
       </c>
@@ -33274,7 +33980,7 @@
       <c r="L340" s="120"/>
       <c r="M340" s="121"/>
     </row>
-    <row r="341" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="341" spans="2:13" ht="15.5">
       <c r="B341" s="118" t="s">
         <v>835</v>
       </c>
@@ -33290,7 +33996,7 @@
       <c r="L341" s="120"/>
       <c r="M341" s="121"/>
     </row>
-    <row r="342" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="342" spans="2:13" ht="15.5">
       <c r="B342" s="118" t="s">
         <v>836</v>
       </c>
@@ -33306,7 +34012,7 @@
       <c r="L342" s="120"/>
       <c r="M342" s="121"/>
     </row>
-    <row r="343" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="343" spans="2:13" ht="15.5">
       <c r="B343" s="118" t="s">
         <v>837</v>
       </c>
@@ -33322,7 +34028,7 @@
       <c r="L343" s="120"/>
       <c r="M343" s="121"/>
     </row>
-    <row r="344" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="344" spans="2:13" ht="15.5">
       <c r="B344" s="118" t="s">
         <v>838</v>
       </c>
@@ -33338,7 +34044,7 @@
       <c r="L344" s="120"/>
       <c r="M344" s="121"/>
     </row>
-    <row r="345" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="345" spans="2:13" ht="15.5">
       <c r="B345" s="118" t="s">
         <v>839</v>
       </c>
@@ -33354,7 +34060,7 @@
       <c r="L345" s="120"/>
       <c r="M345" s="121"/>
     </row>
-    <row r="346" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="346" spans="2:13" ht="15.5">
       <c r="B346" s="118" t="s">
         <v>840</v>
       </c>
@@ -33370,7 +34076,7 @@
       <c r="L346" s="120"/>
       <c r="M346" s="121"/>
     </row>
-    <row r="347" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="347" spans="2:13" ht="15.5">
       <c r="B347" s="118" t="s">
         <v>841</v>
       </c>
@@ -33386,7 +34092,7 @@
       <c r="L347" s="120"/>
       <c r="M347" s="121"/>
     </row>
-    <row r="348" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="348" spans="2:13" ht="15.5">
       <c r="B348" s="118" t="s">
         <v>842</v>
       </c>
@@ -33402,7 +34108,7 @@
       <c r="L348" s="120"/>
       <c r="M348" s="121"/>
     </row>
-    <row r="349" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="349" spans="2:13" ht="15.5">
       <c r="B349" s="118" t="s">
         <v>843</v>
       </c>
@@ -33418,7 +34124,7 @@
       <c r="L349" s="120"/>
       <c r="M349" s="121"/>
     </row>
-    <row r="350" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="350" spans="2:13" ht="15.5">
       <c r="B350" s="118" t="s">
         <v>844</v>
       </c>
@@ -33434,7 +34140,7 @@
       <c r="L350" s="120"/>
       <c r="M350" s="121"/>
     </row>
-    <row r="351" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="351" spans="2:13" ht="15.5">
       <c r="B351" s="118" t="s">
         <v>845</v>
       </c>
@@ -33450,7 +34156,7 @@
       <c r="L351" s="120"/>
       <c r="M351" s="121"/>
     </row>
-    <row r="352" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="352" spans="2:13" ht="15.5">
       <c r="B352" s="118" t="s">
         <v>846</v>
       </c>
@@ -33466,7 +34172,7 @@
       <c r="L352" s="120"/>
       <c r="M352" s="121"/>
     </row>
-    <row r="353" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="353" spans="2:13" ht="15.5">
       <c r="B353" s="118" t="s">
         <v>847</v>
       </c>
@@ -33482,7 +34188,7 @@
       <c r="L353" s="120"/>
       <c r="M353" s="121"/>
     </row>
-    <row r="354" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="354" spans="2:13" ht="15.5">
       <c r="B354" s="118" t="s">
         <v>848</v>
       </c>
@@ -33498,7 +34204,7 @@
       <c r="L354" s="120"/>
       <c r="M354" s="121"/>
     </row>
-    <row r="355" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="355" spans="2:13" ht="15.5">
       <c r="B355" s="118" t="s">
         <v>849</v>
       </c>
@@ -33514,7 +34220,7 @@
       <c r="L355" s="120"/>
       <c r="M355" s="121"/>
     </row>
-    <row r="356" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="356" spans="2:13" ht="15.5">
       <c r="B356" s="118" t="s">
         <v>850</v>
       </c>
@@ -33530,7 +34236,7 @@
       <c r="L356" s="120"/>
       <c r="M356" s="121"/>
     </row>
-    <row r="357" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="357" spans="2:13" ht="15.5">
       <c r="B357" s="118" t="s">
         <v>851</v>
       </c>
@@ -33546,7 +34252,7 @@
       <c r="L357" s="120"/>
       <c r="M357" s="121"/>
     </row>
-    <row r="358" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="358" spans="2:13" ht="15.5">
       <c r="B358" s="118" t="s">
         <v>852</v>
       </c>
@@ -33562,7 +34268,7 @@
       <c r="L358" s="120"/>
       <c r="M358" s="121"/>
     </row>
-    <row r="359" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="359" spans="2:13" ht="15.5">
       <c r="B359" s="118" t="s">
         <v>853</v>
       </c>
@@ -33578,7 +34284,7 @@
       <c r="L359" s="120"/>
       <c r="M359" s="121"/>
     </row>
-    <row r="360" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="360" spans="2:13" ht="15.5">
       <c r="B360" s="118" t="s">
         <v>854</v>
       </c>
@@ -33594,7 +34300,7 @@
       <c r="L360" s="120"/>
       <c r="M360" s="121"/>
     </row>
-    <row r="361" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="361" spans="2:13" ht="15.5">
       <c r="B361" s="118" t="s">
         <v>855</v>
       </c>
@@ -33610,7 +34316,7 @@
       <c r="L361" s="120"/>
       <c r="M361" s="121"/>
     </row>
-    <row r="362" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="362" spans="2:13" ht="15.5">
       <c r="B362" s="118" t="s">
         <v>856</v>
       </c>
@@ -33626,7 +34332,7 @@
       <c r="L362" s="120"/>
       <c r="M362" s="121"/>
     </row>
-    <row r="363" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="363" spans="2:13" ht="15.5">
       <c r="B363" s="118" t="s">
         <v>857</v>
       </c>
@@ -33642,7 +34348,7 @@
       <c r="L363" s="120"/>
       <c r="M363" s="121"/>
     </row>
-    <row r="364" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="364" spans="2:13" ht="15.5">
       <c r="B364" s="118" t="s">
         <v>858</v>
       </c>
@@ -33658,7 +34364,7 @@
       <c r="L364" s="120"/>
       <c r="M364" s="121"/>
     </row>
-    <row r="365" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="365" spans="2:13" ht="15.5">
       <c r="B365" s="118" t="s">
         <v>859</v>
       </c>
@@ -33674,7 +34380,7 @@
       <c r="L365" s="120"/>
       <c r="M365" s="121"/>
     </row>
-    <row r="366" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="366" spans="2:13" ht="15.5">
       <c r="B366" s="118" t="s">
         <v>860</v>
       </c>
@@ -33690,7 +34396,7 @@
       <c r="L366" s="120"/>
       <c r="M366" s="121"/>
     </row>
-    <row r="367" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="367" spans="2:13" ht="15.5">
       <c r="B367" s="118" t="s">
         <v>861</v>
       </c>
@@ -33706,7 +34412,7 @@
       <c r="L367" s="120"/>
       <c r="M367" s="121"/>
     </row>
-    <row r="368" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="368" spans="2:13" ht="15.5">
       <c r="B368" s="118" t="s">
         <v>862</v>
       </c>
@@ -33722,7 +34428,7 @@
       <c r="L368" s="120"/>
       <c r="M368" s="121"/>
     </row>
-    <row r="369" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:13" ht="15.5">
       <c r="B369" s="118" t="s">
         <v>863</v>
       </c>
@@ -33738,7 +34444,7 @@
       <c r="L369" s="120"/>
       <c r="M369" s="121"/>
     </row>
-    <row r="370" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:13" ht="15.5">
       <c r="B370" s="118" t="s">
         <v>864</v>
       </c>
@@ -33754,7 +34460,7 @@
       <c r="L370" s="120"/>
       <c r="M370" s="121"/>
     </row>
-    <row r="371" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="371" spans="2:13" ht="15.5">
       <c r="B371" s="118" t="s">
         <v>865</v>
       </c>
@@ -33770,7 +34476,7 @@
       <c r="L371" s="120"/>
       <c r="M371" s="121"/>
     </row>
-    <row r="372" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:13" ht="15.5">
       <c r="B372" s="118" t="s">
         <v>866</v>
       </c>
@@ -33786,7 +34492,7 @@
       <c r="L372" s="120"/>
       <c r="M372" s="121"/>
     </row>
-    <row r="373" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="373" spans="2:13" ht="15.5">
       <c r="B373" s="118" t="s">
         <v>867</v>
       </c>
@@ -33802,7 +34508,7 @@
       <c r="L373" s="120"/>
       <c r="M373" s="121"/>
     </row>
-    <row r="374" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:13" ht="15.5">
       <c r="B374" s="118" t="s">
         <v>868</v>
       </c>
@@ -33818,7 +34524,7 @@
       <c r="L374" s="120"/>
       <c r="M374" s="121"/>
     </row>
-    <row r="375" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:13" ht="15.5">
       <c r="B375" s="118" t="s">
         <v>869</v>
       </c>
@@ -33834,7 +34540,7 @@
       <c r="L375" s="120"/>
       <c r="M375" s="121"/>
     </row>
-    <row r="376" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="376" spans="2:13" ht="15.5">
       <c r="B376" s="118" t="s">
         <v>870</v>
       </c>
@@ -33850,7 +34556,7 @@
       <c r="L376" s="120"/>
       <c r="M376" s="121"/>
     </row>
-    <row r="377" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="377" spans="2:13" ht="15.5">
       <c r="B377" s="118" t="s">
         <v>871</v>
       </c>
@@ -33866,7 +34572,7 @@
       <c r="L377" s="120"/>
       <c r="M377" s="121"/>
     </row>
-    <row r="378" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="378" spans="2:13" ht="15.5">
       <c r="B378" s="118" t="s">
         <v>872</v>
       </c>
@@ -33882,7 +34588,7 @@
       <c r="L378" s="120"/>
       <c r="M378" s="121"/>
     </row>
-    <row r="379" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="379" spans="2:13" ht="15.5">
       <c r="B379" s="118" t="s">
         <v>873</v>
       </c>
@@ -33898,7 +34604,7 @@
       <c r="L379" s="120"/>
       <c r="M379" s="121"/>
     </row>
-    <row r="380" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="380" spans="2:13" ht="15.5">
       <c r="B380" s="118" t="s">
         <v>874</v>
       </c>
@@ -33914,7 +34620,7 @@
       <c r="L380" s="120"/>
       <c r="M380" s="121"/>
     </row>
-    <row r="381" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="381" spans="2:13" ht="15.5">
       <c r="B381" s="118" t="s">
         <v>875</v>
       </c>
@@ -33930,7 +34636,7 @@
       <c r="L381" s="120"/>
       <c r="M381" s="121"/>
     </row>
-    <row r="382" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="382" spans="2:13" ht="15.5">
       <c r="B382" s="118" t="s">
         <v>876</v>
       </c>
@@ -33946,7 +34652,7 @@
       <c r="L382" s="120"/>
       <c r="M382" s="121"/>
     </row>
-    <row r="383" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="383" spans="2:13" ht="15.5">
       <c r="B383" s="118" t="s">
         <v>877</v>
       </c>
@@ -33962,7 +34668,7 @@
       <c r="L383" s="120"/>
       <c r="M383" s="121"/>
     </row>
-    <row r="384" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="384" spans="2:13" ht="15.5">
       <c r="B384" s="118" t="s">
         <v>878</v>
       </c>
@@ -33978,7 +34684,7 @@
       <c r="L384" s="120"/>
       <c r="M384" s="121"/>
     </row>
-    <row r="385" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="385" spans="2:13" ht="15.5">
       <c r="B385" s="118" t="s">
         <v>879</v>
       </c>
@@ -33994,7 +34700,7 @@
       <c r="L385" s="120"/>
       <c r="M385" s="121"/>
     </row>
-    <row r="386" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="386" spans="2:13" ht="15.5">
       <c r="B386" s="118" t="s">
         <v>880</v>
       </c>
@@ -34010,7 +34716,7 @@
       <c r="L386" s="120"/>
       <c r="M386" s="121"/>
     </row>
-    <row r="387" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="387" spans="2:13" ht="15.5">
       <c r="B387" s="118" t="s">
         <v>881</v>
       </c>
@@ -34026,7 +34732,7 @@
       <c r="L387" s="120"/>
       <c r="M387" s="121"/>
     </row>
-    <row r="388" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="2:13" ht="15.5">
       <c r="B388" s="118" t="s">
         <v>882</v>
       </c>
@@ -34042,7 +34748,7 @@
       <c r="L388" s="120"/>
       <c r="M388" s="121"/>
     </row>
-    <row r="389" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:13" ht="15.5">
       <c r="B389" s="118" t="s">
         <v>883</v>
       </c>
@@ -34058,7 +34764,7 @@
       <c r="L389" s="120"/>
       <c r="M389" s="121"/>
     </row>
-    <row r="390" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="390" spans="2:13" ht="15.5">
       <c r="B390" s="118" t="s">
         <v>884</v>
       </c>
@@ -34074,7 +34780,7 @@
       <c r="L390" s="120"/>
       <c r="M390" s="121"/>
     </row>
-    <row r="391" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="391" spans="2:13" ht="15.5">
       <c r="B391" s="118" t="s">
         <v>885</v>
       </c>
@@ -34090,7 +34796,7 @@
       <c r="L391" s="120"/>
       <c r="M391" s="121"/>
     </row>
-    <row r="392" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="392" spans="2:13" ht="15.5">
       <c r="B392" s="118" t="s">
         <v>886</v>
       </c>
@@ -34106,7 +34812,7 @@
       <c r="L392" s="120"/>
       <c r="M392" s="121"/>
     </row>
-    <row r="393" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="393" spans="2:13" ht="15.5">
       <c r="B393" s="118" t="s">
         <v>887</v>
       </c>
@@ -34122,7 +34828,7 @@
       <c r="L393" s="120"/>
       <c r="M393" s="121"/>
     </row>
-    <row r="394" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="394" spans="2:13" ht="15.5">
       <c r="B394" s="118" t="s">
         <v>888</v>
       </c>
@@ -34138,7 +34844,7 @@
       <c r="L394" s="120"/>
       <c r="M394" s="121"/>
     </row>
-    <row r="395" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="395" spans="2:13" ht="15.5">
       <c r="B395" s="118" t="s">
         <v>889</v>
       </c>
@@ -34154,7 +34860,7 @@
       <c r="L395" s="120"/>
       <c r="M395" s="121"/>
     </row>
-    <row r="396" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="396" spans="2:13" ht="15.5">
       <c r="B396" s="118" t="s">
         <v>890</v>
       </c>
@@ -34170,7 +34876,7 @@
       <c r="L396" s="120"/>
       <c r="M396" s="121"/>
     </row>
-    <row r="397" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="397" spans="2:13" ht="15.5">
       <c r="B397" s="118" t="s">
         <v>891</v>
       </c>
@@ -34186,7 +34892,7 @@
       <c r="L397" s="120"/>
       <c r="M397" s="121"/>
     </row>
-    <row r="398" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="398" spans="2:13" ht="15.5">
       <c r="B398" s="118" t="s">
         <v>892</v>
       </c>
@@ -34202,7 +34908,7 @@
       <c r="L398" s="120"/>
       <c r="M398" s="121"/>
     </row>
-    <row r="399" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="399" spans="2:13" ht="15.5">
       <c r="B399" s="118" t="s">
         <v>893</v>
       </c>
@@ -34218,7 +34924,7 @@
       <c r="L399" s="120"/>
       <c r="M399" s="121"/>
     </row>
-    <row r="400" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="400" spans="2:13" ht="15.5">
       <c r="B400" s="118" t="s">
         <v>894</v>
       </c>
@@ -34234,7 +34940,7 @@
       <c r="L400" s="120"/>
       <c r="M400" s="121"/>
     </row>
-    <row r="401" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="401" spans="2:13" ht="15.5">
       <c r="B401" s="118" t="s">
         <v>895</v>
       </c>
@@ -34250,7 +34956,7 @@
       <c r="L401" s="120"/>
       <c r="M401" s="121"/>
     </row>
-    <row r="402" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="402" spans="2:13" ht="15.5">
       <c r="B402" s="118" t="s">
         <v>896</v>
       </c>
@@ -34266,7 +34972,7 @@
       <c r="L402" s="120"/>
       <c r="M402" s="121"/>
     </row>
-    <row r="403" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="403" spans="2:13" ht="15.5">
       <c r="B403" s="118" t="s">
         <v>897</v>
       </c>
@@ -34282,7 +34988,7 @@
       <c r="L403" s="120"/>
       <c r="M403" s="121"/>
     </row>
-    <row r="404" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="404" spans="2:13" ht="15.5">
       <c r="B404" s="118" t="s">
         <v>898</v>
       </c>
@@ -34298,7 +35004,7 @@
       <c r="L404" s="120"/>
       <c r="M404" s="121"/>
     </row>
-    <row r="405" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="405" spans="2:13" ht="15.5">
       <c r="B405" s="118" t="s">
         <v>899</v>
       </c>
@@ -34314,7 +35020,7 @@
       <c r="L405" s="120"/>
       <c r="M405" s="121"/>
     </row>
-    <row r="406" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="406" spans="2:13" ht="15.5">
       <c r="B406" s="118" t="s">
         <v>900</v>
       </c>
@@ -34330,7 +35036,7 @@
       <c r="L406" s="120"/>
       <c r="M406" s="121"/>
     </row>
-    <row r="407" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="407" spans="2:13" ht="15.5">
       <c r="B407" s="118" t="s">
         <v>901</v>
       </c>
@@ -34346,7 +35052,7 @@
       <c r="L407" s="120"/>
       <c r="M407" s="121"/>
     </row>
-    <row r="408" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="408" spans="2:13" ht="15.5">
       <c r="B408" s="118" t="s">
         <v>902</v>
       </c>
@@ -34362,7 +35068,7 @@
       <c r="L408" s="120"/>
       <c r="M408" s="121"/>
     </row>
-    <row r="409" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="409" spans="2:13" ht="15.5">
       <c r="B409" s="118" t="s">
         <v>903</v>
       </c>
@@ -34378,7 +35084,7 @@
       <c r="L409" s="120"/>
       <c r="M409" s="121"/>
     </row>
-    <row r="410" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="410" spans="2:13" ht="15.5">
       <c r="B410" s="118" t="s">
         <v>904</v>
       </c>
@@ -34394,7 +35100,7 @@
       <c r="L410" s="120"/>
       <c r="M410" s="121"/>
     </row>
-    <row r="411" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="411" spans="2:13" ht="15.5">
       <c r="B411" s="118" t="s">
         <v>905</v>
       </c>
@@ -34410,7 +35116,7 @@
       <c r="L411" s="120"/>
       <c r="M411" s="121"/>
     </row>
-    <row r="412" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="412" spans="2:13" ht="15.5">
       <c r="B412" s="118" t="s">
         <v>906</v>
       </c>
@@ -34426,7 +35132,7 @@
       <c r="L412" s="120"/>
       <c r="M412" s="121"/>
     </row>
-    <row r="413" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="413" spans="2:13" ht="15.5">
       <c r="B413" s="118" t="s">
         <v>907</v>
       </c>
@@ -34442,7 +35148,7 @@
       <c r="L413" s="120"/>
       <c r="M413" s="121"/>
     </row>
-    <row r="414" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="414" spans="2:13" ht="15.5">
       <c r="B414" s="118" t="s">
         <v>908</v>
       </c>
@@ -34458,7 +35164,7 @@
       <c r="L414" s="120"/>
       <c r="M414" s="121"/>
     </row>
-    <row r="415" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="415" spans="2:13" ht="15.5">
       <c r="B415" s="118" t="s">
         <v>909</v>
       </c>
@@ -34474,7 +35180,7 @@
       <c r="L415" s="120"/>
       <c r="M415" s="121"/>
     </row>
-    <row r="416" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="416" spans="2:13" ht="15.5">
       <c r="B416" s="118" t="s">
         <v>910</v>
       </c>
@@ -34490,7 +35196,7 @@
       <c r="L416" s="120"/>
       <c r="M416" s="121"/>
     </row>
-    <row r="417" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="417" spans="2:13" ht="15.5">
       <c r="B417" s="118" t="s">
         <v>911</v>
       </c>
@@ -34506,7 +35212,7 @@
       <c r="L417" s="120"/>
       <c r="M417" s="121"/>
     </row>
-    <row r="418" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="418" spans="2:13" ht="15.5">
       <c r="B418" s="118" t="s">
         <v>912</v>
       </c>
@@ -34522,7 +35228,7 @@
       <c r="L418" s="120"/>
       <c r="M418" s="121"/>
     </row>
-    <row r="419" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="419" spans="2:13" ht="15.5">
       <c r="B419" s="118" t="s">
         <v>913</v>
       </c>
@@ -34538,7 +35244,7 @@
       <c r="L419" s="120"/>
       <c r="M419" s="121"/>
     </row>
-    <row r="420" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="420" spans="2:13" ht="15.5">
       <c r="B420" s="118" t="s">
         <v>914</v>
       </c>
@@ -34554,7 +35260,7 @@
       <c r="L420" s="120"/>
       <c r="M420" s="121"/>
     </row>
-    <row r="421" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="421" spans="2:13" ht="15.5">
       <c r="B421" s="118" t="s">
         <v>915</v>
       </c>
@@ -34570,7 +35276,7 @@
       <c r="L421" s="120"/>
       <c r="M421" s="121"/>
     </row>
-    <row r="422" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="422" spans="2:13" ht="15.5">
       <c r="B422" s="118" t="s">
         <v>916</v>
       </c>
@@ -34586,7 +35292,7 @@
       <c r="L422" s="120"/>
       <c r="M422" s="121"/>
     </row>
-    <row r="423" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="423" spans="2:13" ht="15.5">
       <c r="B423" s="118" t="s">
         <v>917</v>
       </c>
@@ -34602,7 +35308,7 @@
       <c r="L423" s="120"/>
       <c r="M423" s="121"/>
     </row>
-    <row r="424" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="424" spans="2:13" ht="15.5">
       <c r="B424" s="118" t="s">
         <v>918</v>
       </c>
@@ -34618,7 +35324,7 @@
       <c r="L424" s="120"/>
       <c r="M424" s="121"/>
     </row>
-    <row r="425" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="425" spans="2:13" ht="15.5">
       <c r="B425" s="118" t="s">
         <v>919</v>
       </c>
@@ -34634,7 +35340,7 @@
       <c r="L425" s="120"/>
       <c r="M425" s="121"/>
     </row>
-    <row r="426" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="426" spans="2:13" ht="15.5">
       <c r="B426" s="118" t="s">
         <v>920</v>
       </c>
@@ -34650,7 +35356,7 @@
       <c r="L426" s="120"/>
       <c r="M426" s="121"/>
     </row>
-    <row r="427" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="427" spans="2:13" ht="15.5">
       <c r="B427" s="118" t="s">
         <v>921</v>
       </c>
@@ -34666,7 +35372,7 @@
       <c r="L427" s="120"/>
       <c r="M427" s="121"/>
     </row>
-    <row r="428" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="428" spans="2:13" ht="15.5">
       <c r="B428" s="118" t="s">
         <v>922</v>
       </c>
@@ -34682,7 +35388,7 @@
       <c r="L428" s="120"/>
       <c r="M428" s="121"/>
     </row>
-    <row r="429" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="429" spans="2:13" ht="15.5">
       <c r="B429" s="118" t="s">
         <v>923</v>
       </c>
@@ -34698,7 +35404,7 @@
       <c r="L429" s="120"/>
       <c r="M429" s="121"/>
     </row>
-    <row r="430" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="430" spans="2:13" ht="15.5">
       <c r="B430" s="118" t="s">
         <v>924</v>
       </c>
@@ -34714,7 +35420,7 @@
       <c r="L430" s="120"/>
       <c r="M430" s="121"/>
     </row>
-    <row r="431" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="431" spans="2:13" ht="15.5">
       <c r="B431" s="118" t="s">
         <v>925</v>
       </c>
@@ -34730,7 +35436,7 @@
       <c r="L431" s="120"/>
       <c r="M431" s="121"/>
     </row>
-    <row r="432" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="432" spans="2:13" ht="15.5">
       <c r="B432" s="118" t="s">
         <v>926</v>
       </c>
@@ -34746,7 +35452,7 @@
       <c r="L432" s="120"/>
       <c r="M432" s="121"/>
     </row>
-    <row r="433" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="433" spans="2:13" ht="15.5">
       <c r="B433" s="118" t="s">
         <v>927</v>
       </c>
@@ -34762,7 +35468,7 @@
       <c r="L433" s="120"/>
       <c r="M433" s="121"/>
     </row>
-    <row r="434" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="434" spans="2:13" ht="15.5">
       <c r="B434" s="118" t="s">
         <v>928</v>
       </c>
@@ -34778,7 +35484,7 @@
       <c r="L434" s="120"/>
       <c r="M434" s="121"/>
     </row>
-    <row r="435" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="435" spans="2:13" ht="15.5">
       <c r="B435" s="118" t="s">
         <v>929</v>
       </c>
@@ -34794,7 +35500,7 @@
       <c r="L435" s="120"/>
       <c r="M435" s="121"/>
     </row>
-    <row r="436" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="436" spans="2:13" ht="15.5">
       <c r="B436" s="118" t="s">
         <v>930</v>
       </c>
@@ -34810,7 +35516,7 @@
       <c r="L436" s="120"/>
       <c r="M436" s="121"/>
     </row>
-    <row r="437" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="437" spans="2:13" ht="15.5">
       <c r="B437" s="118" t="s">
         <v>931</v>
       </c>
@@ -34826,7 +35532,7 @@
       <c r="L437" s="120"/>
       <c r="M437" s="121"/>
     </row>
-    <row r="438" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="438" spans="2:13" ht="15.5">
       <c r="B438" s="118" t="s">
         <v>932</v>
       </c>
@@ -34842,7 +35548,7 @@
       <c r="L438" s="120"/>
       <c r="M438" s="121"/>
     </row>
-    <row r="439" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="439" spans="2:13" ht="15.5">
       <c r="B439" s="118" t="s">
         <v>933</v>
       </c>
@@ -34858,7 +35564,7 @@
       <c r="L439" s="120"/>
       <c r="M439" s="121"/>
     </row>
-    <row r="440" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="440" spans="2:13" ht="15.5">
       <c r="B440" s="118" t="s">
         <v>934</v>
       </c>
@@ -34874,7 +35580,7 @@
       <c r="L440" s="120"/>
       <c r="M440" s="121"/>
     </row>
-    <row r="441" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="441" spans="2:13" ht="15.5">
       <c r="B441" s="118" t="s">
         <v>935</v>
       </c>
@@ -34890,7 +35596,7 @@
       <c r="L441" s="120"/>
       <c r="M441" s="121"/>
     </row>
-    <row r="442" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="442" spans="2:13" ht="15.5">
       <c r="B442" s="118" t="s">
         <v>936</v>
       </c>
@@ -34906,7 +35612,7 @@
       <c r="L442" s="120"/>
       <c r="M442" s="121"/>
     </row>
-    <row r="443" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="443" spans="2:13" ht="15.5">
       <c r="B443" s="118" t="s">
         <v>937</v>
       </c>
@@ -34922,7 +35628,7 @@
       <c r="L443" s="120"/>
       <c r="M443" s="121"/>
     </row>
-    <row r="444" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="444" spans="2:13" ht="15.5">
       <c r="B444" s="118" t="s">
         <v>938</v>
       </c>
@@ -34938,7 +35644,7 @@
       <c r="L444" s="120"/>
       <c r="M444" s="121"/>
     </row>
-    <row r="445" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="445" spans="2:13" ht="15.5">
       <c r="B445" s="118" t="s">
         <v>939</v>
       </c>
@@ -34954,7 +35660,7 @@
       <c r="L445" s="120"/>
       <c r="M445" s="121"/>
     </row>
-    <row r="446" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="446" spans="2:13" ht="15.5">
       <c r="B446" s="118" t="s">
         <v>940</v>
       </c>
@@ -34970,7 +35676,7 @@
       <c r="L446" s="120"/>
       <c r="M446" s="121"/>
     </row>
-    <row r="447" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="447" spans="2:13" ht="15.5">
       <c r="B447" s="118" t="s">
         <v>941</v>
       </c>
@@ -34986,7 +35692,7 @@
       <c r="L447" s="120"/>
       <c r="M447" s="121"/>
     </row>
-    <row r="448" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="448" spans="2:13" ht="15.5">
       <c r="B448" s="118" t="s">
         <v>942</v>
       </c>
@@ -35002,7 +35708,7 @@
       <c r="L448" s="120"/>
       <c r="M448" s="121"/>
     </row>
-    <row r="449" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="449" spans="2:13" ht="15.5">
       <c r="B449" s="118" t="s">
         <v>943</v>
       </c>
@@ -35018,7 +35724,7 @@
       <c r="L449" s="120"/>
       <c r="M449" s="121"/>
     </row>
-    <row r="450" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="450" spans="2:13" ht="15.5">
       <c r="B450" s="118" t="s">
         <v>944</v>
       </c>
@@ -35034,7 +35740,7 @@
       <c r="L450" s="120"/>
       <c r="M450" s="121"/>
     </row>
-    <row r="451" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="451" spans="2:13" ht="15.5">
       <c r="B451" s="118" t="s">
         <v>945</v>
       </c>
@@ -35050,7 +35756,7 @@
       <c r="L451" s="120"/>
       <c r="M451" s="121"/>
     </row>
-    <row r="452" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="452" spans="2:13" ht="15.5">
       <c r="B452" s="118" t="s">
         <v>946</v>
       </c>
@@ -35066,7 +35772,7 @@
       <c r="L452" s="120"/>
       <c r="M452" s="121"/>
     </row>
-    <row r="453" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="453" spans="2:13" ht="15.5">
       <c r="B453" s="118" t="s">
         <v>947</v>
       </c>
@@ -35082,7 +35788,7 @@
       <c r="L453" s="120"/>
       <c r="M453" s="121"/>
     </row>
-    <row r="454" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="454" spans="2:13" ht="15.5">
       <c r="B454" s="118" t="s">
         <v>948</v>
       </c>
@@ -35098,7 +35804,7 @@
       <c r="L454" s="120"/>
       <c r="M454" s="121"/>
     </row>
-    <row r="455" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="455" spans="2:13" ht="15.5">
       <c r="B455" s="118" t="s">
         <v>949</v>
       </c>
@@ -35114,7 +35820,7 @@
       <c r="L455" s="120"/>
       <c r="M455" s="121"/>
     </row>
-    <row r="456" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="456" spans="2:13" ht="15.5">
       <c r="B456" s="118" t="s">
         <v>950</v>
       </c>
@@ -35130,7 +35836,7 @@
       <c r="L456" s="120"/>
       <c r="M456" s="121"/>
     </row>
-    <row r="457" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="457" spans="2:13" ht="15.5">
       <c r="B457" s="118" t="s">
         <v>951</v>
       </c>
@@ -35146,7 +35852,7 @@
       <c r="L457" s="120"/>
       <c r="M457" s="121"/>
     </row>
-    <row r="458" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="458" spans="2:13" ht="15.5">
       <c r="B458" s="118" t="s">
         <v>952</v>
       </c>
@@ -35162,7 +35868,7 @@
       <c r="L458" s="120"/>
       <c r="M458" s="121"/>
     </row>
-    <row r="459" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="459" spans="2:13" ht="15.5">
       <c r="B459" s="118" t="s">
         <v>953</v>
       </c>
@@ -35178,7 +35884,7 @@
       <c r="L459" s="120"/>
       <c r="M459" s="121"/>
     </row>
-    <row r="460" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="460" spans="2:13" ht="15.5">
       <c r="B460" s="118" t="s">
         <v>954</v>
       </c>
@@ -35194,7 +35900,7 @@
       <c r="L460" s="120"/>
       <c r="M460" s="121"/>
     </row>
-    <row r="461" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="461" spans="2:13" ht="15.5">
       <c r="B461" s="118" t="s">
         <v>955</v>
       </c>
@@ -35210,7 +35916,7 @@
       <c r="L461" s="120"/>
       <c r="M461" s="121"/>
     </row>
-    <row r="462" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="462" spans="2:13" ht="15.5">
       <c r="B462" s="118" t="s">
         <v>956</v>
       </c>
@@ -35226,7 +35932,7 @@
       <c r="L462" s="120"/>
       <c r="M462" s="121"/>
     </row>
-    <row r="463" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="463" spans="2:13" ht="15.5">
       <c r="B463" s="118" t="s">
         <v>957</v>
       </c>
@@ -35242,7 +35948,7 @@
       <c r="L463" s="120"/>
       <c r="M463" s="121"/>
     </row>
-    <row r="464" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="464" spans="2:13" ht="15.5">
       <c r="B464" s="118" t="s">
         <v>958</v>
       </c>
@@ -35258,7 +35964,7 @@
       <c r="L464" s="120"/>
       <c r="M464" s="121"/>
     </row>
-    <row r="465" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="465" spans="2:13" ht="15.5">
       <c r="B465" s="118" t="s">
         <v>959</v>
       </c>
@@ -35274,7 +35980,7 @@
       <c r="L465" s="120"/>
       <c r="M465" s="121"/>
     </row>
-    <row r="466" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="466" spans="2:13" ht="15.5">
       <c r="B466" s="118" t="s">
         <v>960</v>
       </c>
@@ -35290,7 +35996,7 @@
       <c r="L466" s="120"/>
       <c r="M466" s="121"/>
     </row>
-    <row r="467" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="467" spans="2:13" ht="15.5">
       <c r="B467" s="118" t="s">
         <v>961</v>
       </c>
@@ -35306,7 +36012,7 @@
       <c r="L467" s="120"/>
       <c r="M467" s="121"/>
     </row>
-    <row r="468" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="468" spans="2:13" ht="15.5">
       <c r="B468" s="118" t="s">
         <v>962</v>
       </c>
@@ -35322,7 +36028,7 @@
       <c r="L468" s="120"/>
       <c r="M468" s="121"/>
     </row>
-    <row r="469" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="469" spans="2:13" ht="15.5">
       <c r="B469" s="118" t="s">
         <v>963</v>
       </c>
@@ -35338,7 +36044,7 @@
       <c r="L469" s="120"/>
       <c r="M469" s="121"/>
     </row>
-    <row r="470" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="470" spans="2:13" ht="15.5">
       <c r="B470" s="118" t="s">
         <v>964</v>
       </c>
@@ -35354,7 +36060,7 @@
       <c r="L470" s="120"/>
       <c r="M470" s="121"/>
     </row>
-    <row r="471" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="471" spans="2:13" ht="15.5">
       <c r="B471" s="118" t="s">
         <v>965</v>
       </c>
@@ -35370,7 +36076,7 @@
       <c r="L471" s="120"/>
       <c r="M471" s="121"/>
     </row>
-    <row r="472" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="472" spans="2:13" ht="15.5">
       <c r="B472" s="118" t="s">
         <v>966</v>
       </c>
@@ -35386,7 +36092,7 @@
       <c r="L472" s="120"/>
       <c r="M472" s="121"/>
     </row>
-    <row r="473" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="473" spans="2:13" ht="15.5">
       <c r="B473" s="118" t="s">
         <v>967</v>
       </c>
@@ -35402,7 +36108,7 @@
       <c r="L473" s="120"/>
       <c r="M473" s="121"/>
     </row>
-    <row r="474" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="474" spans="2:13" ht="15.5">
       <c r="B474" s="118" t="s">
         <v>968</v>
       </c>
@@ -35418,7 +36124,7 @@
       <c r="L474" s="120"/>
       <c r="M474" s="121"/>
     </row>
-    <row r="475" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="475" spans="2:13" ht="15.5">
       <c r="B475" s="118" t="s">
         <v>969</v>
       </c>
@@ -35434,7 +36140,7 @@
       <c r="L475" s="120"/>
       <c r="M475" s="121"/>
     </row>
-    <row r="476" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="476" spans="2:13" ht="15.5">
       <c r="B476" s="118" t="s">
         <v>970</v>
       </c>
@@ -35450,7 +36156,7 @@
       <c r="L476" s="120"/>
       <c r="M476" s="121"/>
     </row>
-    <row r="477" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="477" spans="2:13" ht="15.5">
       <c r="B477" s="118" t="s">
         <v>971</v>
       </c>
@@ -35466,7 +36172,7 @@
       <c r="L477" s="120"/>
       <c r="M477" s="121"/>
     </row>
-    <row r="478" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="478" spans="2:13" ht="15.5">
       <c r="B478" s="118" t="s">
         <v>972</v>
       </c>
@@ -35482,7 +36188,7 @@
       <c r="L478" s="120"/>
       <c r="M478" s="121"/>
     </row>
-    <row r="479" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="479" spans="2:13" ht="15.5">
       <c r="B479" s="118" t="s">
         <v>973</v>
       </c>
@@ -35498,7 +36204,7 @@
       <c r="L479" s="120"/>
       <c r="M479" s="121"/>
     </row>
-    <row r="480" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="480" spans="2:13" ht="15.5">
       <c r="B480" s="118" t="s">
         <v>974</v>
       </c>
@@ -35514,7 +36220,7 @@
       <c r="L480" s="120"/>
       <c r="M480" s="121"/>
     </row>
-    <row r="481" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="481" spans="2:13" ht="15.5">
       <c r="B481" s="118" t="s">
         <v>975</v>
       </c>
@@ -35530,7 +36236,7 @@
       <c r="L481" s="120"/>
       <c r="M481" s="121"/>
     </row>
-    <row r="482" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="482" spans="2:13" ht="15.5">
       <c r="B482" s="118" t="s">
         <v>976</v>
       </c>
@@ -35546,7 +36252,7 @@
       <c r="L482" s="120"/>
       <c r="M482" s="121"/>
     </row>
-    <row r="483" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="483" spans="2:13" ht="15.5">
       <c r="B483" s="118" t="s">
         <v>977</v>
       </c>
@@ -35562,7 +36268,7 @@
       <c r="L483" s="120"/>
       <c r="M483" s="121"/>
     </row>
-    <row r="484" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="484" spans="2:13" ht="15.5">
       <c r="B484" s="118" t="s">
         <v>978</v>
       </c>
@@ -35578,7 +36284,7 @@
       <c r="L484" s="120"/>
       <c r="M484" s="121"/>
     </row>
-    <row r="485" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="485" spans="2:13" ht="15.5">
       <c r="B485" s="118" t="s">
         <v>979</v>
       </c>
@@ -35594,7 +36300,7 @@
       <c r="L485" s="120"/>
       <c r="M485" s="121"/>
     </row>
-    <row r="486" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="486" spans="2:13" ht="15.5">
       <c r="B486" s="118" t="s">
         <v>980</v>
       </c>
@@ -35610,7 +36316,7 @@
       <c r="L486" s="120"/>
       <c r="M486" s="121"/>
     </row>
-    <row r="487" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="487" spans="2:13" ht="15.5">
       <c r="B487" s="118" t="s">
         <v>981</v>
       </c>
@@ -35626,7 +36332,7 @@
       <c r="L487" s="120"/>
       <c r="M487" s="121"/>
     </row>
-    <row r="488" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="488" spans="2:13" ht="15.5">
       <c r="B488" s="118" t="s">
         <v>982</v>
       </c>
@@ -35642,7 +36348,7 @@
       <c r="L488" s="120"/>
       <c r="M488" s="121"/>
     </row>
-    <row r="489" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="489" spans="2:13" ht="15.5">
       <c r="B489" s="118" t="s">
         <v>983</v>
       </c>
@@ -35658,7 +36364,7 @@
       <c r="L489" s="120"/>
       <c r="M489" s="121"/>
     </row>
-    <row r="490" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="490" spans="2:13" ht="15.5">
       <c r="B490" s="118" t="s">
         <v>984</v>
       </c>
@@ -35674,7 +36380,7 @@
       <c r="L490" s="120"/>
       <c r="M490" s="121"/>
     </row>
-    <row r="491" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="491" spans="2:13" ht="15.5">
       <c r="B491" s="118" t="s">
         <v>985</v>
       </c>
@@ -35690,7 +36396,7 @@
       <c r="L491" s="120"/>
       <c r="M491" s="121"/>
     </row>
-    <row r="492" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="492" spans="2:13" ht="15.5">
       <c r="B492" s="118" t="s">
         <v>986</v>
       </c>
@@ -35706,7 +36412,7 @@
       <c r="L492" s="120"/>
       <c r="M492" s="121"/>
     </row>
-    <row r="493" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="493" spans="2:13" ht="15.5">
       <c r="B493" s="118" t="s">
         <v>987</v>
       </c>
@@ -35722,7 +36428,7 @@
       <c r="L493" s="120"/>
       <c r="M493" s="121"/>
     </row>
-    <row r="494" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="494" spans="2:13" ht="15.5">
       <c r="B494" s="118" t="s">
         <v>988</v>
       </c>
@@ -35738,7 +36444,7 @@
       <c r="L494" s="120"/>
       <c r="M494" s="121"/>
     </row>
-    <row r="495" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="495" spans="2:13" ht="15.5">
       <c r="B495" s="118" t="s">
         <v>989</v>
       </c>
@@ -35754,7 +36460,7 @@
       <c r="L495" s="120"/>
       <c r="M495" s="121"/>
     </row>
-    <row r="496" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="496" spans="2:13" ht="15.5">
       <c r="B496" s="118" t="s">
         <v>990</v>
       </c>
@@ -35770,7 +36476,7 @@
       <c r="L496" s="120"/>
       <c r="M496" s="121"/>
     </row>
-    <row r="497" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="497" spans="2:13" ht="15.5">
       <c r="B497" s="118" t="s">
         <v>991</v>
       </c>
@@ -35786,7 +36492,7 @@
       <c r="L497" s="120"/>
       <c r="M497" s="121"/>
     </row>
-    <row r="498" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="498" spans="2:13" ht="15.5">
       <c r="B498" s="118" t="s">
         <v>992</v>
       </c>
@@ -35802,7 +36508,7 @@
       <c r="L498" s="120"/>
       <c r="M498" s="121"/>
     </row>
-    <row r="499" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="499" spans="2:13" ht="15.5">
       <c r="B499" s="118" t="s">
         <v>993</v>
       </c>
@@ -35818,7 +36524,7 @@
       <c r="L499" s="120"/>
       <c r="M499" s="121"/>
     </row>
-    <row r="500" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="500" spans="2:13" ht="15.5">
       <c r="B500" s="118" t="s">
         <v>994</v>
       </c>
@@ -35834,7 +36540,7 @@
       <c r="L500" s="120"/>
       <c r="M500" s="121"/>
     </row>
-    <row r="501" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="501" spans="2:13" ht="15.5">
       <c r="B501" s="118" t="s">
         <v>995</v>
       </c>
@@ -35850,7 +36556,7 @@
       <c r="L501" s="120"/>
       <c r="M501" s="121"/>
     </row>
-    <row r="502" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="502" spans="2:13" ht="15.5">
       <c r="B502" s="118" t="s">
         <v>996</v>
       </c>
@@ -35866,7 +36572,7 @@
       <c r="L502" s="120"/>
       <c r="M502" s="121"/>
     </row>
-    <row r="503" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="503" spans="2:13" ht="15.5">
       <c r="B503" s="118" t="s">
         <v>997</v>
       </c>
@@ -35882,7 +36588,7 @@
       <c r="L503" s="120"/>
       <c r="M503" s="121"/>
     </row>
-    <row r="504" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="504" spans="2:13" ht="15.5">
       <c r="B504" s="118" t="s">
         <v>998</v>
       </c>
@@ -35898,7 +36604,7 @@
       <c r="L504" s="120"/>
       <c r="M504" s="121"/>
     </row>
-    <row r="505" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="505" spans="2:13" ht="15.5">
       <c r="B505" s="118" t="s">
         <v>999</v>
       </c>
@@ -35914,7 +36620,7 @@
       <c r="L505" s="120"/>
       <c r="M505" s="121"/>
     </row>
-    <row r="506" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="506" spans="2:13" ht="15.5">
       <c r="B506" s="118" t="s">
         <v>1000</v>
       </c>
@@ -35930,7 +36636,7 @@
       <c r="L506" s="120"/>
       <c r="M506" s="121"/>
     </row>
-    <row r="507" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="507" spans="2:13" ht="15.5">
       <c r="B507" s="118" t="s">
         <v>1001</v>
       </c>
@@ -35946,7 +36652,7 @@
       <c r="L507" s="120"/>
       <c r="M507" s="121"/>
     </row>
-    <row r="508" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="508" spans="2:13" ht="15.5">
       <c r="B508" s="118" t="s">
         <v>1002</v>
       </c>
@@ -35962,7 +36668,7 @@
       <c r="L508" s="120"/>
       <c r="M508" s="121"/>
     </row>
-    <row r="509" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="509" spans="2:13" ht="15.5">
       <c r="B509" s="118" t="s">
         <v>1003</v>
       </c>
@@ -35978,7 +36684,7 @@
       <c r="L509" s="120"/>
       <c r="M509" s="121"/>
     </row>
-    <row r="510" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="510" spans="2:13" ht="15.5">
       <c r="B510" s="118" t="s">
         <v>1004</v>
       </c>
@@ -35994,7 +36700,7 @@
       <c r="L510" s="120"/>
       <c r="M510" s="121"/>
     </row>
-    <row r="511" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="511" spans="2:13" ht="15.5">
       <c r="B511" s="118" t="s">
         <v>1005</v>
       </c>
@@ -36010,7 +36716,7 @@
       <c r="L511" s="120"/>
       <c r="M511" s="121"/>
     </row>
-    <row r="512" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="512" spans="2:13" ht="15.5">
       <c r="B512" s="118" t="s">
         <v>1006</v>
       </c>
@@ -36026,7 +36732,7 @@
       <c r="L512" s="120"/>
       <c r="M512" s="121"/>
     </row>
-    <row r="513" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="513" spans="2:13" ht="15.5">
       <c r="B513" s="118" t="s">
         <v>1007</v>
       </c>
@@ -36042,7 +36748,7 @@
       <c r="L513" s="120"/>
       <c r="M513" s="121"/>
     </row>
-    <row r="514" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="514" spans="2:13" ht="15.5">
       <c r="B514" s="118" t="s">
         <v>1008</v>
       </c>
@@ -36058,7 +36764,7 @@
       <c r="L514" s="120"/>
       <c r="M514" s="121"/>
     </row>
-    <row r="515" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="515" spans="2:13" ht="15.5">
       <c r="B515" s="118" t="s">
         <v>1009</v>
       </c>
@@ -36074,7 +36780,7 @@
       <c r="L515" s="120"/>
       <c r="M515" s="121"/>
     </row>
-    <row r="516" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="516" spans="2:13" ht="15.5">
       <c r="B516" s="118" t="s">
         <v>1010</v>
       </c>
@@ -36090,7 +36796,7 @@
       <c r="L516" s="120"/>
       <c r="M516" s="121"/>
     </row>
-    <row r="517" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="517" spans="2:13" ht="15.5">
       <c r="B517" s="118" t="s">
         <v>1011</v>
       </c>
@@ -36106,7 +36812,7 @@
       <c r="L517" s="120"/>
       <c r="M517" s="121"/>
     </row>
-    <row r="518" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="518" spans="2:13" ht="15.5">
       <c r="B518" s="118" t="s">
         <v>1012</v>
       </c>
@@ -36122,7 +36828,7 @@
       <c r="L518" s="120"/>
       <c r="M518" s="121"/>
     </row>
-    <row r="519" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="519" spans="2:13" ht="15.5">
       <c r="B519" s="118" t="s">
         <v>1013</v>
       </c>
@@ -36138,7 +36844,7 @@
       <c r="L519" s="120"/>
       <c r="M519" s="121"/>
     </row>
-    <row r="520" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="520" spans="2:13" ht="15.5">
       <c r="B520" s="118" t="s">
         <v>1014</v>
       </c>
@@ -36154,7 +36860,7 @@
       <c r="L520" s="120"/>
       <c r="M520" s="121"/>
     </row>
-    <row r="521" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="521" spans="2:13" ht="15.5">
       <c r="B521" s="118" t="s">
         <v>1015</v>
       </c>
@@ -36170,7 +36876,7 @@
       <c r="L521" s="120"/>
       <c r="M521" s="121"/>
     </row>
-    <row r="522" spans="2:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="522" spans="2:13" ht="15.5">
       <c r="B522" s="122" t="s">
         <v>1016</v>
       </c>

--- a/Lab9_11-v1-3.xlsx
+++ b/Lab9_11-v1-3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/528060d74b554012/Pictures/Lab-9-and-11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{ACD3182E-A37D-3D45-8E9A-761CA87F184A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02F2EE6C-FC6A-4EA3-A3BC-A3D1DB39AA20}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{ACD3182E-A37D-3D45-8E9A-761CA87F184A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DB87DE1-4A1C-44CD-8A74-2CCE8B653AD9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8298,6 +8298,12 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.6863812502485096E-2"/>
+                  <c:y val="-0.20763082015606879"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
             </c:trendlineLbl>
           </c:trendline>
@@ -11551,8 +11557,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12737625" y="14866620"/>
-          <a:ext cx="7947417" cy="2252980"/>
+          <a:off x="12753916" y="14777049"/>
+          <a:ext cx="7957927" cy="2241418"/>
           <a:chOff x="12798585" y="15278100"/>
           <a:chExt cx="7993137" cy="2308860"/>
         </a:xfrm>
@@ -11871,8 +11877,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="17366763" y="17739360"/>
-          <a:ext cx="10667217" cy="3334242"/>
+          <a:off x="17388893" y="17634023"/>
+          <a:ext cx="10682399" cy="3315207"/>
           <a:chOff x="17747763" y="19822160"/>
           <a:chExt cx="10733257" cy="3410442"/>
         </a:xfrm>
@@ -12292,8 +12298,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="26609040" y="15641320"/>
-          <a:ext cx="5148580" cy="2410460"/>
+          <a:off x="26644016" y="15547544"/>
+          <a:ext cx="5155587" cy="2397848"/>
           <a:chOff x="22555200" y="16062960"/>
           <a:chExt cx="5179060" cy="2471420"/>
         </a:xfrm>
@@ -12456,8 +12462,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="21757640" y="15679405"/>
-          <a:ext cx="4409589" cy="1597675"/>
+          <a:off x="21786777" y="15585629"/>
+          <a:ext cx="4415428" cy="1589267"/>
           <a:chOff x="21539200" y="15989285"/>
           <a:chExt cx="4434989" cy="1638315"/>
         </a:xfrm>
@@ -12597,8 +12603,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="28483560" y="18338800"/>
-          <a:ext cx="7696750" cy="1425008"/>
+          <a:off x="28522040" y="18228091"/>
+          <a:ext cx="7707260" cy="1417651"/>
           <a:chOff x="28691840" y="16012160"/>
           <a:chExt cx="7742470" cy="1460568"/>
         </a:xfrm>
